--- a/tests/integration/test_data/test_populate_allotments.xlsx
+++ b/tests/integration/test_data/test_populate_allotments.xlsx
@@ -6,19 +6,19 @@
     <sheet state="visible" name="test1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">test1!$D$1:$D$972</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">test1!$D$1:$D$973</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="fOSRwbsHh20l4Jv6KNlccqYZeOBhDTxFReM5bH6CF5A="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KdMONzKx2RgUMF7Hn9XFoDCdsdI0lszfFr6W9fhYryY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="103">
   <si>
     <t>amdt_idx</t>
   </si>
@@ -348,7 +348,7 @@
     <t>Article add. ap. 11</t>
   </si>
   <si>
-    <t>1100,2037</t>
+    <t>1100,2037, 1654</t>
   </si>
   <si>
     <t>I. – Le 3° du III de l’article L. 245‑6 du code de la sécurité sociale est abrogé.
@@ -356,6 +356,10 @@
   </si>
   <si>
     <t>Le 3° du III de l’article L. 245‑6 du code de la sécurité sociale est abrogé.</t>
+  </si>
+  <si>
+    <t>I. – Le 3° du III de l’article L. 245‑6 du code de la sécurité sociale est abrogé.
+II. – La charge pour l’État et les collectivités territoriales est compensée</t>
   </si>
   <si>
     <t>1807,2439</t>
@@ -468,7 +472,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -507,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -521,9 +524,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -532,6 +532,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -806,7 +812,7 @@
       <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="3"/>
@@ -844,7 +850,7 @@
       <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="3"/>
@@ -882,7 +888,7 @@
       <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="3"/>
@@ -2174,7 +2180,7 @@
       <c r="D38" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F38" s="3"/>
@@ -2212,7 +2218,7 @@
       <c r="D39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F39" s="3"/>
@@ -2962,7 +2968,7 @@
         <v>2821.0</v>
       </c>
       <c r="D59" s="7"/>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F59" s="3"/>
@@ -3717,7 +3723,7 @@
       <c r="C80" s="3">
         <v>2007.0</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E80" s="3" t="s">
@@ -3755,7 +3761,7 @@
       <c r="C81" s="3">
         <v>1812.0</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E81" s="3" t="s">
@@ -3793,7 +3799,7 @@
       <c r="C82" s="3">
         <v>2153.0</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3831,7 +3837,7 @@
       <c r="C83" s="3">
         <v>581.0</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3869,7 +3875,7 @@
       <c r="C84" s="3">
         <v>1710.0</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E84" s="3" t="s">
@@ -3907,7 +3913,7 @@
       <c r="C85" s="3">
         <v>1729.0</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E85" s="3" t="s">
@@ -3939,19 +3945,19 @@
       <c r="A86" s="4">
         <v>84.0</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="11">
         <v>1024.0</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="G86" s="11"/>
+      <c r="G86" s="10"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
@@ -3976,19 +3982,19 @@
       <c r="A87" s="4">
         <v>85.0</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="11">
         <v>1143.0</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="G87" s="11"/>
+      <c r="G87" s="10"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
@@ -4013,19 +4019,19 @@
       <c r="A88" s="4">
         <v>86.0</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="11">
         <v>1603.0</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G88" s="11"/>
+      <c r="G88" s="10"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
@@ -4050,16 +4056,16 @@
       <c r="A89" s="4">
         <v>87.0</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="11">
         <v>743.0</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="10" t="s">
         <v>76</v>
       </c>
       <c r="G89" s="3"/>
@@ -4087,16 +4093,16 @@
       <c r="A90" s="4">
         <v>88.0</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="11">
         <v>1691.0</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="10" t="s">
         <v>77</v>
       </c>
       <c r="G90" s="3"/>
@@ -4124,16 +4130,16 @@
       <c r="A91" s="4">
         <v>89.0</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="11">
         <v>1100.0</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="10" t="s">
         <v>80</v>
       </c>
       <c r="G91" s="3"/>
@@ -4161,16 +4167,16 @@
       <c r="A92" s="4">
         <v>90.0</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92" s="11">
         <v>2037.0</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="10" t="s">
         <v>81</v>
       </c>
       <c r="G92" s="3"/>
@@ -4198,17 +4204,17 @@
       <c r="A93" s="4">
         <v>91.0</v>
       </c>
-      <c r="B93" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C93" s="12">
-        <v>1807.0</v>
+      <c r="B93" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C93" s="14">
+        <v>1654.0</v>
       </c>
       <c r="D93" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E93" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
@@ -4235,16 +4241,16 @@
       <c r="A94" s="4">
         <v>92.0</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="12">
-        <v>2439.0</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E94" s="11" t="s">
+      <c r="C94" s="11">
+        <v>1807.0</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94" s="10" t="s">
         <v>84</v>
       </c>
       <c r="G94" s="3"/>
@@ -4272,17 +4278,17 @@
       <c r="A95" s="4">
         <v>93.0</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="11">
+        <v>2439.0</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="C95" s="12">
-        <v>62.0</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>33</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
@@ -4309,16 +4315,16 @@
       <c r="A96" s="4">
         <v>94.0</v>
       </c>
-      <c r="B96" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C96" s="12">
-        <v>260.0</v>
-      </c>
-      <c r="D96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="C96" s="11">
+        <v>62.0</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E96" s="10" t="s">
         <v>33</v>
       </c>
       <c r="G96" s="3"/>
@@ -4346,16 +4352,16 @@
       <c r="A97" s="4">
         <v>95.0</v>
       </c>
-      <c r="B97" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C97" s="12">
-        <v>2297.0</v>
-      </c>
-      <c r="D97" s="13" t="s">
+      <c r="B97" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="C97" s="11">
+        <v>260.0</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E97" s="10" t="s">
         <v>33</v>
       </c>
       <c r="G97" s="3"/>
@@ -4383,16 +4389,16 @@
       <c r="A98" s="4">
         <v>96.0</v>
       </c>
-      <c r="B98" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C98" s="12">
-        <v>3284.0</v>
-      </c>
-      <c r="D98" s="13" t="s">
+      <c r="B98" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="C98" s="11">
+        <v>2297.0</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>33</v>
       </c>
       <c r="G98" s="3"/>
@@ -4420,17 +4426,17 @@
       <c r="A99" s="4">
         <v>97.0</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C99" s="11">
+        <v>3284.0</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C99" s="12">
-        <v>675.0</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E99" s="11" t="s">
-        <v>89</v>
+      <c r="E99" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
@@ -4457,16 +4463,16 @@
       <c r="A100" s="4">
         <v>98.0</v>
       </c>
-      <c r="B100" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" s="12">
-        <v>836.0</v>
-      </c>
-      <c r="D100" s="13" t="s">
+      <c r="B100" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="C100" s="11">
+        <v>675.0</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E100" s="10" t="s">
         <v>90</v>
       </c>
       <c r="G100" s="3"/>
@@ -4494,17 +4500,17 @@
       <c r="A101" s="4">
         <v>99.0</v>
       </c>
-      <c r="B101" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C101" s="12">
-        <v>913.0</v>
-      </c>
-      <c r="D101" s="13" t="s">
+      <c r="B101" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E101" s="11" t="s">
-        <v>90</v>
+      <c r="C101" s="11">
+        <v>836.0</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
@@ -4531,17 +4537,17 @@
       <c r="A102" s="4">
         <v>100.0</v>
       </c>
-      <c r="B102" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C102" s="12">
-        <v>2394.0</v>
-      </c>
-      <c r="D102" s="13" t="s">
+      <c r="B102" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E102" s="11" t="s">
-        <v>90</v>
+      <c r="C102" s="11">
+        <v>913.0</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
@@ -4568,17 +4574,17 @@
       <c r="A103" s="4">
         <v>101.0</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" s="11">
+        <v>2394.0</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E103" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="C103" s="12">
-        <v>793.0</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E103" s="11" t="s">
-        <v>93</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
@@ -4605,17 +4611,17 @@
       <c r="A104" s="4">
         <v>102.0</v>
       </c>
-      <c r="B104" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" s="12">
-        <v>1713.0</v>
-      </c>
-      <c r="D104" s="13" t="s">
+      <c r="B104" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="C104" s="11">
+        <v>793.0</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>93</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
@@ -4642,16 +4648,16 @@
       <c r="A105" s="4">
         <v>103.0</v>
       </c>
-      <c r="B105" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" s="12">
-        <v>1814.0</v>
-      </c>
-      <c r="D105" s="13" t="s">
+      <c r="B105" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="C105" s="11">
+        <v>1713.0</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E105" s="10" t="s">
         <v>94</v>
       </c>
       <c r="G105" s="3"/>
@@ -4679,17 +4685,17 @@
       <c r="A106" s="4">
         <v>104.0</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C106" s="11">
+        <v>1814.0</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E106" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="C106" s="12">
-        <v>1001.0</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E106" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
@@ -4716,16 +4722,16 @@
       <c r="A107" s="4">
         <v>105.0</v>
       </c>
-      <c r="B107" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C107" s="12">
-        <v>1106.0</v>
-      </c>
-      <c r="D107" s="13" t="s">
+      <c r="B107" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E107" s="14" t="s">
+      <c r="C107" s="11">
+        <v>1001.0</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E107" s="10" t="s">
         <v>98</v>
       </c>
       <c r="G107" s="3"/>
@@ -4753,16 +4759,16 @@
       <c r="A108" s="4">
         <v>106.0</v>
       </c>
-      <c r="B108" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C108" s="12">
-        <v>1164.0</v>
-      </c>
-      <c r="D108" s="13" t="s">
+      <c r="B108" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="C108" s="11">
+        <v>1106.0</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E108" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G108" s="3"/>
@@ -4790,16 +4796,16 @@
       <c r="A109" s="4">
         <v>107.0</v>
       </c>
-      <c r="B109" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C109" s="12">
-        <v>2025.0</v>
-      </c>
-      <c r="D109" s="13" t="s">
+      <c r="B109" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="C109" s="11">
+        <v>1164.0</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E109" s="10" t="s">
         <v>100</v>
       </c>
       <c r="G109" s="3"/>
@@ -4827,16 +4833,16 @@
       <c r="A110" s="4">
         <v>108.0</v>
       </c>
-      <c r="B110" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C110" s="12">
-        <v>2056.0</v>
-      </c>
-      <c r="D110" s="13" t="s">
+      <c r="B110" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E110" s="11" t="s">
+      <c r="C110" s="11">
+        <v>2025.0</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>101</v>
       </c>
       <c r="G110" s="3"/>
@@ -4861,11 +4867,21 @@
       <c r="Z110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="10"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
+      <c r="A111" s="4">
+        <v>109.0</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C111" s="11">
+        <v>2056.0</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
@@ -4890,7 +4906,7 @@
     <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="10"/>
+      <c r="D112" s="9"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -4917,7 +4933,7 @@
     <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="10"/>
+      <c r="D113" s="9"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -4944,7 +4960,7 @@
     <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="10"/>
+      <c r="D114" s="9"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
@@ -4971,7 +4987,7 @@
     <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="10"/>
+      <c r="D115" s="9"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -4998,7 +5014,7 @@
     <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="10"/>
+      <c r="D116" s="9"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
@@ -5025,7 +5041,7 @@
     <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="10"/>
+      <c r="D117" s="9"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
@@ -5052,7 +5068,7 @@
     <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="10"/>
+      <c r="D118" s="9"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -5079,7 +5095,7 @@
     <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="10"/>
+      <c r="D119" s="9"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -5106,7 +5122,7 @@
     <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="10"/>
+      <c r="D120" s="9"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -5133,7 +5149,7 @@
     <row r="121" ht="15.75" customHeight="1">
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="10"/>
+      <c r="D121" s="9"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -5160,7 +5176,7 @@
     <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="10"/>
+      <c r="D122" s="9"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -5187,7 +5203,7 @@
     <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="10"/>
+      <c r="D123" s="9"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
@@ -5214,7 +5230,7 @@
     <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="10"/>
+      <c r="D124" s="9"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -5241,7 +5257,7 @@
     <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="10"/>
+      <c r="D125" s="9"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
@@ -5268,7 +5284,7 @@
     <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="10"/>
+      <c r="D126" s="9"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
@@ -5295,7 +5311,7 @@
     <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="10"/>
+      <c r="D127" s="9"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
@@ -5322,7 +5338,7 @@
     <row r="128" ht="15.75" customHeight="1">
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="10"/>
+      <c r="D128" s="9"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
@@ -5349,7 +5365,7 @@
     <row r="129" ht="15.75" customHeight="1">
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="10"/>
+      <c r="D129" s="9"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -5376,7 +5392,7 @@
     <row r="130" ht="15.75" customHeight="1">
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="10"/>
+      <c r="D130" s="9"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -5403,7 +5419,7 @@
     <row r="131" ht="15.75" customHeight="1">
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="10"/>
+      <c r="D131" s="9"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -5430,7 +5446,7 @@
     <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="10"/>
+      <c r="D132" s="9"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
@@ -5457,7 +5473,7 @@
     <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="10"/>
+      <c r="D133" s="9"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
@@ -5484,7 +5500,7 @@
     <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="10"/>
+      <c r="D134" s="9"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
@@ -5511,7 +5527,7 @@
     <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="10"/>
+      <c r="D135" s="9"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -5538,7 +5554,7 @@
     <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="10"/>
+      <c r="D136" s="9"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
@@ -5565,7 +5581,7 @@
     <row r="137" ht="15.75" customHeight="1">
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="10"/>
+      <c r="D137" s="9"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
@@ -5592,7 +5608,7 @@
     <row r="138" ht="15.75" customHeight="1">
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="10"/>
+      <c r="D138" s="9"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
@@ -5619,7 +5635,7 @@
     <row r="139" ht="15.75" customHeight="1">
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="10"/>
+      <c r="D139" s="9"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
@@ -5646,7 +5662,7 @@
     <row r="140" ht="15.75" customHeight="1">
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="10"/>
+      <c r="D140" s="9"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
@@ -5673,7 +5689,7 @@
     <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="10"/>
+      <c r="D141" s="9"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
@@ -5700,7 +5716,7 @@
     <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="10"/>
+      <c r="D142" s="9"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
@@ -5727,7 +5743,7 @@
     <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="10"/>
+      <c r="D143" s="9"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
@@ -5754,7 +5770,7 @@
     <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="10"/>
+      <c r="D144" s="9"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
@@ -5781,7 +5797,7 @@
     <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="10"/>
+      <c r="D145" s="9"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
@@ -5808,7 +5824,7 @@
     <row r="146" ht="15.75" customHeight="1">
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="10"/>
+      <c r="D146" s="9"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
@@ -5835,7 +5851,7 @@
     <row r="147" ht="15.75" customHeight="1">
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="10"/>
+      <c r="D147" s="9"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
@@ -5862,7 +5878,7 @@
     <row r="148" ht="15.75" customHeight="1">
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="10"/>
+      <c r="D148" s="9"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
@@ -5889,7 +5905,7 @@
     <row r="149" ht="15.75" customHeight="1">
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="10"/>
+      <c r="D149" s="9"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
@@ -5916,7 +5932,7 @@
     <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="10"/>
+      <c r="D150" s="9"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
@@ -5943,7 +5959,7 @@
     <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="10"/>
+      <c r="D151" s="9"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
@@ -5970,7 +5986,7 @@
     <row r="152" ht="15.75" customHeight="1">
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="10"/>
+      <c r="D152" s="9"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -5997,7 +6013,7 @@
     <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="10"/>
+      <c r="D153" s="9"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
@@ -6024,7 +6040,7 @@
     <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="10"/>
+      <c r="D154" s="9"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
@@ -6051,7 +6067,7 @@
     <row r="155" ht="15.75" customHeight="1">
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="10"/>
+      <c r="D155" s="9"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -6078,7 +6094,7 @@
     <row r="156" ht="15.75" customHeight="1">
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="10"/>
+      <c r="D156" s="9"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
@@ -6105,7 +6121,7 @@
     <row r="157" ht="15.75" customHeight="1">
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="10"/>
+      <c r="D157" s="9"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
@@ -6132,7 +6148,7 @@
     <row r="158" ht="15.75" customHeight="1">
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="10"/>
+      <c r="D158" s="9"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
@@ -6159,7 +6175,7 @@
     <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="10"/>
+      <c r="D159" s="9"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -6186,7 +6202,7 @@
     <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="10"/>
+      <c r="D160" s="9"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
@@ -6213,7 +6229,7 @@
     <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="10"/>
+      <c r="D161" s="9"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
@@ -6240,7 +6256,7 @@
     <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="10"/>
+      <c r="D162" s="9"/>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
@@ -6267,7 +6283,7 @@
     <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="10"/>
+      <c r="D163" s="9"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
@@ -6294,7 +6310,7 @@
     <row r="164" ht="15.75" customHeight="1">
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="10"/>
+      <c r="D164" s="9"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -6321,7 +6337,7 @@
     <row r="165" ht="15.75" customHeight="1">
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="10"/>
+      <c r="D165" s="9"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -6348,7 +6364,7 @@
     <row r="166" ht="15.75" customHeight="1">
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="10"/>
+      <c r="D166" s="9"/>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
@@ -6375,7 +6391,7 @@
     <row r="167" ht="15.75" customHeight="1">
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="10"/>
+      <c r="D167" s="9"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
@@ -6402,7 +6418,7 @@
     <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="10"/>
+      <c r="D168" s="9"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -6429,7 +6445,7 @@
     <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="10"/>
+      <c r="D169" s="9"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -6456,7 +6472,7 @@
     <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="10"/>
+      <c r="D170" s="9"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -6483,7 +6499,7 @@
     <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="10"/>
+      <c r="D171" s="9"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -6510,7 +6526,7 @@
     <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="10"/>
+      <c r="D172" s="9"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
@@ -6537,7 +6553,7 @@
     <row r="173" ht="15.75" customHeight="1">
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="10"/>
+      <c r="D173" s="9"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
@@ -6564,7 +6580,7 @@
     <row r="174" ht="15.75" customHeight="1">
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="10"/>
+      <c r="D174" s="9"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
@@ -6591,7 +6607,7 @@
     <row r="175" ht="15.75" customHeight="1">
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="10"/>
+      <c r="D175" s="9"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
@@ -6618,7 +6634,7 @@
     <row r="176" ht="15.75" customHeight="1">
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="10"/>
+      <c r="D176" s="9"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
@@ -6645,7 +6661,7 @@
     <row r="177" ht="15.75" customHeight="1">
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="10"/>
+      <c r="D177" s="9"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
@@ -6672,7 +6688,7 @@
     <row r="178" ht="15.75" customHeight="1">
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="10"/>
+      <c r="D178" s="9"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
@@ -6699,7 +6715,7 @@
     <row r="179" ht="15.75" customHeight="1">
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="10"/>
+      <c r="D179" s="9"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
@@ -6726,7 +6742,7 @@
     <row r="180" ht="15.75" customHeight="1">
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="10"/>
+      <c r="D180" s="9"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
@@ -6753,7 +6769,7 @@
     <row r="181" ht="15.75" customHeight="1">
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="10"/>
+      <c r="D181" s="9"/>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
@@ -6780,7 +6796,7 @@
     <row r="182" ht="15.75" customHeight="1">
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="10"/>
+      <c r="D182" s="9"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
@@ -6807,7 +6823,7 @@
     <row r="183" ht="15.75" customHeight="1">
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="10"/>
+      <c r="D183" s="9"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
@@ -6834,7 +6850,7 @@
     <row r="184" ht="15.75" customHeight="1">
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="10"/>
+      <c r="D184" s="9"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
@@ -6861,7 +6877,7 @@
     <row r="185" ht="15.75" customHeight="1">
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="10"/>
+      <c r="D185" s="9"/>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
@@ -6888,7 +6904,7 @@
     <row r="186" ht="15.75" customHeight="1">
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="10"/>
+      <c r="D186" s="9"/>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
@@ -6915,7 +6931,7 @@
     <row r="187" ht="15.75" customHeight="1">
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="10"/>
+      <c r="D187" s="9"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
@@ -6942,7 +6958,7 @@
     <row r="188" ht="15.75" customHeight="1">
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="10"/>
+      <c r="D188" s="9"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
@@ -6969,7 +6985,7 @@
     <row r="189" ht="15.75" customHeight="1">
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="10"/>
+      <c r="D189" s="9"/>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
@@ -6996,7 +7012,7 @@
     <row r="190" ht="15.75" customHeight="1">
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="10"/>
+      <c r="D190" s="9"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
@@ -7023,7 +7039,7 @@
     <row r="191" ht="15.75" customHeight="1">
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="10"/>
+      <c r="D191" s="9"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
@@ -7050,7 +7066,7 @@
     <row r="192" ht="15.75" customHeight="1">
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="10"/>
+      <c r="D192" s="9"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
@@ -7077,7 +7093,7 @@
     <row r="193" ht="15.75" customHeight="1">
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="10"/>
+      <c r="D193" s="9"/>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
@@ -7104,7 +7120,7 @@
     <row r="194" ht="15.75" customHeight="1">
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="10"/>
+      <c r="D194" s="9"/>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
@@ -7131,7 +7147,7 @@
     <row r="195" ht="15.75" customHeight="1">
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="10"/>
+      <c r="D195" s="9"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
@@ -7158,7 +7174,7 @@
     <row r="196" ht="15.75" customHeight="1">
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="10"/>
+      <c r="D196" s="9"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
@@ -7185,7 +7201,7 @@
     <row r="197" ht="15.75" customHeight="1">
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="10"/>
+      <c r="D197" s="9"/>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
@@ -7212,7 +7228,7 @@
     <row r="198" ht="15.75" customHeight="1">
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="10"/>
+      <c r="D198" s="9"/>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
@@ -7239,7 +7255,7 @@
     <row r="199" ht="15.75" customHeight="1">
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="10"/>
+      <c r="D199" s="9"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
@@ -7266,7 +7282,7 @@
     <row r="200" ht="15.75" customHeight="1">
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="10"/>
+      <c r="D200" s="9"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
@@ -7293,7 +7309,7 @@
     <row r="201" ht="15.75" customHeight="1">
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="10"/>
+      <c r="D201" s="9"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
@@ -7320,7 +7336,7 @@
     <row r="202" ht="15.75" customHeight="1">
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="10"/>
+      <c r="D202" s="9"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
@@ -7347,7 +7363,7 @@
     <row r="203" ht="15.75" customHeight="1">
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="10"/>
+      <c r="D203" s="9"/>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -7374,7 +7390,7 @@
     <row r="204" ht="15.75" customHeight="1">
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="10"/>
+      <c r="D204" s="9"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
@@ -7401,7 +7417,7 @@
     <row r="205" ht="15.75" customHeight="1">
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="10"/>
+      <c r="D205" s="9"/>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
@@ -7428,7 +7444,7 @@
     <row r="206" ht="15.75" customHeight="1">
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="10"/>
+      <c r="D206" s="9"/>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
@@ -7455,7 +7471,7 @@
     <row r="207" ht="15.75" customHeight="1">
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="10"/>
+      <c r="D207" s="9"/>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
@@ -7482,7 +7498,7 @@
     <row r="208" ht="15.75" customHeight="1">
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="10"/>
+      <c r="D208" s="9"/>
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
@@ -7509,7 +7525,7 @@
     <row r="209" ht="15.75" customHeight="1">
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="10"/>
+      <c r="D209" s="9"/>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
@@ -7536,7 +7552,7 @@
     <row r="210" ht="15.75" customHeight="1">
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="10"/>
+      <c r="D210" s="9"/>
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -7563,7 +7579,7 @@
     <row r="211" ht="15.75" customHeight="1">
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="10"/>
+      <c r="D211" s="9"/>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
@@ -7590,7 +7606,7 @@
     <row r="212" ht="15.75" customHeight="1">
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="10"/>
+      <c r="D212" s="9"/>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
@@ -7617,7 +7633,7 @@
     <row r="213" ht="15.75" customHeight="1">
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="10"/>
+      <c r="D213" s="9"/>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
@@ -7644,7 +7660,7 @@
     <row r="214" ht="15.75" customHeight="1">
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="10"/>
+      <c r="D214" s="9"/>
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
@@ -7671,7 +7687,7 @@
     <row r="215" ht="15.75" customHeight="1">
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="10"/>
+      <c r="D215" s="9"/>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="3"/>
@@ -7698,7 +7714,7 @@
     <row r="216" ht="15.75" customHeight="1">
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="10"/>
+      <c r="D216" s="9"/>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
@@ -7725,7 +7741,7 @@
     <row r="217" ht="15.75" customHeight="1">
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="10"/>
+      <c r="D217" s="9"/>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
@@ -7752,7 +7768,7 @@
     <row r="218" ht="15.75" customHeight="1">
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="10"/>
+      <c r="D218" s="9"/>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -7779,7 +7795,7 @@
     <row r="219" ht="15.75" customHeight="1">
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="10"/>
+      <c r="D219" s="9"/>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
@@ -7806,7 +7822,7 @@
     <row r="220" ht="15.75" customHeight="1">
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="10"/>
+      <c r="D220" s="9"/>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -7833,7 +7849,7 @@
     <row r="221" ht="15.75" customHeight="1">
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="10"/>
+      <c r="D221" s="9"/>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -7860,7 +7876,7 @@
     <row r="222" ht="15.75" customHeight="1">
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
-      <c r="D222" s="10"/>
+      <c r="D222" s="9"/>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="3"/>
@@ -7887,7 +7903,7 @@
     <row r="223" ht="15.75" customHeight="1">
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
-      <c r="D223" s="10"/>
+      <c r="D223" s="9"/>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
@@ -7914,7 +7930,7 @@
     <row r="224" ht="15.75" customHeight="1">
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="10"/>
+      <c r="D224" s="9"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
@@ -7941,7 +7957,7 @@
     <row r="225" ht="15.75" customHeight="1">
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
-      <c r="D225" s="10"/>
+      <c r="D225" s="9"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
@@ -7968,7 +7984,7 @@
     <row r="226" ht="15.75" customHeight="1">
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
-      <c r="D226" s="10"/>
+      <c r="D226" s="9"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -7995,7 +8011,7 @@
     <row r="227" ht="15.75" customHeight="1">
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
-      <c r="D227" s="10"/>
+      <c r="D227" s="9"/>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -8022,7 +8038,7 @@
     <row r="228" ht="15.75" customHeight="1">
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
-      <c r="D228" s="10"/>
+      <c r="D228" s="9"/>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -8049,7 +8065,7 @@
     <row r="229" ht="15.75" customHeight="1">
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="10"/>
+      <c r="D229" s="9"/>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -8076,7 +8092,7 @@
     <row r="230" ht="15.75" customHeight="1">
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
-      <c r="D230" s="10"/>
+      <c r="D230" s="9"/>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="G230" s="3"/>
@@ -8103,7 +8119,7 @@
     <row r="231" ht="15.75" customHeight="1">
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
-      <c r="D231" s="10"/>
+      <c r="D231" s="9"/>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
@@ -8130,7 +8146,7 @@
     <row r="232" ht="15.75" customHeight="1">
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="10"/>
+      <c r="D232" s="9"/>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -8157,7 +8173,7 @@
     <row r="233" ht="15.75" customHeight="1">
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
-      <c r="D233" s="10"/>
+      <c r="D233" s="9"/>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -8184,7 +8200,7 @@
     <row r="234" ht="15.75" customHeight="1">
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
-      <c r="D234" s="10"/>
+      <c r="D234" s="9"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -8211,7 +8227,7 @@
     <row r="235" ht="15.75" customHeight="1">
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
-      <c r="D235" s="10"/>
+      <c r="D235" s="9"/>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
@@ -8238,7 +8254,7 @@
     <row r="236" ht="15.75" customHeight="1">
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
-      <c r="D236" s="10"/>
+      <c r="D236" s="9"/>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -8265,7 +8281,7 @@
     <row r="237" ht="15.75" customHeight="1">
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="10"/>
+      <c r="D237" s="9"/>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="G237" s="3"/>
@@ -8292,7 +8308,7 @@
     <row r="238" ht="15.75" customHeight="1">
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="10"/>
+      <c r="D238" s="9"/>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="G238" s="3"/>
@@ -8319,7 +8335,7 @@
     <row r="239" ht="15.75" customHeight="1">
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="10"/>
+      <c r="D239" s="9"/>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
@@ -8346,7 +8362,7 @@
     <row r="240" ht="15.75" customHeight="1">
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="10"/>
+      <c r="D240" s="9"/>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -8373,7 +8389,7 @@
     <row r="241" ht="15.75" customHeight="1">
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="10"/>
+      <c r="D241" s="9"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -8400,7 +8416,7 @@
     <row r="242" ht="15.75" customHeight="1">
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="10"/>
+      <c r="D242" s="9"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -8427,7 +8443,7 @@
     <row r="243" ht="15.75" customHeight="1">
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="10"/>
+      <c r="D243" s="9"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="3"/>
@@ -8454,7 +8470,7 @@
     <row r="244" ht="15.75" customHeight="1">
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="10"/>
+      <c r="D244" s="9"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
@@ -8481,7 +8497,7 @@
     <row r="245" ht="15.75" customHeight="1">
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="10"/>
+      <c r="D245" s="9"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
@@ -8508,7 +8524,7 @@
     <row r="246" ht="15.75" customHeight="1">
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="10"/>
+      <c r="D246" s="9"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
@@ -8535,7 +8551,7 @@
     <row r="247" ht="15.75" customHeight="1">
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="10"/>
+      <c r="D247" s="9"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="3"/>
@@ -8562,7 +8578,7 @@
     <row r="248" ht="15.75" customHeight="1">
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="10"/>
+      <c r="D248" s="9"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
@@ -8589,7 +8605,7 @@
     <row r="249" ht="15.75" customHeight="1">
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="10"/>
+      <c r="D249" s="9"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="G249" s="3"/>
@@ -8616,7 +8632,7 @@
     <row r="250" ht="15.75" customHeight="1">
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="10"/>
+      <c r="D250" s="9"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
@@ -8643,7 +8659,7 @@
     <row r="251" ht="15.75" customHeight="1">
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="10"/>
+      <c r="D251" s="9"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="3"/>
@@ -8670,7 +8686,7 @@
     <row r="252" ht="15.75" customHeight="1">
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
-      <c r="D252" s="10"/>
+      <c r="D252" s="9"/>
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
       <c r="G252" s="3"/>
@@ -8697,7 +8713,7 @@
     <row r="253" ht="15.75" customHeight="1">
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
-      <c r="D253" s="10"/>
+      <c r="D253" s="9"/>
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="G253" s="3"/>
@@ -8724,7 +8740,7 @@
     <row r="254" ht="15.75" customHeight="1">
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="10"/>
+      <c r="D254" s="9"/>
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="G254" s="3"/>
@@ -8751,7 +8767,7 @@
     <row r="255" ht="15.75" customHeight="1">
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
-      <c r="D255" s="10"/>
+      <c r="D255" s="9"/>
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
       <c r="G255" s="3"/>
@@ -8778,7 +8794,7 @@
     <row r="256" ht="15.75" customHeight="1">
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
-      <c r="D256" s="10"/>
+      <c r="D256" s="9"/>
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
       <c r="G256" s="3"/>
@@ -8805,7 +8821,7 @@
     <row r="257" ht="15.75" customHeight="1">
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
-      <c r="D257" s="10"/>
+      <c r="D257" s="9"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
       <c r="G257" s="3"/>
@@ -8832,7 +8848,7 @@
     <row r="258" ht="15.75" customHeight="1">
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
-      <c r="D258" s="10"/>
+      <c r="D258" s="9"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
       <c r="G258" s="3"/>
@@ -8859,7 +8875,7 @@
     <row r="259" ht="15.75" customHeight="1">
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
-      <c r="D259" s="10"/>
+      <c r="D259" s="9"/>
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -8886,7 +8902,7 @@
     <row r="260" ht="15.75" customHeight="1">
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
-      <c r="D260" s="10"/>
+      <c r="D260" s="9"/>
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
       <c r="G260" s="3"/>
@@ -8913,7 +8929,7 @@
     <row r="261" ht="15.75" customHeight="1">
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
-      <c r="D261" s="10"/>
+      <c r="D261" s="9"/>
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
       <c r="G261" s="3"/>
@@ -8940,7 +8956,7 @@
     <row r="262" ht="15.75" customHeight="1">
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
-      <c r="D262" s="10"/>
+      <c r="D262" s="9"/>
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
       <c r="G262" s="3"/>
@@ -8967,7 +8983,7 @@
     <row r="263" ht="15.75" customHeight="1">
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
-      <c r="D263" s="10"/>
+      <c r="D263" s="9"/>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
       <c r="G263" s="3"/>
@@ -8994,7 +9010,7 @@
     <row r="264" ht="15.75" customHeight="1">
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
-      <c r="D264" s="10"/>
+      <c r="D264" s="9"/>
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
       <c r="G264" s="3"/>
@@ -9021,7 +9037,7 @@
     <row r="265" ht="15.75" customHeight="1">
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
-      <c r="D265" s="10"/>
+      <c r="D265" s="9"/>
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
       <c r="G265" s="3"/>
@@ -9048,7 +9064,7 @@
     <row r="266" ht="15.75" customHeight="1">
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
-      <c r="D266" s="10"/>
+      <c r="D266" s="9"/>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
       <c r="G266" s="3"/>
@@ -9075,7 +9091,7 @@
     <row r="267" ht="15.75" customHeight="1">
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
-      <c r="D267" s="10"/>
+      <c r="D267" s="9"/>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
       <c r="G267" s="3"/>
@@ -9102,7 +9118,7 @@
     <row r="268" ht="15.75" customHeight="1">
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
-      <c r="D268" s="10"/>
+      <c r="D268" s="9"/>
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
       <c r="G268" s="3"/>
@@ -9129,7 +9145,7 @@
     <row r="269" ht="15.75" customHeight="1">
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
-      <c r="D269" s="10"/>
+      <c r="D269" s="9"/>
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
       <c r="G269" s="3"/>
@@ -9156,7 +9172,7 @@
     <row r="270" ht="15.75" customHeight="1">
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
-      <c r="D270" s="10"/>
+      <c r="D270" s="9"/>
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
       <c r="G270" s="3"/>
@@ -9183,7 +9199,7 @@
     <row r="271" ht="15.75" customHeight="1">
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
-      <c r="D271" s="10"/>
+      <c r="D271" s="9"/>
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
       <c r="G271" s="3"/>
@@ -9210,7 +9226,7 @@
     <row r="272" ht="15.75" customHeight="1">
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
-      <c r="D272" s="10"/>
+      <c r="D272" s="9"/>
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
       <c r="G272" s="3"/>
@@ -9237,7 +9253,7 @@
     <row r="273" ht="15.75" customHeight="1">
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
-      <c r="D273" s="10"/>
+      <c r="D273" s="9"/>
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
       <c r="G273" s="3"/>
@@ -9264,7 +9280,7 @@
     <row r="274" ht="15.75" customHeight="1">
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
-      <c r="D274" s="10"/>
+      <c r="D274" s="9"/>
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3"/>
@@ -9291,7 +9307,7 @@
     <row r="275" ht="15.75" customHeight="1">
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
-      <c r="D275" s="10"/>
+      <c r="D275" s="9"/>
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
       <c r="G275" s="3"/>
@@ -9318,7 +9334,7 @@
     <row r="276" ht="15.75" customHeight="1">
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
-      <c r="D276" s="10"/>
+      <c r="D276" s="9"/>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
       <c r="G276" s="3"/>
@@ -9345,7 +9361,7 @@
     <row r="277" ht="15.75" customHeight="1">
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
-      <c r="D277" s="10"/>
+      <c r="D277" s="9"/>
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
       <c r="G277" s="3"/>
@@ -9372,7 +9388,7 @@
     <row r="278" ht="15.75" customHeight="1">
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
-      <c r="D278" s="10"/>
+      <c r="D278" s="9"/>
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
       <c r="G278" s="3"/>
@@ -9399,7 +9415,7 @@
     <row r="279" ht="15.75" customHeight="1">
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
-      <c r="D279" s="10"/>
+      <c r="D279" s="9"/>
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="G279" s="3"/>
@@ -9426,7 +9442,7 @@
     <row r="280" ht="15.75" customHeight="1">
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
-      <c r="D280" s="10"/>
+      <c r="D280" s="9"/>
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
       <c r="G280" s="3"/>
@@ -9453,7 +9469,7 @@
     <row r="281" ht="15.75" customHeight="1">
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
-      <c r="D281" s="10"/>
+      <c r="D281" s="9"/>
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
       <c r="G281" s="3"/>
@@ -9480,7 +9496,7 @@
     <row r="282" ht="15.75" customHeight="1">
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="10"/>
+      <c r="D282" s="9"/>
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
       <c r="G282" s="3"/>
@@ -9507,7 +9523,7 @@
     <row r="283" ht="15.75" customHeight="1">
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
-      <c r="D283" s="10"/>
+      <c r="D283" s="9"/>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
       <c r="G283" s="3"/>
@@ -9534,7 +9550,7 @@
     <row r="284" ht="15.75" customHeight="1">
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
-      <c r="D284" s="10"/>
+      <c r="D284" s="9"/>
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
       <c r="G284" s="3"/>
@@ -9561,7 +9577,7 @@
     <row r="285" ht="15.75" customHeight="1">
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
-      <c r="D285" s="10"/>
+      <c r="D285" s="9"/>
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="G285" s="3"/>
@@ -9588,7 +9604,7 @@
     <row r="286" ht="15.75" customHeight="1">
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="10"/>
+      <c r="D286" s="9"/>
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
       <c r="G286" s="3"/>
@@ -9615,7 +9631,7 @@
     <row r="287" ht="15.75" customHeight="1">
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
-      <c r="D287" s="10"/>
+      <c r="D287" s="9"/>
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
       <c r="G287" s="3"/>
@@ -9642,7 +9658,7 @@
     <row r="288" ht="15.75" customHeight="1">
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
-      <c r="D288" s="10"/>
+      <c r="D288" s="9"/>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
       <c r="G288" s="3"/>
@@ -9669,7 +9685,7 @@
     <row r="289" ht="15.75" customHeight="1">
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
-      <c r="D289" s="10"/>
+      <c r="D289" s="9"/>
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
       <c r="G289" s="3"/>
@@ -9696,7 +9712,7 @@
     <row r="290" ht="15.75" customHeight="1">
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
-      <c r="D290" s="10"/>
+      <c r="D290" s="9"/>
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="G290" s="3"/>
@@ -9723,7 +9739,7 @@
     <row r="291" ht="15.75" customHeight="1">
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
-      <c r="D291" s="10"/>
+      <c r="D291" s="9"/>
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="G291" s="3"/>
@@ -9750,7 +9766,7 @@
     <row r="292" ht="15.75" customHeight="1">
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
-      <c r="D292" s="10"/>
+      <c r="D292" s="9"/>
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
       <c r="G292" s="3"/>
@@ -9777,7 +9793,7 @@
     <row r="293" ht="15.75" customHeight="1">
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
-      <c r="D293" s="10"/>
+      <c r="D293" s="9"/>
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
       <c r="G293" s="3"/>
@@ -9804,7 +9820,7 @@
     <row r="294" ht="15.75" customHeight="1">
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
-      <c r="D294" s="10"/>
+      <c r="D294" s="9"/>
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
       <c r="G294" s="3"/>
@@ -9831,7 +9847,7 @@
     <row r="295" ht="15.75" customHeight="1">
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
-      <c r="D295" s="10"/>
+      <c r="D295" s="9"/>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
       <c r="G295" s="3"/>
@@ -9858,7 +9874,7 @@
     <row r="296" ht="15.75" customHeight="1">
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
-      <c r="D296" s="10"/>
+      <c r="D296" s="9"/>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
       <c r="G296" s="3"/>
@@ -9885,7 +9901,7 @@
     <row r="297" ht="15.75" customHeight="1">
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
-      <c r="D297" s="10"/>
+      <c r="D297" s="9"/>
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
       <c r="G297" s="3"/>
@@ -9912,7 +9928,7 @@
     <row r="298" ht="15.75" customHeight="1">
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
-      <c r="D298" s="10"/>
+      <c r="D298" s="9"/>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
       <c r="G298" s="3"/>
@@ -9939,7 +9955,7 @@
     <row r="299" ht="15.75" customHeight="1">
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
-      <c r="D299" s="10"/>
+      <c r="D299" s="9"/>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
       <c r="G299" s="3"/>
@@ -9966,7 +9982,7 @@
     <row r="300" ht="15.75" customHeight="1">
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
-      <c r="D300" s="10"/>
+      <c r="D300" s="9"/>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="3"/>
@@ -9993,7 +10009,7 @@
     <row r="301" ht="15.75" customHeight="1">
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
-      <c r="D301" s="10"/>
+      <c r="D301" s="9"/>
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
       <c r="G301" s="3"/>
@@ -10020,7 +10036,7 @@
     <row r="302" ht="15.75" customHeight="1">
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
-      <c r="D302" s="10"/>
+      <c r="D302" s="9"/>
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="G302" s="3"/>
@@ -10047,7 +10063,7 @@
     <row r="303" ht="15.75" customHeight="1">
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
-      <c r="D303" s="10"/>
+      <c r="D303" s="9"/>
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3"/>
@@ -10074,7 +10090,7 @@
     <row r="304" ht="15.75" customHeight="1">
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
-      <c r="D304" s="10"/>
+      <c r="D304" s="9"/>
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
       <c r="G304" s="3"/>
@@ -10101,7 +10117,7 @@
     <row r="305" ht="15.75" customHeight="1">
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
-      <c r="D305" s="10"/>
+      <c r="D305" s="9"/>
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
       <c r="G305" s="3"/>
@@ -10128,7 +10144,7 @@
     <row r="306" ht="15.75" customHeight="1">
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="10"/>
+      <c r="D306" s="9"/>
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
       <c r="G306" s="3"/>
@@ -10155,7 +10171,7 @@
     <row r="307" ht="15.75" customHeight="1">
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
-      <c r="D307" s="10"/>
+      <c r="D307" s="9"/>
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
       <c r="G307" s="3"/>
@@ -10182,7 +10198,7 @@
     <row r="308" ht="15.75" customHeight="1">
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
-      <c r="D308" s="10"/>
+      <c r="D308" s="9"/>
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
       <c r="G308" s="3"/>
@@ -10209,7 +10225,7 @@
     <row r="309" ht="15.75" customHeight="1">
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
-      <c r="D309" s="10"/>
+      <c r="D309" s="9"/>
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
       <c r="G309" s="3"/>
@@ -10236,7 +10252,7 @@
     <row r="310" ht="15.75" customHeight="1">
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
-      <c r="D310" s="10"/>
+      <c r="D310" s="9"/>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
       <c r="G310" s="3"/>
@@ -10263,7 +10279,7 @@
     <row r="311" ht="15.75" customHeight="1">
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
-      <c r="D311" s="10"/>
+      <c r="D311" s="9"/>
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
       <c r="G311" s="3"/>
@@ -10290,7 +10306,7 @@
     <row r="312" ht="15.75" customHeight="1">
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
-      <c r="D312" s="10"/>
+      <c r="D312" s="9"/>
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
       <c r="G312" s="3"/>
@@ -10317,7 +10333,7 @@
     <row r="313" ht="15.75" customHeight="1">
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
-      <c r="D313" s="10"/>
+      <c r="D313" s="9"/>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
       <c r="G313" s="3"/>
@@ -10344,7 +10360,7 @@
     <row r="314" ht="15.75" customHeight="1">
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
-      <c r="D314" s="10"/>
+      <c r="D314" s="9"/>
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
       <c r="G314" s="3"/>
@@ -10371,7 +10387,7 @@
     <row r="315" ht="15.75" customHeight="1">
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
-      <c r="D315" s="10"/>
+      <c r="D315" s="9"/>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="G315" s="3"/>
@@ -10398,7 +10414,7 @@
     <row r="316" ht="15.75" customHeight="1">
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
-      <c r="D316" s="10"/>
+      <c r="D316" s="9"/>
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="3"/>
@@ -10425,7 +10441,7 @@
     <row r="317" ht="15.75" customHeight="1">
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
-      <c r="D317" s="10"/>
+      <c r="D317" s="9"/>
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
       <c r="G317" s="3"/>
@@ -10452,7 +10468,7 @@
     <row r="318" ht="15.75" customHeight="1">
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
-      <c r="D318" s="10"/>
+      <c r="D318" s="9"/>
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
       <c r="G318" s="3"/>
@@ -10479,7 +10495,7 @@
     <row r="319" ht="15.75" customHeight="1">
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
-      <c r="D319" s="10"/>
+      <c r="D319" s="9"/>
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
       <c r="G319" s="3"/>
@@ -10506,7 +10522,7 @@
     <row r="320" ht="15.75" customHeight="1">
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="10"/>
+      <c r="D320" s="9"/>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="G320" s="3"/>
@@ -10533,7 +10549,7 @@
     <row r="321" ht="15.75" customHeight="1">
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="10"/>
+      <c r="D321" s="9"/>
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="G321" s="3"/>
@@ -10560,7 +10576,7 @@
     <row r="322" ht="15.75" customHeight="1">
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
-      <c r="D322" s="10"/>
+      <c r="D322" s="9"/>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
       <c r="G322" s="3"/>
@@ -10587,7 +10603,7 @@
     <row r="323" ht="15.75" customHeight="1">
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
-      <c r="D323" s="10"/>
+      <c r="D323" s="9"/>
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
       <c r="G323" s="3"/>
@@ -10614,7 +10630,7 @@
     <row r="324" ht="15.75" customHeight="1">
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="10"/>
+      <c r="D324" s="9"/>
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
       <c r="G324" s="3"/>
@@ -10641,7 +10657,7 @@
     <row r="325" ht="15.75" customHeight="1">
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
-      <c r="D325" s="10"/>
+      <c r="D325" s="9"/>
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
       <c r="G325" s="3"/>
@@ -10668,7 +10684,7 @@
     <row r="326" ht="15.75" customHeight="1">
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
-      <c r="D326" s="10"/>
+      <c r="D326" s="9"/>
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="G326" s="3"/>
@@ -10695,7 +10711,7 @@
     <row r="327" ht="15.75" customHeight="1">
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
-      <c r="D327" s="10"/>
+      <c r="D327" s="9"/>
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
       <c r="G327" s="3"/>
@@ -10722,7 +10738,7 @@
     <row r="328" ht="15.75" customHeight="1">
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
-      <c r="D328" s="10"/>
+      <c r="D328" s="9"/>
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="G328" s="3"/>
@@ -10749,7 +10765,7 @@
     <row r="329" ht="15.75" customHeight="1">
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
-      <c r="D329" s="10"/>
+      <c r="D329" s="9"/>
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
       <c r="G329" s="3"/>
@@ -10776,7 +10792,7 @@
     <row r="330" ht="15.75" customHeight="1">
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
-      <c r="D330" s="10"/>
+      <c r="D330" s="9"/>
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
       <c r="G330" s="3"/>
@@ -10803,7 +10819,7 @@
     <row r="331" ht="15.75" customHeight="1">
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
-      <c r="D331" s="10"/>
+      <c r="D331" s="9"/>
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
       <c r="G331" s="3"/>
@@ -10830,7 +10846,7 @@
     <row r="332" ht="15.75" customHeight="1">
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
-      <c r="D332" s="10"/>
+      <c r="D332" s="9"/>
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3"/>
@@ -10857,7 +10873,7 @@
     <row r="333" ht="15.75" customHeight="1">
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
-      <c r="D333" s="10"/>
+      <c r="D333" s="9"/>
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
       <c r="G333" s="3"/>
@@ -10884,7 +10900,7 @@
     <row r="334" ht="15.75" customHeight="1">
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
-      <c r="D334" s="10"/>
+      <c r="D334" s="9"/>
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
       <c r="G334" s="3"/>
@@ -10911,7 +10927,7 @@
     <row r="335" ht="15.75" customHeight="1">
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
-      <c r="D335" s="10"/>
+      <c r="D335" s="9"/>
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
       <c r="G335" s="3"/>
@@ -10938,7 +10954,7 @@
     <row r="336" ht="15.75" customHeight="1">
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
-      <c r="D336" s="10"/>
+      <c r="D336" s="9"/>
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
       <c r="G336" s="3"/>
@@ -10965,7 +10981,7 @@
     <row r="337" ht="15.75" customHeight="1">
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
-      <c r="D337" s="10"/>
+      <c r="D337" s="9"/>
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
       <c r="G337" s="3"/>
@@ -10992,7 +11008,7 @@
     <row r="338" ht="15.75" customHeight="1">
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
-      <c r="D338" s="10"/>
+      <c r="D338" s="9"/>
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
       <c r="G338" s="3"/>
@@ -11019,7 +11035,7 @@
     <row r="339" ht="15.75" customHeight="1">
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
-      <c r="D339" s="10"/>
+      <c r="D339" s="9"/>
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
       <c r="G339" s="3"/>
@@ -11046,7 +11062,7 @@
     <row r="340" ht="15.75" customHeight="1">
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
-      <c r="D340" s="10"/>
+      <c r="D340" s="9"/>
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
       <c r="G340" s="3"/>
@@ -11073,7 +11089,7 @@
     <row r="341" ht="15.75" customHeight="1">
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
-      <c r="D341" s="10"/>
+      <c r="D341" s="9"/>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="G341" s="3"/>
@@ -11100,7 +11116,7 @@
     <row r="342" ht="15.75" customHeight="1">
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
-      <c r="D342" s="10"/>
+      <c r="D342" s="9"/>
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
       <c r="G342" s="3"/>
@@ -11127,7 +11143,7 @@
     <row r="343" ht="15.75" customHeight="1">
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
-      <c r="D343" s="10"/>
+      <c r="D343" s="9"/>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
       <c r="G343" s="3"/>
@@ -11154,7 +11170,7 @@
     <row r="344" ht="15.75" customHeight="1">
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
-      <c r="D344" s="10"/>
+      <c r="D344" s="9"/>
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
       <c r="G344" s="3"/>
@@ -11181,7 +11197,7 @@
     <row r="345" ht="15.75" customHeight="1">
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
-      <c r="D345" s="10"/>
+      <c r="D345" s="9"/>
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
       <c r="G345" s="3"/>
@@ -11208,7 +11224,7 @@
     <row r="346" ht="15.75" customHeight="1">
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
-      <c r="D346" s="10"/>
+      <c r="D346" s="9"/>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
       <c r="G346" s="3"/>
@@ -11235,7 +11251,7 @@
     <row r="347" ht="15.75" customHeight="1">
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
-      <c r="D347" s="10"/>
+      <c r="D347" s="9"/>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
       <c r="G347" s="3"/>
@@ -11262,7 +11278,7 @@
     <row r="348" ht="15.75" customHeight="1">
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
-      <c r="D348" s="10"/>
+      <c r="D348" s="9"/>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
       <c r="G348" s="3"/>
@@ -11289,7 +11305,7 @@
     <row r="349" ht="15.75" customHeight="1">
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
-      <c r="D349" s="10"/>
+      <c r="D349" s="9"/>
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
       <c r="G349" s="3"/>
@@ -11316,7 +11332,7 @@
     <row r="350" ht="15.75" customHeight="1">
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
-      <c r="D350" s="10"/>
+      <c r="D350" s="9"/>
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
       <c r="G350" s="3"/>
@@ -11343,7 +11359,7 @@
     <row r="351" ht="15.75" customHeight="1">
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
-      <c r="D351" s="10"/>
+      <c r="D351" s="9"/>
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
       <c r="G351" s="3"/>
@@ -11370,7 +11386,7 @@
     <row r="352" ht="15.75" customHeight="1">
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
-      <c r="D352" s="10"/>
+      <c r="D352" s="9"/>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
       <c r="G352" s="3"/>
@@ -11397,7 +11413,7 @@
     <row r="353" ht="15.75" customHeight="1">
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
-      <c r="D353" s="10"/>
+      <c r="D353" s="9"/>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
       <c r="G353" s="3"/>
@@ -11424,7 +11440,7 @@
     <row r="354" ht="15.75" customHeight="1">
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
-      <c r="D354" s="10"/>
+      <c r="D354" s="9"/>
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
       <c r="G354" s="3"/>
@@ -11451,7 +11467,7 @@
     <row r="355" ht="15.75" customHeight="1">
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
-      <c r="D355" s="10"/>
+      <c r="D355" s="9"/>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
       <c r="G355" s="3"/>
@@ -11478,7 +11494,7 @@
     <row r="356" ht="15.75" customHeight="1">
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
-      <c r="D356" s="10"/>
+      <c r="D356" s="9"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
       <c r="G356" s="3"/>
@@ -11505,7 +11521,7 @@
     <row r="357" ht="15.75" customHeight="1">
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
-      <c r="D357" s="10"/>
+      <c r="D357" s="9"/>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
       <c r="G357" s="3"/>
@@ -11532,7 +11548,7 @@
     <row r="358" ht="15.75" customHeight="1">
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
-      <c r="D358" s="10"/>
+      <c r="D358" s="9"/>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
       <c r="G358" s="3"/>
@@ -11559,7 +11575,7 @@
     <row r="359" ht="15.75" customHeight="1">
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
-      <c r="D359" s="10"/>
+      <c r="D359" s="9"/>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
       <c r="G359" s="3"/>
@@ -11586,7 +11602,7 @@
     <row r="360" ht="15.75" customHeight="1">
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
-      <c r="D360" s="10"/>
+      <c r="D360" s="9"/>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
       <c r="G360" s="3"/>
@@ -11613,7 +11629,7 @@
     <row r="361" ht="15.75" customHeight="1">
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
-      <c r="D361" s="10"/>
+      <c r="D361" s="9"/>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3"/>
@@ -11640,7 +11656,7 @@
     <row r="362" ht="15.75" customHeight="1">
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
-      <c r="D362" s="10"/>
+      <c r="D362" s="9"/>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
       <c r="G362" s="3"/>
@@ -11667,7 +11683,7 @@
     <row r="363" ht="15.75" customHeight="1">
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
-      <c r="D363" s="10"/>
+      <c r="D363" s="9"/>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
       <c r="G363" s="3"/>
@@ -11694,7 +11710,7 @@
     <row r="364" ht="15.75" customHeight="1">
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
-      <c r="D364" s="10"/>
+      <c r="D364" s="9"/>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
       <c r="G364" s="3"/>
@@ -11721,7 +11737,7 @@
     <row r="365" ht="15.75" customHeight="1">
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
-      <c r="D365" s="10"/>
+      <c r="D365" s="9"/>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
       <c r="G365" s="3"/>
@@ -11748,7 +11764,7 @@
     <row r="366" ht="15.75" customHeight="1">
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
-      <c r="D366" s="10"/>
+      <c r="D366" s="9"/>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
       <c r="G366" s="3"/>
@@ -11775,7 +11791,7 @@
     <row r="367" ht="15.75" customHeight="1">
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="10"/>
+      <c r="D367" s="9"/>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
       <c r="G367" s="3"/>
@@ -11802,7 +11818,7 @@
     <row r="368" ht="15.75" customHeight="1">
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="10"/>
+      <c r="D368" s="9"/>
       <c r="E368" s="3"/>
       <c r="F368" s="3"/>
       <c r="G368" s="3"/>
@@ -11829,7 +11845,7 @@
     <row r="369" ht="15.75" customHeight="1">
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
-      <c r="D369" s="10"/>
+      <c r="D369" s="9"/>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
       <c r="G369" s="3"/>
@@ -11856,7 +11872,7 @@
     <row r="370" ht="15.75" customHeight="1">
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
-      <c r="D370" s="10"/>
+      <c r="D370" s="9"/>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
       <c r="G370" s="3"/>
@@ -11883,7 +11899,7 @@
     <row r="371" ht="15.75" customHeight="1">
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
-      <c r="D371" s="10"/>
+      <c r="D371" s="9"/>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
       <c r="G371" s="3"/>
@@ -11910,7 +11926,7 @@
     <row r="372" ht="15.75" customHeight="1">
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
-      <c r="D372" s="10"/>
+      <c r="D372" s="9"/>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
       <c r="G372" s="3"/>
@@ -11937,7 +11953,7 @@
     <row r="373" ht="15.75" customHeight="1">
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
-      <c r="D373" s="10"/>
+      <c r="D373" s="9"/>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
       <c r="G373" s="3"/>
@@ -11964,7 +11980,7 @@
     <row r="374" ht="15.75" customHeight="1">
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
-      <c r="D374" s="10"/>
+      <c r="D374" s="9"/>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
       <c r="G374" s="3"/>
@@ -11991,7 +12007,7 @@
     <row r="375" ht="15.75" customHeight="1">
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
-      <c r="D375" s="10"/>
+      <c r="D375" s="9"/>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
       <c r="G375" s="3"/>
@@ -12018,7 +12034,7 @@
     <row r="376" ht="15.75" customHeight="1">
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
-      <c r="D376" s="10"/>
+      <c r="D376" s="9"/>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
@@ -12045,7 +12061,7 @@
     <row r="377" ht="15.75" customHeight="1">
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
-      <c r="D377" s="10"/>
+      <c r="D377" s="9"/>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
       <c r="G377" s="3"/>
@@ -12072,7 +12088,7 @@
     <row r="378" ht="15.75" customHeight="1">
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="10"/>
+      <c r="D378" s="9"/>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
       <c r="G378" s="3"/>
@@ -12099,7 +12115,7 @@
     <row r="379" ht="15.75" customHeight="1">
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="10"/>
+      <c r="D379" s="9"/>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
       <c r="G379" s="3"/>
@@ -12126,7 +12142,7 @@
     <row r="380" ht="15.75" customHeight="1">
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="10"/>
+      <c r="D380" s="9"/>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
       <c r="G380" s="3"/>
@@ -12153,7 +12169,7 @@
     <row r="381" ht="15.75" customHeight="1">
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
-      <c r="D381" s="10"/>
+      <c r="D381" s="9"/>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
       <c r="G381" s="3"/>
@@ -12180,7 +12196,7 @@
     <row r="382" ht="15.75" customHeight="1">
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="10"/>
+      <c r="D382" s="9"/>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
       <c r="G382" s="3"/>
@@ -12207,7 +12223,7 @@
     <row r="383" ht="15.75" customHeight="1">
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
-      <c r="D383" s="10"/>
+      <c r="D383" s="9"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
       <c r="G383" s="3"/>
@@ -12234,7 +12250,7 @@
     <row r="384" ht="15.75" customHeight="1">
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
-      <c r="D384" s="10"/>
+      <c r="D384" s="9"/>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
       <c r="G384" s="3"/>
@@ -12261,7 +12277,7 @@
     <row r="385" ht="15.75" customHeight="1">
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
-      <c r="D385" s="10"/>
+      <c r="D385" s="9"/>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
       <c r="G385" s="3"/>
@@ -12288,7 +12304,7 @@
     <row r="386" ht="15.75" customHeight="1">
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
-      <c r="D386" s="10"/>
+      <c r="D386" s="9"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
       <c r="G386" s="3"/>
@@ -12315,7 +12331,7 @@
     <row r="387" ht="15.75" customHeight="1">
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
-      <c r="D387" s="10"/>
+      <c r="D387" s="9"/>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
       <c r="G387" s="3"/>
@@ -12342,7 +12358,7 @@
     <row r="388" ht="15.75" customHeight="1">
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
-      <c r="D388" s="10"/>
+      <c r="D388" s="9"/>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
       <c r="G388" s="3"/>
@@ -12369,7 +12385,7 @@
     <row r="389" ht="15.75" customHeight="1">
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
-      <c r="D389" s="10"/>
+      <c r="D389" s="9"/>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
       <c r="G389" s="3"/>
@@ -12396,7 +12412,7 @@
     <row r="390" ht="15.75" customHeight="1">
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
-      <c r="D390" s="10"/>
+      <c r="D390" s="9"/>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3"/>
@@ -12423,7 +12439,7 @@
     <row r="391" ht="15.75" customHeight="1">
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
-      <c r="D391" s="10"/>
+      <c r="D391" s="9"/>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
       <c r="G391" s="3"/>
@@ -12450,7 +12466,7 @@
     <row r="392" ht="15.75" customHeight="1">
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
-      <c r="D392" s="10"/>
+      <c r="D392" s="9"/>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
       <c r="G392" s="3"/>
@@ -12477,7 +12493,7 @@
     <row r="393" ht="15.75" customHeight="1">
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
-      <c r="D393" s="10"/>
+      <c r="D393" s="9"/>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
       <c r="G393" s="3"/>
@@ -12504,7 +12520,7 @@
     <row r="394" ht="15.75" customHeight="1">
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
-      <c r="D394" s="10"/>
+      <c r="D394" s="9"/>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
       <c r="G394" s="3"/>
@@ -12531,7 +12547,7 @@
     <row r="395" ht="15.75" customHeight="1">
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
-      <c r="D395" s="10"/>
+      <c r="D395" s="9"/>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
       <c r="G395" s="3"/>
@@ -12558,7 +12574,7 @@
     <row r="396" ht="15.75" customHeight="1">
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
-      <c r="D396" s="10"/>
+      <c r="D396" s="9"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
       <c r="G396" s="3"/>
@@ -12585,7 +12601,7 @@
     <row r="397" ht="15.75" customHeight="1">
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
-      <c r="D397" s="10"/>
+      <c r="D397" s="9"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
       <c r="G397" s="3"/>
@@ -12612,7 +12628,7 @@
     <row r="398" ht="15.75" customHeight="1">
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
-      <c r="D398" s="10"/>
+      <c r="D398" s="9"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
       <c r="G398" s="3"/>
@@ -12639,7 +12655,7 @@
     <row r="399" ht="15.75" customHeight="1">
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
-      <c r="D399" s="10"/>
+      <c r="D399" s="9"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
       <c r="G399" s="3"/>
@@ -12666,7 +12682,7 @@
     <row r="400" ht="15.75" customHeight="1">
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
-      <c r="D400" s="10"/>
+      <c r="D400" s="9"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
       <c r="G400" s="3"/>
@@ -12693,7 +12709,7 @@
     <row r="401" ht="15.75" customHeight="1">
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
-      <c r="D401" s="10"/>
+      <c r="D401" s="9"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
       <c r="G401" s="3"/>
@@ -12720,7 +12736,7 @@
     <row r="402" ht="15.75" customHeight="1">
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
-      <c r="D402" s="10"/>
+      <c r="D402" s="9"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
       <c r="G402" s="3"/>
@@ -12747,7 +12763,7 @@
     <row r="403" ht="15.75" customHeight="1">
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
-      <c r="D403" s="10"/>
+      <c r="D403" s="9"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
       <c r="G403" s="3"/>
@@ -12774,7 +12790,7 @@
     <row r="404" ht="15.75" customHeight="1">
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
-      <c r="D404" s="10"/>
+      <c r="D404" s="9"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
       <c r="G404" s="3"/>
@@ -12801,7 +12817,7 @@
     <row r="405" ht="15.75" customHeight="1">
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
-      <c r="D405" s="10"/>
+      <c r="D405" s="9"/>
       <c r="E405" s="3"/>
       <c r="F405" s="3"/>
       <c r="G405" s="3"/>
@@ -12828,7 +12844,7 @@
     <row r="406" ht="15.75" customHeight="1">
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
-      <c r="D406" s="10"/>
+      <c r="D406" s="9"/>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
       <c r="G406" s="3"/>
@@ -12855,7 +12871,7 @@
     <row r="407" ht="15.75" customHeight="1">
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
-      <c r="D407" s="10"/>
+      <c r="D407" s="9"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
       <c r="G407" s="3"/>
@@ -12882,7 +12898,7 @@
     <row r="408" ht="15.75" customHeight="1">
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
-      <c r="D408" s="10"/>
+      <c r="D408" s="9"/>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
       <c r="G408" s="3"/>
@@ -12909,7 +12925,7 @@
     <row r="409" ht="15.75" customHeight="1">
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
-      <c r="D409" s="10"/>
+      <c r="D409" s="9"/>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
       <c r="G409" s="3"/>
@@ -12936,7 +12952,7 @@
     <row r="410" ht="15.75" customHeight="1">
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
-      <c r="D410" s="10"/>
+      <c r="D410" s="9"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="3"/>
@@ -12963,7 +12979,7 @@
     <row r="411" ht="15.75" customHeight="1">
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
-      <c r="D411" s="10"/>
+      <c r="D411" s="9"/>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
       <c r="G411" s="3"/>
@@ -12990,7 +13006,7 @@
     <row r="412" ht="15.75" customHeight="1">
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
-      <c r="D412" s="10"/>
+      <c r="D412" s="9"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
       <c r="G412" s="3"/>
@@ -13017,7 +13033,7 @@
     <row r="413" ht="15.75" customHeight="1">
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
-      <c r="D413" s="10"/>
+      <c r="D413" s="9"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
       <c r="G413" s="3"/>
@@ -13044,7 +13060,7 @@
     <row r="414" ht="15.75" customHeight="1">
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
-      <c r="D414" s="10"/>
+      <c r="D414" s="9"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
       <c r="G414" s="3"/>
@@ -13071,7 +13087,7 @@
     <row r="415" ht="15.75" customHeight="1">
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
-      <c r="D415" s="10"/>
+      <c r="D415" s="9"/>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
       <c r="G415" s="3"/>
@@ -13098,7 +13114,7 @@
     <row r="416" ht="15.75" customHeight="1">
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
-      <c r="D416" s="10"/>
+      <c r="D416" s="9"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
       <c r="G416" s="3"/>
@@ -13125,7 +13141,7 @@
     <row r="417" ht="15.75" customHeight="1">
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
-      <c r="D417" s="10"/>
+      <c r="D417" s="9"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
       <c r="G417" s="3"/>
@@ -13152,7 +13168,7 @@
     <row r="418" ht="15.75" customHeight="1">
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
-      <c r="D418" s="10"/>
+      <c r="D418" s="9"/>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
       <c r="G418" s="3"/>
@@ -13179,7 +13195,7 @@
     <row r="419" ht="15.75" customHeight="1">
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
-      <c r="D419" s="10"/>
+      <c r="D419" s="9"/>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3"/>
@@ -13206,7 +13222,7 @@
     <row r="420" ht="15.75" customHeight="1">
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
-      <c r="D420" s="10"/>
+      <c r="D420" s="9"/>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
       <c r="G420" s="3"/>
@@ -13233,7 +13249,7 @@
     <row r="421" ht="15.75" customHeight="1">
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
-      <c r="D421" s="10"/>
+      <c r="D421" s="9"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
       <c r="G421" s="3"/>
@@ -13260,7 +13276,7 @@
     <row r="422" ht="15.75" customHeight="1">
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
-      <c r="D422" s="10"/>
+      <c r="D422" s="9"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
       <c r="G422" s="3"/>
@@ -13287,7 +13303,7 @@
     <row r="423" ht="15.75" customHeight="1">
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
-      <c r="D423" s="10"/>
+      <c r="D423" s="9"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
       <c r="G423" s="3"/>
@@ -13314,7 +13330,7 @@
     <row r="424" ht="15.75" customHeight="1">
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
-      <c r="D424" s="10"/>
+      <c r="D424" s="9"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
       <c r="G424" s="3"/>
@@ -13341,7 +13357,7 @@
     <row r="425" ht="15.75" customHeight="1">
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
-      <c r="D425" s="10"/>
+      <c r="D425" s="9"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
       <c r="G425" s="3"/>
@@ -13368,7 +13384,7 @@
     <row r="426" ht="15.75" customHeight="1">
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
-      <c r="D426" s="10"/>
+      <c r="D426" s="9"/>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
       <c r="G426" s="3"/>
@@ -13395,7 +13411,7 @@
     <row r="427" ht="15.75" customHeight="1">
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
-      <c r="D427" s="10"/>
+      <c r="D427" s="9"/>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
       <c r="G427" s="3"/>
@@ -13422,7 +13438,7 @@
     <row r="428" ht="15.75" customHeight="1">
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
-      <c r="D428" s="10"/>
+      <c r="D428" s="9"/>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
       <c r="G428" s="3"/>
@@ -13449,7 +13465,7 @@
     <row r="429" ht="15.75" customHeight="1">
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
-      <c r="D429" s="10"/>
+      <c r="D429" s="9"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
       <c r="G429" s="3"/>
@@ -13476,7 +13492,7 @@
     <row r="430" ht="15.75" customHeight="1">
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
-      <c r="D430" s="10"/>
+      <c r="D430" s="9"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
       <c r="G430" s="3"/>
@@ -13503,7 +13519,7 @@
     <row r="431" ht="15.75" customHeight="1">
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
-      <c r="D431" s="10"/>
+      <c r="D431" s="9"/>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
       <c r="G431" s="3"/>
@@ -13530,7 +13546,7 @@
     <row r="432" ht="15.75" customHeight="1">
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
-      <c r="D432" s="10"/>
+      <c r="D432" s="9"/>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
       <c r="G432" s="3"/>
@@ -13557,7 +13573,7 @@
     <row r="433" ht="15.75" customHeight="1">
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
-      <c r="D433" s="10"/>
+      <c r="D433" s="9"/>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
       <c r="G433" s="3"/>
@@ -13584,7 +13600,7 @@
     <row r="434" ht="15.75" customHeight="1">
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
-      <c r="D434" s="10"/>
+      <c r="D434" s="9"/>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
       <c r="G434" s="3"/>
@@ -13611,7 +13627,7 @@
     <row r="435" ht="15.75" customHeight="1">
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
-      <c r="D435" s="10"/>
+      <c r="D435" s="9"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
       <c r="G435" s="3"/>
@@ -13638,7 +13654,7 @@
     <row r="436" ht="15.75" customHeight="1">
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
-      <c r="D436" s="10"/>
+      <c r="D436" s="9"/>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
       <c r="G436" s="3"/>
@@ -13665,7 +13681,7 @@
     <row r="437" ht="15.75" customHeight="1">
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
-      <c r="D437" s="10"/>
+      <c r="D437" s="9"/>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
       <c r="G437" s="3"/>
@@ -13692,7 +13708,7 @@
     <row r="438" ht="15.75" customHeight="1">
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
-      <c r="D438" s="10"/>
+      <c r="D438" s="9"/>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
       <c r="G438" s="3"/>
@@ -13719,7 +13735,7 @@
     <row r="439" ht="15.75" customHeight="1">
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
-      <c r="D439" s="10"/>
+      <c r="D439" s="9"/>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
       <c r="G439" s="3"/>
@@ -13746,7 +13762,7 @@
     <row r="440" ht="15.75" customHeight="1">
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
-      <c r="D440" s="10"/>
+      <c r="D440" s="9"/>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
       <c r="G440" s="3"/>
@@ -13773,7 +13789,7 @@
     <row r="441" ht="15.75" customHeight="1">
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
-      <c r="D441" s="10"/>
+      <c r="D441" s="9"/>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
       <c r="G441" s="3"/>
@@ -13800,7 +13816,7 @@
     <row r="442" ht="15.75" customHeight="1">
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
-      <c r="D442" s="10"/>
+      <c r="D442" s="9"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
       <c r="G442" s="3"/>
@@ -13827,7 +13843,7 @@
     <row r="443" ht="15.75" customHeight="1">
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
-      <c r="D443" s="10"/>
+      <c r="D443" s="9"/>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
       <c r="G443" s="3"/>
@@ -13854,7 +13870,7 @@
     <row r="444" ht="15.75" customHeight="1">
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
-      <c r="D444" s="10"/>
+      <c r="D444" s="9"/>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
       <c r="G444" s="3"/>
@@ -13881,7 +13897,7 @@
     <row r="445" ht="15.75" customHeight="1">
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
-      <c r="D445" s="10"/>
+      <c r="D445" s="9"/>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
       <c r="G445" s="3"/>
@@ -13908,7 +13924,7 @@
     <row r="446" ht="15.75" customHeight="1">
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
-      <c r="D446" s="10"/>
+      <c r="D446" s="9"/>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
       <c r="G446" s="3"/>
@@ -13935,7 +13951,7 @@
     <row r="447" ht="15.75" customHeight="1">
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
-      <c r="D447" s="10"/>
+      <c r="D447" s="9"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
       <c r="G447" s="3"/>
@@ -13962,7 +13978,7 @@
     <row r="448" ht="15.75" customHeight="1">
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
-      <c r="D448" s="10"/>
+      <c r="D448" s="9"/>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3"/>
@@ -13989,7 +14005,7 @@
     <row r="449" ht="15.75" customHeight="1">
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
-      <c r="D449" s="10"/>
+      <c r="D449" s="9"/>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
       <c r="G449" s="3"/>
@@ -14016,7 +14032,7 @@
     <row r="450" ht="15.75" customHeight="1">
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
-      <c r="D450" s="10"/>
+      <c r="D450" s="9"/>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
       <c r="G450" s="3"/>
@@ -14043,7 +14059,7 @@
     <row r="451" ht="15.75" customHeight="1">
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
-      <c r="D451" s="10"/>
+      <c r="D451" s="9"/>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
       <c r="G451" s="3"/>
@@ -14070,7 +14086,7 @@
     <row r="452" ht="15.75" customHeight="1">
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
-      <c r="D452" s="10"/>
+      <c r="D452" s="9"/>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
       <c r="G452" s="3"/>
@@ -14097,7 +14113,7 @@
     <row r="453" ht="15.75" customHeight="1">
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
-      <c r="D453" s="10"/>
+      <c r="D453" s="9"/>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
       <c r="G453" s="3"/>
@@ -14124,7 +14140,7 @@
     <row r="454" ht="15.75" customHeight="1">
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
-      <c r="D454" s="10"/>
+      <c r="D454" s="9"/>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
       <c r="G454" s="3"/>
@@ -14151,7 +14167,7 @@
     <row r="455" ht="15.75" customHeight="1">
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
-      <c r="D455" s="10"/>
+      <c r="D455" s="9"/>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
       <c r="G455" s="3"/>
@@ -14178,7 +14194,7 @@
     <row r="456" ht="15.75" customHeight="1">
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
-      <c r="D456" s="10"/>
+      <c r="D456" s="9"/>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
       <c r="G456" s="3"/>
@@ -14205,7 +14221,7 @@
     <row r="457" ht="15.75" customHeight="1">
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
-      <c r="D457" s="10"/>
+      <c r="D457" s="9"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
       <c r="G457" s="3"/>
@@ -14232,7 +14248,7 @@
     <row r="458" ht="15.75" customHeight="1">
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
-      <c r="D458" s="10"/>
+      <c r="D458" s="9"/>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
       <c r="G458" s="3"/>
@@ -14259,7 +14275,7 @@
     <row r="459" ht="15.75" customHeight="1">
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
-      <c r="D459" s="10"/>
+      <c r="D459" s="9"/>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
       <c r="G459" s="3"/>
@@ -14286,7 +14302,7 @@
     <row r="460" ht="15.75" customHeight="1">
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
-      <c r="D460" s="10"/>
+      <c r="D460" s="9"/>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
       <c r="G460" s="3"/>
@@ -14313,7 +14329,7 @@
     <row r="461" ht="15.75" customHeight="1">
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
-      <c r="D461" s="10"/>
+      <c r="D461" s="9"/>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
       <c r="G461" s="3"/>
@@ -14340,7 +14356,7 @@
     <row r="462" ht="15.75" customHeight="1">
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
-      <c r="D462" s="10"/>
+      <c r="D462" s="9"/>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
       <c r="G462" s="3"/>
@@ -14367,7 +14383,7 @@
     <row r="463" ht="15.75" customHeight="1">
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
-      <c r="D463" s="10"/>
+      <c r="D463" s="9"/>
       <c r="E463" s="3"/>
       <c r="F463" s="3"/>
       <c r="G463" s="3"/>
@@ -14394,7 +14410,7 @@
     <row r="464" ht="15.75" customHeight="1">
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
-      <c r="D464" s="10"/>
+      <c r="D464" s="9"/>
       <c r="E464" s="3"/>
       <c r="F464" s="3"/>
       <c r="G464" s="3"/>
@@ -14421,7 +14437,7 @@
     <row r="465" ht="15.75" customHeight="1">
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
-      <c r="D465" s="10"/>
+      <c r="D465" s="9"/>
       <c r="E465" s="3"/>
       <c r="F465" s="3"/>
       <c r="G465" s="3"/>
@@ -14448,7 +14464,7 @@
     <row r="466" ht="15.75" customHeight="1">
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
-      <c r="D466" s="10"/>
+      <c r="D466" s="9"/>
       <c r="E466" s="3"/>
       <c r="F466" s="3"/>
       <c r="G466" s="3"/>
@@ -14475,7 +14491,7 @@
     <row r="467" ht="15.75" customHeight="1">
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
-      <c r="D467" s="10"/>
+      <c r="D467" s="9"/>
       <c r="E467" s="3"/>
       <c r="F467" s="3"/>
       <c r="G467" s="3"/>
@@ -14502,7 +14518,7 @@
     <row r="468" ht="15.75" customHeight="1">
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
-      <c r="D468" s="10"/>
+      <c r="D468" s="9"/>
       <c r="E468" s="3"/>
       <c r="F468" s="3"/>
       <c r="G468" s="3"/>
@@ -14529,7 +14545,7 @@
     <row r="469" ht="15.75" customHeight="1">
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
-      <c r="D469" s="10"/>
+      <c r="D469" s="9"/>
       <c r="E469" s="3"/>
       <c r="F469" s="3"/>
       <c r="G469" s="3"/>
@@ -14556,7 +14572,7 @@
     <row r="470" ht="15.75" customHeight="1">
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
-      <c r="D470" s="10"/>
+      <c r="D470" s="9"/>
       <c r="E470" s="3"/>
       <c r="F470" s="3"/>
       <c r="G470" s="3"/>
@@ -14583,7 +14599,7 @@
     <row r="471" ht="15.75" customHeight="1">
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
-      <c r="D471" s="10"/>
+      <c r="D471" s="9"/>
       <c r="E471" s="3"/>
       <c r="F471" s="3"/>
       <c r="G471" s="3"/>
@@ -14610,7 +14626,7 @@
     <row r="472" ht="15.75" customHeight="1">
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
-      <c r="D472" s="10"/>
+      <c r="D472" s="9"/>
       <c r="E472" s="3"/>
       <c r="F472" s="3"/>
       <c r="G472" s="3"/>
@@ -14637,7 +14653,7 @@
     <row r="473" ht="15.75" customHeight="1">
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
-      <c r="D473" s="10"/>
+      <c r="D473" s="9"/>
       <c r="E473" s="3"/>
       <c r="F473" s="3"/>
       <c r="G473" s="3"/>
@@ -14664,7 +14680,7 @@
     <row r="474" ht="15.75" customHeight="1">
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
-      <c r="D474" s="10"/>
+      <c r="D474" s="9"/>
       <c r="E474" s="3"/>
       <c r="F474" s="3"/>
       <c r="G474" s="3"/>
@@ -14691,7 +14707,7 @@
     <row r="475" ht="15.75" customHeight="1">
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
-      <c r="D475" s="10"/>
+      <c r="D475" s="9"/>
       <c r="E475" s="3"/>
       <c r="F475" s="3"/>
       <c r="G475" s="3"/>
@@ -14718,7 +14734,7 @@
     <row r="476" ht="15.75" customHeight="1">
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
-      <c r="D476" s="10"/>
+      <c r="D476" s="9"/>
       <c r="E476" s="3"/>
       <c r="F476" s="3"/>
       <c r="G476" s="3"/>
@@ -14745,7 +14761,7 @@
     <row r="477" ht="15.75" customHeight="1">
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
-      <c r="D477" s="10"/>
+      <c r="D477" s="9"/>
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3"/>
@@ -14772,7 +14788,7 @@
     <row r="478" ht="15.75" customHeight="1">
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
-      <c r="D478" s="10"/>
+      <c r="D478" s="9"/>
       <c r="E478" s="3"/>
       <c r="F478" s="3"/>
       <c r="G478" s="3"/>
@@ -14799,7 +14815,7 @@
     <row r="479" ht="15.75" customHeight="1">
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
-      <c r="D479" s="10"/>
+      <c r="D479" s="9"/>
       <c r="E479" s="3"/>
       <c r="F479" s="3"/>
       <c r="G479" s="3"/>
@@ -14826,7 +14842,7 @@
     <row r="480" ht="15.75" customHeight="1">
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
-      <c r="D480" s="10"/>
+      <c r="D480" s="9"/>
       <c r="E480" s="3"/>
       <c r="F480" s="3"/>
       <c r="G480" s="3"/>
@@ -14853,7 +14869,7 @@
     <row r="481" ht="15.75" customHeight="1">
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
-      <c r="D481" s="10"/>
+      <c r="D481" s="9"/>
       <c r="E481" s="3"/>
       <c r="F481" s="3"/>
       <c r="G481" s="3"/>
@@ -14880,7 +14896,7 @@
     <row r="482" ht="15.75" customHeight="1">
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
-      <c r="D482" s="10"/>
+      <c r="D482" s="9"/>
       <c r="E482" s="3"/>
       <c r="F482" s="3"/>
       <c r="G482" s="3"/>
@@ -14907,7 +14923,7 @@
     <row r="483" ht="15.75" customHeight="1">
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
-      <c r="D483" s="10"/>
+      <c r="D483" s="9"/>
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
       <c r="G483" s="3"/>
@@ -14934,7 +14950,7 @@
     <row r="484" ht="15.75" customHeight="1">
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
-      <c r="D484" s="10"/>
+      <c r="D484" s="9"/>
       <c r="E484" s="3"/>
       <c r="F484" s="3"/>
       <c r="G484" s="3"/>
@@ -14961,7 +14977,7 @@
     <row r="485" ht="15.75" customHeight="1">
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
-      <c r="D485" s="10"/>
+      <c r="D485" s="9"/>
       <c r="E485" s="3"/>
       <c r="F485" s="3"/>
       <c r="G485" s="3"/>
@@ -14988,7 +15004,7 @@
     <row r="486" ht="15.75" customHeight="1">
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
-      <c r="D486" s="10"/>
+      <c r="D486" s="9"/>
       <c r="E486" s="3"/>
       <c r="F486" s="3"/>
       <c r="G486" s="3"/>
@@ -15015,7 +15031,7 @@
     <row r="487" ht="15.75" customHeight="1">
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
-      <c r="D487" s="10"/>
+      <c r="D487" s="9"/>
       <c r="E487" s="3"/>
       <c r="F487" s="3"/>
       <c r="G487" s="3"/>
@@ -15042,7 +15058,7 @@
     <row r="488" ht="15.75" customHeight="1">
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
-      <c r="D488" s="10"/>
+      <c r="D488" s="9"/>
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
       <c r="G488" s="3"/>
@@ -15069,7 +15085,7 @@
     <row r="489" ht="15.75" customHeight="1">
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
-      <c r="D489" s="10"/>
+      <c r="D489" s="9"/>
       <c r="E489" s="3"/>
       <c r="F489" s="3"/>
       <c r="G489" s="3"/>
@@ -15096,7 +15112,7 @@
     <row r="490" ht="15.75" customHeight="1">
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
-      <c r="D490" s="10"/>
+      <c r="D490" s="9"/>
       <c r="E490" s="3"/>
       <c r="F490" s="3"/>
       <c r="G490" s="3"/>
@@ -15123,7 +15139,7 @@
     <row r="491" ht="15.75" customHeight="1">
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
-      <c r="D491" s="10"/>
+      <c r="D491" s="9"/>
       <c r="E491" s="3"/>
       <c r="F491" s="3"/>
       <c r="G491" s="3"/>
@@ -15150,7 +15166,7 @@
     <row r="492" ht="15.75" customHeight="1">
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
-      <c r="D492" s="10"/>
+      <c r="D492" s="9"/>
       <c r="E492" s="3"/>
       <c r="F492" s="3"/>
       <c r="G492" s="3"/>
@@ -15177,7 +15193,7 @@
     <row r="493" ht="15.75" customHeight="1">
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
-      <c r="D493" s="10"/>
+      <c r="D493" s="9"/>
       <c r="E493" s="3"/>
       <c r="F493" s="3"/>
       <c r="G493" s="3"/>
@@ -15204,7 +15220,7 @@
     <row r="494" ht="15.75" customHeight="1">
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
-      <c r="D494" s="10"/>
+      <c r="D494" s="9"/>
       <c r="E494" s="3"/>
       <c r="F494" s="3"/>
       <c r="G494" s="3"/>
@@ -15231,7 +15247,7 @@
     <row r="495" ht="15.75" customHeight="1">
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
-      <c r="D495" s="10"/>
+      <c r="D495" s="9"/>
       <c r="E495" s="3"/>
       <c r="F495" s="3"/>
       <c r="G495" s="3"/>
@@ -15258,7 +15274,7 @@
     <row r="496" ht="15.75" customHeight="1">
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
-      <c r="D496" s="10"/>
+      <c r="D496" s="9"/>
       <c r="E496" s="3"/>
       <c r="F496" s="3"/>
       <c r="G496" s="3"/>
@@ -15285,7 +15301,7 @@
     <row r="497" ht="15.75" customHeight="1">
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
-      <c r="D497" s="10"/>
+      <c r="D497" s="9"/>
       <c r="E497" s="3"/>
       <c r="F497" s="3"/>
       <c r="G497" s="3"/>
@@ -15312,7 +15328,7 @@
     <row r="498" ht="15.75" customHeight="1">
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
-      <c r="D498" s="10"/>
+      <c r="D498" s="9"/>
       <c r="E498" s="3"/>
       <c r="F498" s="3"/>
       <c r="G498" s="3"/>
@@ -15339,7 +15355,7 @@
     <row r="499" ht="15.75" customHeight="1">
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
-      <c r="D499" s="10"/>
+      <c r="D499" s="9"/>
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
       <c r="G499" s="3"/>
@@ -15366,7 +15382,7 @@
     <row r="500" ht="15.75" customHeight="1">
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
-      <c r="D500" s="10"/>
+      <c r="D500" s="9"/>
       <c r="E500" s="3"/>
       <c r="F500" s="3"/>
       <c r="G500" s="3"/>
@@ -15393,7 +15409,7 @@
     <row r="501" ht="15.75" customHeight="1">
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
-      <c r="D501" s="10"/>
+      <c r="D501" s="9"/>
       <c r="E501" s="3"/>
       <c r="F501" s="3"/>
       <c r="G501" s="3"/>
@@ -15420,7 +15436,7 @@
     <row r="502" ht="15.75" customHeight="1">
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
-      <c r="D502" s="10"/>
+      <c r="D502" s="9"/>
       <c r="E502" s="3"/>
       <c r="F502" s="3"/>
       <c r="G502" s="3"/>
@@ -15447,7 +15463,7 @@
     <row r="503" ht="15.75" customHeight="1">
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
-      <c r="D503" s="10"/>
+      <c r="D503" s="9"/>
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
       <c r="G503" s="3"/>
@@ -15474,7 +15490,7 @@
     <row r="504" ht="15.75" customHeight="1">
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
-      <c r="D504" s="10"/>
+      <c r="D504" s="9"/>
       <c r="E504" s="3"/>
       <c r="F504" s="3"/>
       <c r="G504" s="3"/>
@@ -15501,7 +15517,7 @@
     <row r="505" ht="15.75" customHeight="1">
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
-      <c r="D505" s="10"/>
+      <c r="D505" s="9"/>
       <c r="E505" s="3"/>
       <c r="F505" s="3"/>
       <c r="G505" s="3"/>
@@ -15528,7 +15544,7 @@
     <row r="506" ht="15.75" customHeight="1">
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
-      <c r="D506" s="10"/>
+      <c r="D506" s="9"/>
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3"/>
@@ -15555,7 +15571,7 @@
     <row r="507" ht="15.75" customHeight="1">
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
-      <c r="D507" s="10"/>
+      <c r="D507" s="9"/>
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
       <c r="G507" s="3"/>
@@ -15582,7 +15598,7 @@
     <row r="508" ht="15.75" customHeight="1">
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
-      <c r="D508" s="10"/>
+      <c r="D508" s="9"/>
       <c r="E508" s="3"/>
       <c r="F508" s="3"/>
       <c r="G508" s="3"/>
@@ -15609,7 +15625,7 @@
     <row r="509" ht="15.75" customHeight="1">
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
-      <c r="D509" s="10"/>
+      <c r="D509" s="9"/>
       <c r="E509" s="3"/>
       <c r="F509" s="3"/>
       <c r="G509" s="3"/>
@@ -15636,7 +15652,7 @@
     <row r="510" ht="15.75" customHeight="1">
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
-      <c r="D510" s="10"/>
+      <c r="D510" s="9"/>
       <c r="E510" s="3"/>
       <c r="F510" s="3"/>
       <c r="G510" s="3"/>
@@ -15663,7 +15679,7 @@
     <row r="511" ht="15.75" customHeight="1">
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
-      <c r="D511" s="10"/>
+      <c r="D511" s="9"/>
       <c r="E511" s="3"/>
       <c r="F511" s="3"/>
       <c r="G511" s="3"/>
@@ -15690,7 +15706,7 @@
     <row r="512" ht="15.75" customHeight="1">
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
-      <c r="D512" s="10"/>
+      <c r="D512" s="9"/>
       <c r="E512" s="3"/>
       <c r="F512" s="3"/>
       <c r="G512" s="3"/>
@@ -15717,7 +15733,7 @@
     <row r="513" ht="15.75" customHeight="1">
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
-      <c r="D513" s="10"/>
+      <c r="D513" s="9"/>
       <c r="E513" s="3"/>
       <c r="F513" s="3"/>
       <c r="G513" s="3"/>
@@ -15744,7 +15760,7 @@
     <row r="514" ht="15.75" customHeight="1">
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
-      <c r="D514" s="10"/>
+      <c r="D514" s="9"/>
       <c r="E514" s="3"/>
       <c r="F514" s="3"/>
       <c r="G514" s="3"/>
@@ -15771,7 +15787,7 @@
     <row r="515" ht="15.75" customHeight="1">
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
-      <c r="D515" s="10"/>
+      <c r="D515" s="9"/>
       <c r="E515" s="3"/>
       <c r="F515" s="3"/>
       <c r="G515" s="3"/>
@@ -15798,7 +15814,7 @@
     <row r="516" ht="15.75" customHeight="1">
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
-      <c r="D516" s="10"/>
+      <c r="D516" s="9"/>
       <c r="E516" s="3"/>
       <c r="F516" s="3"/>
       <c r="G516" s="3"/>
@@ -15825,7 +15841,7 @@
     <row r="517" ht="15.75" customHeight="1">
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
-      <c r="D517" s="10"/>
+      <c r="D517" s="9"/>
       <c r="E517" s="3"/>
       <c r="F517" s="3"/>
       <c r="G517" s="3"/>
@@ -15852,7 +15868,7 @@
     <row r="518" ht="15.75" customHeight="1">
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
-      <c r="D518" s="10"/>
+      <c r="D518" s="9"/>
       <c r="E518" s="3"/>
       <c r="F518" s="3"/>
       <c r="G518" s="3"/>
@@ -15879,7 +15895,7 @@
     <row r="519" ht="15.75" customHeight="1">
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
-      <c r="D519" s="10"/>
+      <c r="D519" s="9"/>
       <c r="E519" s="3"/>
       <c r="F519" s="3"/>
       <c r="G519" s="3"/>
@@ -15906,7 +15922,7 @@
     <row r="520" ht="15.75" customHeight="1">
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
-      <c r="D520" s="10"/>
+      <c r="D520" s="9"/>
       <c r="E520" s="3"/>
       <c r="F520" s="3"/>
       <c r="G520" s="3"/>
@@ -15933,7 +15949,7 @@
     <row r="521" ht="15.75" customHeight="1">
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
-      <c r="D521" s="10"/>
+      <c r="D521" s="9"/>
       <c r="E521" s="3"/>
       <c r="F521" s="3"/>
       <c r="G521" s="3"/>
@@ -15960,7 +15976,7 @@
     <row r="522" ht="15.75" customHeight="1">
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
-      <c r="D522" s="10"/>
+      <c r="D522" s="9"/>
       <c r="E522" s="3"/>
       <c r="F522" s="3"/>
       <c r="G522" s="3"/>
@@ -15987,7 +16003,7 @@
     <row r="523" ht="15.75" customHeight="1">
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
-      <c r="D523" s="10"/>
+      <c r="D523" s="9"/>
       <c r="E523" s="3"/>
       <c r="F523" s="3"/>
       <c r="G523" s="3"/>
@@ -16014,7 +16030,7 @@
     <row r="524" ht="15.75" customHeight="1">
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
-      <c r="D524" s="10"/>
+      <c r="D524" s="9"/>
       <c r="E524" s="3"/>
       <c r="F524" s="3"/>
       <c r="G524" s="3"/>
@@ -16041,7 +16057,7 @@
     <row r="525" ht="15.75" customHeight="1">
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
-      <c r="D525" s="10"/>
+      <c r="D525" s="9"/>
       <c r="E525" s="3"/>
       <c r="F525" s="3"/>
       <c r="G525" s="3"/>
@@ -16068,7 +16084,7 @@
     <row r="526" ht="15.75" customHeight="1">
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
-      <c r="D526" s="10"/>
+      <c r="D526" s="9"/>
       <c r="E526" s="3"/>
       <c r="F526" s="3"/>
       <c r="G526" s="3"/>
@@ -16095,7 +16111,7 @@
     <row r="527" ht="15.75" customHeight="1">
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
-      <c r="D527" s="10"/>
+      <c r="D527" s="9"/>
       <c r="E527" s="3"/>
       <c r="F527" s="3"/>
       <c r="G527" s="3"/>
@@ -16122,7 +16138,7 @@
     <row r="528" ht="15.75" customHeight="1">
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
-      <c r="D528" s="10"/>
+      <c r="D528" s="9"/>
       <c r="E528" s="3"/>
       <c r="F528" s="3"/>
       <c r="G528" s="3"/>
@@ -16149,7 +16165,7 @@
     <row r="529" ht="15.75" customHeight="1">
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
-      <c r="D529" s="10"/>
+      <c r="D529" s="9"/>
       <c r="E529" s="3"/>
       <c r="F529" s="3"/>
       <c r="G529" s="3"/>
@@ -16176,7 +16192,7 @@
     <row r="530" ht="15.75" customHeight="1">
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
-      <c r="D530" s="10"/>
+      <c r="D530" s="9"/>
       <c r="E530" s="3"/>
       <c r="F530" s="3"/>
       <c r="G530" s="3"/>
@@ -16203,7 +16219,7 @@
     <row r="531" ht="15.75" customHeight="1">
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
-      <c r="D531" s="10"/>
+      <c r="D531" s="9"/>
       <c r="E531" s="3"/>
       <c r="F531" s="3"/>
       <c r="G531" s="3"/>
@@ -16230,7 +16246,7 @@
     <row r="532" ht="15.75" customHeight="1">
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
-      <c r="D532" s="10"/>
+      <c r="D532" s="9"/>
       <c r="E532" s="3"/>
       <c r="F532" s="3"/>
       <c r="G532" s="3"/>
@@ -16257,7 +16273,7 @@
     <row r="533" ht="15.75" customHeight="1">
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
-      <c r="D533" s="10"/>
+      <c r="D533" s="9"/>
       <c r="E533" s="3"/>
       <c r="F533" s="3"/>
       <c r="G533" s="3"/>
@@ -16284,7 +16300,7 @@
     <row r="534" ht="15.75" customHeight="1">
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
-      <c r="D534" s="10"/>
+      <c r="D534" s="9"/>
       <c r="E534" s="3"/>
       <c r="F534" s="3"/>
       <c r="G534" s="3"/>
@@ -16311,7 +16327,7 @@
     <row r="535" ht="15.75" customHeight="1">
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
-      <c r="D535" s="10"/>
+      <c r="D535" s="9"/>
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3"/>
@@ -16338,7 +16354,7 @@
     <row r="536" ht="15.75" customHeight="1">
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
-      <c r="D536" s="10"/>
+      <c r="D536" s="9"/>
       <c r="E536" s="3"/>
       <c r="F536" s="3"/>
       <c r="G536" s="3"/>
@@ -16365,7 +16381,7 @@
     <row r="537" ht="15.75" customHeight="1">
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
-      <c r="D537" s="10"/>
+      <c r="D537" s="9"/>
       <c r="E537" s="3"/>
       <c r="F537" s="3"/>
       <c r="G537" s="3"/>
@@ -16392,7 +16408,7 @@
     <row r="538" ht="15.75" customHeight="1">
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
-      <c r="D538" s="10"/>
+      <c r="D538" s="9"/>
       <c r="E538" s="3"/>
       <c r="F538" s="3"/>
       <c r="G538" s="3"/>
@@ -16419,7 +16435,7 @@
     <row r="539" ht="15.75" customHeight="1">
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
-      <c r="D539" s="10"/>
+      <c r="D539" s="9"/>
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
       <c r="G539" s="3"/>
@@ -16446,7 +16462,7 @@
     <row r="540" ht="15.75" customHeight="1">
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
-      <c r="D540" s="10"/>
+      <c r="D540" s="9"/>
       <c r="E540" s="3"/>
       <c r="F540" s="3"/>
       <c r="G540" s="3"/>
@@ -16473,7 +16489,7 @@
     <row r="541" ht="15.75" customHeight="1">
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
-      <c r="D541" s="10"/>
+      <c r="D541" s="9"/>
       <c r="E541" s="3"/>
       <c r="F541" s="3"/>
       <c r="G541" s="3"/>
@@ -16500,7 +16516,7 @@
     <row r="542" ht="15.75" customHeight="1">
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
-      <c r="D542" s="10"/>
+      <c r="D542" s="9"/>
       <c r="E542" s="3"/>
       <c r="F542" s="3"/>
       <c r="G542" s="3"/>
@@ -16527,7 +16543,7 @@
     <row r="543" ht="15.75" customHeight="1">
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
-      <c r="D543" s="10"/>
+      <c r="D543" s="9"/>
       <c r="E543" s="3"/>
       <c r="F543" s="3"/>
       <c r="G543" s="3"/>
@@ -16554,7 +16570,7 @@
     <row r="544" ht="15.75" customHeight="1">
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
-      <c r="D544" s="10"/>
+      <c r="D544" s="9"/>
       <c r="E544" s="3"/>
       <c r="F544" s="3"/>
       <c r="G544" s="3"/>
@@ -16581,7 +16597,7 @@
     <row r="545" ht="15.75" customHeight="1">
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
-      <c r="D545" s="10"/>
+      <c r="D545" s="9"/>
       <c r="E545" s="3"/>
       <c r="F545" s="3"/>
       <c r="G545" s="3"/>
@@ -16608,7 +16624,7 @@
     <row r="546" ht="15.75" customHeight="1">
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
-      <c r="D546" s="10"/>
+      <c r="D546" s="9"/>
       <c r="E546" s="3"/>
       <c r="F546" s="3"/>
       <c r="G546" s="3"/>
@@ -16635,7 +16651,7 @@
     <row r="547" ht="15.75" customHeight="1">
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
-      <c r="D547" s="10"/>
+      <c r="D547" s="9"/>
       <c r="E547" s="3"/>
       <c r="F547" s="3"/>
       <c r="G547" s="3"/>
@@ -16662,7 +16678,7 @@
     <row r="548" ht="15.75" customHeight="1">
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
-      <c r="D548" s="10"/>
+      <c r="D548" s="9"/>
       <c r="E548" s="3"/>
       <c r="F548" s="3"/>
       <c r="G548" s="3"/>
@@ -16689,7 +16705,7 @@
     <row r="549" ht="15.75" customHeight="1">
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
-      <c r="D549" s="10"/>
+      <c r="D549" s="9"/>
       <c r="E549" s="3"/>
       <c r="F549" s="3"/>
       <c r="G549" s="3"/>
@@ -16716,7 +16732,7 @@
     <row r="550" ht="15.75" customHeight="1">
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
-      <c r="D550" s="10"/>
+      <c r="D550" s="9"/>
       <c r="E550" s="3"/>
       <c r="F550" s="3"/>
       <c r="G550" s="3"/>
@@ -16743,7 +16759,7 @@
     <row r="551" ht="15.75" customHeight="1">
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
-      <c r="D551" s="10"/>
+      <c r="D551" s="9"/>
       <c r="E551" s="3"/>
       <c r="F551" s="3"/>
       <c r="G551" s="3"/>
@@ -16770,7 +16786,7 @@
     <row r="552" ht="15.75" customHeight="1">
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
-      <c r="D552" s="10"/>
+      <c r="D552" s="9"/>
       <c r="E552" s="3"/>
       <c r="F552" s="3"/>
       <c r="G552" s="3"/>
@@ -16797,7 +16813,7 @@
     <row r="553" ht="15.75" customHeight="1">
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
-      <c r="D553" s="10"/>
+      <c r="D553" s="9"/>
       <c r="E553" s="3"/>
       <c r="F553" s="3"/>
       <c r="G553" s="3"/>
@@ -16824,7 +16840,7 @@
     <row r="554" ht="15.75" customHeight="1">
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
-      <c r="D554" s="10"/>
+      <c r="D554" s="9"/>
       <c r="E554" s="3"/>
       <c r="F554" s="3"/>
       <c r="G554" s="3"/>
@@ -16851,7 +16867,7 @@
     <row r="555" ht="15.75" customHeight="1">
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
-      <c r="D555" s="10"/>
+      <c r="D555" s="9"/>
       <c r="E555" s="3"/>
       <c r="F555" s="3"/>
       <c r="G555" s="3"/>
@@ -16878,7 +16894,7 @@
     <row r="556" ht="15.75" customHeight="1">
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
-      <c r="D556" s="10"/>
+      <c r="D556" s="9"/>
       <c r="E556" s="3"/>
       <c r="F556" s="3"/>
       <c r="G556" s="3"/>
@@ -16905,7 +16921,7 @@
     <row r="557" ht="15.75" customHeight="1">
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
-      <c r="D557" s="10"/>
+      <c r="D557" s="9"/>
       <c r="E557" s="3"/>
       <c r="F557" s="3"/>
       <c r="G557" s="3"/>
@@ -16932,7 +16948,7 @@
     <row r="558" ht="15.75" customHeight="1">
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
-      <c r="D558" s="10"/>
+      <c r="D558" s="9"/>
       <c r="E558" s="3"/>
       <c r="F558" s="3"/>
       <c r="G558" s="3"/>
@@ -16959,7 +16975,7 @@
     <row r="559" ht="15.75" customHeight="1">
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
-      <c r="D559" s="10"/>
+      <c r="D559" s="9"/>
       <c r="E559" s="3"/>
       <c r="F559" s="3"/>
       <c r="G559" s="3"/>
@@ -16986,7 +17002,7 @@
     <row r="560" ht="15.75" customHeight="1">
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
-      <c r="D560" s="10"/>
+      <c r="D560" s="9"/>
       <c r="E560" s="3"/>
       <c r="F560" s="3"/>
       <c r="G560" s="3"/>
@@ -17013,7 +17029,7 @@
     <row r="561" ht="15.75" customHeight="1">
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
-      <c r="D561" s="10"/>
+      <c r="D561" s="9"/>
       <c r="E561" s="3"/>
       <c r="F561" s="3"/>
       <c r="G561" s="3"/>
@@ -17040,7 +17056,7 @@
     <row r="562" ht="15.75" customHeight="1">
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
-      <c r="D562" s="10"/>
+      <c r="D562" s="9"/>
       <c r="E562" s="3"/>
       <c r="F562" s="3"/>
       <c r="G562" s="3"/>
@@ -17067,7 +17083,7 @@
     <row r="563" ht="15.75" customHeight="1">
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
-      <c r="D563" s="10"/>
+      <c r="D563" s="9"/>
       <c r="E563" s="3"/>
       <c r="F563" s="3"/>
       <c r="G563" s="3"/>
@@ -17094,7 +17110,7 @@
     <row r="564" ht="15.75" customHeight="1">
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
-      <c r="D564" s="10"/>
+      <c r="D564" s="9"/>
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3"/>
@@ -17121,7 +17137,7 @@
     <row r="565" ht="15.75" customHeight="1">
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
-      <c r="D565" s="10"/>
+      <c r="D565" s="9"/>
       <c r="E565" s="3"/>
       <c r="F565" s="3"/>
       <c r="G565" s="3"/>
@@ -17148,7 +17164,7 @@
     <row r="566" ht="15.75" customHeight="1">
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
-      <c r="D566" s="10"/>
+      <c r="D566" s="9"/>
       <c r="E566" s="3"/>
       <c r="F566" s="3"/>
       <c r="G566" s="3"/>
@@ -17175,7 +17191,7 @@
     <row r="567" ht="15.75" customHeight="1">
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
-      <c r="D567" s="10"/>
+      <c r="D567" s="9"/>
       <c r="E567" s="3"/>
       <c r="F567" s="3"/>
       <c r="G567" s="3"/>
@@ -17202,7 +17218,7 @@
     <row r="568" ht="15.75" customHeight="1">
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
-      <c r="D568" s="10"/>
+      <c r="D568" s="9"/>
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
       <c r="G568" s="3"/>
@@ -17229,7 +17245,7 @@
     <row r="569" ht="15.75" customHeight="1">
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
-      <c r="D569" s="10"/>
+      <c r="D569" s="9"/>
       <c r="E569" s="3"/>
       <c r="F569" s="3"/>
       <c r="G569" s="3"/>
@@ -17256,7 +17272,7 @@
     <row r="570" ht="15.75" customHeight="1">
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
-      <c r="D570" s="10"/>
+      <c r="D570" s="9"/>
       <c r="E570" s="3"/>
       <c r="F570" s="3"/>
       <c r="G570" s="3"/>
@@ -17283,7 +17299,7 @@
     <row r="571" ht="15.75" customHeight="1">
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
-      <c r="D571" s="10"/>
+      <c r="D571" s="9"/>
       <c r="E571" s="3"/>
       <c r="F571" s="3"/>
       <c r="G571" s="3"/>
@@ -17310,7 +17326,7 @@
     <row r="572" ht="15.75" customHeight="1">
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
-      <c r="D572" s="10"/>
+      <c r="D572" s="9"/>
       <c r="E572" s="3"/>
       <c r="F572" s="3"/>
       <c r="G572" s="3"/>
@@ -17337,7 +17353,7 @@
     <row r="573" ht="15.75" customHeight="1">
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
-      <c r="D573" s="10"/>
+      <c r="D573" s="9"/>
       <c r="E573" s="3"/>
       <c r="F573" s="3"/>
       <c r="G573" s="3"/>
@@ -17364,7 +17380,7 @@
     <row r="574" ht="15.75" customHeight="1">
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
-      <c r="D574" s="10"/>
+      <c r="D574" s="9"/>
       <c r="E574" s="3"/>
       <c r="F574" s="3"/>
       <c r="G574" s="3"/>
@@ -17391,7 +17407,7 @@
     <row r="575" ht="15.75" customHeight="1">
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
-      <c r="D575" s="10"/>
+      <c r="D575" s="9"/>
       <c r="E575" s="3"/>
       <c r="F575" s="3"/>
       <c r="G575" s="3"/>
@@ -17418,7 +17434,7 @@
     <row r="576" ht="15.75" customHeight="1">
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
-      <c r="D576" s="10"/>
+      <c r="D576" s="9"/>
       <c r="E576" s="3"/>
       <c r="F576" s="3"/>
       <c r="G576" s="3"/>
@@ -17445,7 +17461,7 @@
     <row r="577" ht="15.75" customHeight="1">
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
-      <c r="D577" s="10"/>
+      <c r="D577" s="9"/>
       <c r="E577" s="3"/>
       <c r="F577" s="3"/>
       <c r="G577" s="3"/>
@@ -17472,7 +17488,7 @@
     <row r="578" ht="15.75" customHeight="1">
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
-      <c r="D578" s="10"/>
+      <c r="D578" s="9"/>
       <c r="E578" s="3"/>
       <c r="F578" s="3"/>
       <c r="G578" s="3"/>
@@ -17499,7 +17515,7 @@
     <row r="579" ht="15.75" customHeight="1">
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
-      <c r="D579" s="10"/>
+      <c r="D579" s="9"/>
       <c r="E579" s="3"/>
       <c r="F579" s="3"/>
       <c r="G579" s="3"/>
@@ -17526,7 +17542,7 @@
     <row r="580" ht="15.75" customHeight="1">
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
-      <c r="D580" s="10"/>
+      <c r="D580" s="9"/>
       <c r="E580" s="3"/>
       <c r="F580" s="3"/>
       <c r="G580" s="3"/>
@@ -17553,7 +17569,7 @@
     <row r="581" ht="15.75" customHeight="1">
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
-      <c r="D581" s="10"/>
+      <c r="D581" s="9"/>
       <c r="E581" s="3"/>
       <c r="F581" s="3"/>
       <c r="G581" s="3"/>
@@ -17580,7 +17596,7 @@
     <row r="582" ht="15.75" customHeight="1">
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
-      <c r="D582" s="10"/>
+      <c r="D582" s="9"/>
       <c r="E582" s="3"/>
       <c r="F582" s="3"/>
       <c r="G582" s="3"/>
@@ -17607,7 +17623,7 @@
     <row r="583" ht="15.75" customHeight="1">
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
-      <c r="D583" s="10"/>
+      <c r="D583" s="9"/>
       <c r="E583" s="3"/>
       <c r="F583" s="3"/>
       <c r="G583" s="3"/>
@@ -17634,7 +17650,7 @@
     <row r="584" ht="15.75" customHeight="1">
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
-      <c r="D584" s="10"/>
+      <c r="D584" s="9"/>
       <c r="E584" s="3"/>
       <c r="F584" s="3"/>
       <c r="G584" s="3"/>
@@ -17661,7 +17677,7 @@
     <row r="585" ht="15.75" customHeight="1">
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
-      <c r="D585" s="10"/>
+      <c r="D585" s="9"/>
       <c r="E585" s="3"/>
       <c r="F585" s="3"/>
       <c r="G585" s="3"/>
@@ -17688,7 +17704,7 @@
     <row r="586" ht="15.75" customHeight="1">
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
-      <c r="D586" s="10"/>
+      <c r="D586" s="9"/>
       <c r="E586" s="3"/>
       <c r="F586" s="3"/>
       <c r="G586" s="3"/>
@@ -17715,7 +17731,7 @@
     <row r="587" ht="15.75" customHeight="1">
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
-      <c r="D587" s="10"/>
+      <c r="D587" s="9"/>
       <c r="E587" s="3"/>
       <c r="F587" s="3"/>
       <c r="G587" s="3"/>
@@ -17742,7 +17758,7 @@
     <row r="588" ht="15.75" customHeight="1">
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
-      <c r="D588" s="10"/>
+      <c r="D588" s="9"/>
       <c r="E588" s="3"/>
       <c r="F588" s="3"/>
       <c r="G588" s="3"/>
@@ -17769,7 +17785,7 @@
     <row r="589" ht="15.75" customHeight="1">
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
-      <c r="D589" s="10"/>
+      <c r="D589" s="9"/>
       <c r="E589" s="3"/>
       <c r="F589" s="3"/>
       <c r="G589" s="3"/>
@@ -17796,7 +17812,7 @@
     <row r="590" ht="15.75" customHeight="1">
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
-      <c r="D590" s="10"/>
+      <c r="D590" s="9"/>
       <c r="E590" s="3"/>
       <c r="F590" s="3"/>
       <c r="G590" s="3"/>
@@ -17823,7 +17839,7 @@
     <row r="591" ht="15.75" customHeight="1">
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
-      <c r="D591" s="10"/>
+      <c r="D591" s="9"/>
       <c r="E591" s="3"/>
       <c r="F591" s="3"/>
       <c r="G591" s="3"/>
@@ -17850,7 +17866,7 @@
     <row r="592" ht="15.75" customHeight="1">
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
-      <c r="D592" s="10"/>
+      <c r="D592" s="9"/>
       <c r="E592" s="3"/>
       <c r="F592" s="3"/>
       <c r="G592" s="3"/>
@@ -17877,7 +17893,7 @@
     <row r="593" ht="15.75" customHeight="1">
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
-      <c r="D593" s="10"/>
+      <c r="D593" s="9"/>
       <c r="E593" s="3"/>
       <c r="F593" s="3"/>
       <c r="G593" s="3"/>
@@ -17904,7 +17920,7 @@
     <row r="594" ht="15.75" customHeight="1">
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
-      <c r="D594" s="10"/>
+      <c r="D594" s="9"/>
       <c r="E594" s="3"/>
       <c r="F594" s="3"/>
       <c r="G594" s="3"/>
@@ -17931,7 +17947,7 @@
     <row r="595" ht="15.75" customHeight="1">
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
-      <c r="D595" s="10"/>
+      <c r="D595" s="9"/>
       <c r="E595" s="3"/>
       <c r="F595" s="3"/>
       <c r="G595" s="3"/>
@@ -17958,7 +17974,7 @@
     <row r="596" ht="15.75" customHeight="1">
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
-      <c r="D596" s="10"/>
+      <c r="D596" s="9"/>
       <c r="E596" s="3"/>
       <c r="F596" s="3"/>
       <c r="G596" s="3"/>
@@ -17985,7 +18001,7 @@
     <row r="597" ht="15.75" customHeight="1">
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
-      <c r="D597" s="10"/>
+      <c r="D597" s="9"/>
       <c r="E597" s="3"/>
       <c r="F597" s="3"/>
       <c r="G597" s="3"/>
@@ -18012,7 +18028,7 @@
     <row r="598" ht="15.75" customHeight="1">
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
-      <c r="D598" s="10"/>
+      <c r="D598" s="9"/>
       <c r="E598" s="3"/>
       <c r="F598" s="3"/>
       <c r="G598" s="3"/>
@@ -18039,7 +18055,7 @@
     <row r="599" ht="15.75" customHeight="1">
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
-      <c r="D599" s="10"/>
+      <c r="D599" s="9"/>
       <c r="E599" s="3"/>
       <c r="F599" s="3"/>
       <c r="G599" s="3"/>
@@ -18066,7 +18082,7 @@
     <row r="600" ht="15.75" customHeight="1">
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
-      <c r="D600" s="10"/>
+      <c r="D600" s="9"/>
       <c r="E600" s="3"/>
       <c r="F600" s="3"/>
       <c r="G600" s="3"/>
@@ -18093,7 +18109,7 @@
     <row r="601" ht="15.75" customHeight="1">
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
-      <c r="D601" s="10"/>
+      <c r="D601" s="9"/>
       <c r="E601" s="3"/>
       <c r="F601" s="3"/>
       <c r="G601" s="3"/>
@@ -18120,7 +18136,7 @@
     <row r="602" ht="15.75" customHeight="1">
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
-      <c r="D602" s="10"/>
+      <c r="D602" s="9"/>
       <c r="E602" s="3"/>
       <c r="F602" s="3"/>
       <c r="G602" s="3"/>
@@ -18147,7 +18163,7 @@
     <row r="603" ht="15.75" customHeight="1">
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
-      <c r="D603" s="10"/>
+      <c r="D603" s="9"/>
       <c r="E603" s="3"/>
       <c r="F603" s="3"/>
       <c r="G603" s="3"/>
@@ -18174,7 +18190,7 @@
     <row r="604" ht="15.75" customHeight="1">
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
-      <c r="D604" s="10"/>
+      <c r="D604" s="9"/>
       <c r="E604" s="3"/>
       <c r="F604" s="3"/>
       <c r="G604" s="3"/>
@@ -18201,7 +18217,7 @@
     <row r="605" ht="15.75" customHeight="1">
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
-      <c r="D605" s="10"/>
+      <c r="D605" s="9"/>
       <c r="E605" s="3"/>
       <c r="F605" s="3"/>
       <c r="G605" s="3"/>
@@ -18228,7 +18244,7 @@
     <row r="606" ht="15.75" customHeight="1">
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
-      <c r="D606" s="10"/>
+      <c r="D606" s="9"/>
       <c r="E606" s="3"/>
       <c r="F606" s="3"/>
       <c r="G606" s="3"/>
@@ -18255,7 +18271,7 @@
     <row r="607" ht="15.75" customHeight="1">
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
-      <c r="D607" s="10"/>
+      <c r="D607" s="9"/>
       <c r="E607" s="3"/>
       <c r="F607" s="3"/>
       <c r="G607" s="3"/>
@@ -18282,7 +18298,7 @@
     <row r="608" ht="15.75" customHeight="1">
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
-      <c r="D608" s="10"/>
+      <c r="D608" s="9"/>
       <c r="E608" s="3"/>
       <c r="F608" s="3"/>
       <c r="G608" s="3"/>
@@ -18309,7 +18325,7 @@
     <row r="609" ht="15.75" customHeight="1">
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
-      <c r="D609" s="10"/>
+      <c r="D609" s="9"/>
       <c r="E609" s="3"/>
       <c r="F609" s="3"/>
       <c r="G609" s="3"/>
@@ -18336,7 +18352,7 @@
     <row r="610" ht="15.75" customHeight="1">
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
-      <c r="D610" s="10"/>
+      <c r="D610" s="9"/>
       <c r="E610" s="3"/>
       <c r="F610" s="3"/>
       <c r="G610" s="3"/>
@@ -18363,7 +18379,7 @@
     <row r="611" ht="15.75" customHeight="1">
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
-      <c r="D611" s="10"/>
+      <c r="D611" s="9"/>
       <c r="E611" s="3"/>
       <c r="F611" s="3"/>
       <c r="G611" s="3"/>
@@ -18390,7 +18406,7 @@
     <row r="612" ht="15.75" customHeight="1">
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
-      <c r="D612" s="10"/>
+      <c r="D612" s="9"/>
       <c r="E612" s="3"/>
       <c r="F612" s="3"/>
       <c r="G612" s="3"/>
@@ -18417,7 +18433,7 @@
     <row r="613" ht="15.75" customHeight="1">
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
-      <c r="D613" s="10"/>
+      <c r="D613" s="9"/>
       <c r="E613" s="3"/>
       <c r="F613" s="3"/>
       <c r="G613" s="3"/>
@@ -18444,7 +18460,7 @@
     <row r="614" ht="15.75" customHeight="1">
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
-      <c r="D614" s="10"/>
+      <c r="D614" s="9"/>
       <c r="E614" s="3"/>
       <c r="F614" s="3"/>
       <c r="G614" s="3"/>
@@ -18471,7 +18487,7 @@
     <row r="615" ht="15.75" customHeight="1">
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
-      <c r="D615" s="10"/>
+      <c r="D615" s="9"/>
       <c r="E615" s="3"/>
       <c r="F615" s="3"/>
       <c r="G615" s="3"/>
@@ -18498,7 +18514,7 @@
     <row r="616" ht="15.75" customHeight="1">
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
-      <c r="D616" s="10"/>
+      <c r="D616" s="9"/>
       <c r="E616" s="3"/>
       <c r="F616" s="3"/>
       <c r="G616" s="3"/>
@@ -18525,7 +18541,7 @@
     <row r="617" ht="15.75" customHeight="1">
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
-      <c r="D617" s="10"/>
+      <c r="D617" s="9"/>
       <c r="E617" s="3"/>
       <c r="F617" s="3"/>
       <c r="G617" s="3"/>
@@ -18552,7 +18568,7 @@
     <row r="618" ht="15.75" customHeight="1">
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
-      <c r="D618" s="10"/>
+      <c r="D618" s="9"/>
       <c r="E618" s="3"/>
       <c r="F618" s="3"/>
       <c r="G618" s="3"/>
@@ -18579,7 +18595,7 @@
     <row r="619" ht="15.75" customHeight="1">
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
-      <c r="D619" s="10"/>
+      <c r="D619" s="9"/>
       <c r="E619" s="3"/>
       <c r="F619" s="3"/>
       <c r="G619" s="3"/>
@@ -18606,7 +18622,7 @@
     <row r="620" ht="15.75" customHeight="1">
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
-      <c r="D620" s="10"/>
+      <c r="D620" s="9"/>
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
       <c r="G620" s="3"/>
@@ -18633,7 +18649,7 @@
     <row r="621" ht="15.75" customHeight="1">
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
-      <c r="D621" s="10"/>
+      <c r="D621" s="9"/>
       <c r="E621" s="3"/>
       <c r="F621" s="3"/>
       <c r="G621" s="3"/>
@@ -18660,7 +18676,7 @@
     <row r="622" ht="15.75" customHeight="1">
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
-      <c r="D622" s="10"/>
+      <c r="D622" s="9"/>
       <c r="E622" s="3"/>
       <c r="F622" s="3"/>
       <c r="G622" s="3"/>
@@ -18687,7 +18703,7 @@
     <row r="623" ht="15.75" customHeight="1">
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
-      <c r="D623" s="10"/>
+      <c r="D623" s="9"/>
       <c r="E623" s="3"/>
       <c r="F623" s="3"/>
       <c r="G623" s="3"/>
@@ -18714,7 +18730,7 @@
     <row r="624" ht="15.75" customHeight="1">
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
-      <c r="D624" s="10"/>
+      <c r="D624" s="9"/>
       <c r="E624" s="3"/>
       <c r="F624" s="3"/>
       <c r="G624" s="3"/>
@@ -18741,7 +18757,7 @@
     <row r="625" ht="15.75" customHeight="1">
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
-      <c r="D625" s="10"/>
+      <c r="D625" s="9"/>
       <c r="E625" s="3"/>
       <c r="F625" s="3"/>
       <c r="G625" s="3"/>
@@ -18768,7 +18784,7 @@
     <row r="626" ht="15.75" customHeight="1">
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
-      <c r="D626" s="10"/>
+      <c r="D626" s="9"/>
       <c r="E626" s="3"/>
       <c r="F626" s="3"/>
       <c r="G626" s="3"/>
@@ -18795,7 +18811,7 @@
     <row r="627" ht="15.75" customHeight="1">
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
-      <c r="D627" s="10"/>
+      <c r="D627" s="9"/>
       <c r="E627" s="3"/>
       <c r="F627" s="3"/>
       <c r="G627" s="3"/>
@@ -18822,7 +18838,7 @@
     <row r="628" ht="15.75" customHeight="1">
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
-      <c r="D628" s="10"/>
+      <c r="D628" s="9"/>
       <c r="E628" s="3"/>
       <c r="F628" s="3"/>
       <c r="G628" s="3"/>
@@ -18849,7 +18865,7 @@
     <row r="629" ht="15.75" customHeight="1">
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
-      <c r="D629" s="10"/>
+      <c r="D629" s="9"/>
       <c r="E629" s="3"/>
       <c r="F629" s="3"/>
       <c r="G629" s="3"/>
@@ -18876,7 +18892,7 @@
     <row r="630" ht="15.75" customHeight="1">
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
-      <c r="D630" s="10"/>
+      <c r="D630" s="9"/>
       <c r="E630" s="3"/>
       <c r="F630" s="3"/>
       <c r="G630" s="3"/>
@@ -18903,7 +18919,7 @@
     <row r="631" ht="15.75" customHeight="1">
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
-      <c r="D631" s="10"/>
+      <c r="D631" s="9"/>
       <c r="E631" s="3"/>
       <c r="F631" s="3"/>
       <c r="G631" s="3"/>
@@ -18930,7 +18946,7 @@
     <row r="632" ht="15.75" customHeight="1">
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
-      <c r="D632" s="10"/>
+      <c r="D632" s="9"/>
       <c r="E632" s="3"/>
       <c r="F632" s="3"/>
       <c r="G632" s="3"/>
@@ -18957,7 +18973,7 @@
     <row r="633" ht="15.75" customHeight="1">
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
-      <c r="D633" s="10"/>
+      <c r="D633" s="9"/>
       <c r="E633" s="3"/>
       <c r="F633" s="3"/>
       <c r="G633" s="3"/>
@@ -18984,7 +19000,7 @@
     <row r="634" ht="15.75" customHeight="1">
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
-      <c r="D634" s="10"/>
+      <c r="D634" s="9"/>
       <c r="E634" s="3"/>
       <c r="F634" s="3"/>
       <c r="G634" s="3"/>
@@ -19011,7 +19027,7 @@
     <row r="635" ht="15.75" customHeight="1">
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
-      <c r="D635" s="10"/>
+      <c r="D635" s="9"/>
       <c r="E635" s="3"/>
       <c r="F635" s="3"/>
       <c r="G635" s="3"/>
@@ -19038,7 +19054,7 @@
     <row r="636" ht="15.75" customHeight="1">
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
-      <c r="D636" s="10"/>
+      <c r="D636" s="9"/>
       <c r="E636" s="3"/>
       <c r="F636" s="3"/>
       <c r="G636" s="3"/>
@@ -19065,7 +19081,7 @@
     <row r="637" ht="15.75" customHeight="1">
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
-      <c r="D637" s="10"/>
+      <c r="D637" s="9"/>
       <c r="E637" s="3"/>
       <c r="F637" s="3"/>
       <c r="G637" s="3"/>
@@ -19092,7 +19108,7 @@
     <row r="638" ht="15.75" customHeight="1">
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
-      <c r="D638" s="10"/>
+      <c r="D638" s="9"/>
       <c r="E638" s="3"/>
       <c r="F638" s="3"/>
       <c r="G638" s="3"/>
@@ -19119,7 +19135,7 @@
     <row r="639" ht="15.75" customHeight="1">
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
-      <c r="D639" s="10"/>
+      <c r="D639" s="9"/>
       <c r="E639" s="3"/>
       <c r="F639" s="3"/>
       <c r="G639" s="3"/>
@@ -19146,7 +19162,7 @@
     <row r="640" ht="15.75" customHeight="1">
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
-      <c r="D640" s="10"/>
+      <c r="D640" s="9"/>
       <c r="E640" s="3"/>
       <c r="F640" s="3"/>
       <c r="G640" s="3"/>
@@ -19173,7 +19189,7 @@
     <row r="641" ht="15.75" customHeight="1">
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
-      <c r="D641" s="10"/>
+      <c r="D641" s="9"/>
       <c r="E641" s="3"/>
       <c r="F641" s="3"/>
       <c r="G641" s="3"/>
@@ -19200,7 +19216,7 @@
     <row r="642" ht="15.75" customHeight="1">
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
-      <c r="D642" s="10"/>
+      <c r="D642" s="9"/>
       <c r="E642" s="3"/>
       <c r="F642" s="3"/>
       <c r="G642" s="3"/>
@@ -19227,7 +19243,7 @@
     <row r="643" ht="15.75" customHeight="1">
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
-      <c r="D643" s="10"/>
+      <c r="D643" s="9"/>
       <c r="E643" s="3"/>
       <c r="F643" s="3"/>
       <c r="G643" s="3"/>
@@ -19254,7 +19270,7 @@
     <row r="644" ht="15.75" customHeight="1">
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
-      <c r="D644" s="10"/>
+      <c r="D644" s="9"/>
       <c r="E644" s="3"/>
       <c r="F644" s="3"/>
       <c r="G644" s="3"/>
@@ -19281,7 +19297,7 @@
     <row r="645" ht="15.75" customHeight="1">
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
-      <c r="D645" s="10"/>
+      <c r="D645" s="9"/>
       <c r="E645" s="3"/>
       <c r="F645" s="3"/>
       <c r="G645" s="3"/>
@@ -19308,7 +19324,7 @@
     <row r="646" ht="15.75" customHeight="1">
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
-      <c r="D646" s="10"/>
+      <c r="D646" s="9"/>
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
       <c r="G646" s="3"/>
@@ -19335,7 +19351,7 @@
     <row r="647" ht="15.75" customHeight="1">
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
-      <c r="D647" s="10"/>
+      <c r="D647" s="9"/>
       <c r="E647" s="3"/>
       <c r="F647" s="3"/>
       <c r="G647" s="3"/>
@@ -19362,7 +19378,7 @@
     <row r="648" ht="15.75" customHeight="1">
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
-      <c r="D648" s="10"/>
+      <c r="D648" s="9"/>
       <c r="E648" s="3"/>
       <c r="F648" s="3"/>
       <c r="G648" s="3"/>
@@ -19389,7 +19405,7 @@
     <row r="649" ht="15.75" customHeight="1">
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
-      <c r="D649" s="10"/>
+      <c r="D649" s="9"/>
       <c r="E649" s="3"/>
       <c r="F649" s="3"/>
       <c r="G649" s="3"/>
@@ -19416,7 +19432,7 @@
     <row r="650" ht="15.75" customHeight="1">
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
-      <c r="D650" s="10"/>
+      <c r="D650" s="9"/>
       <c r="E650" s="3"/>
       <c r="F650" s="3"/>
       <c r="G650" s="3"/>
@@ -19443,7 +19459,7 @@
     <row r="651" ht="15.75" customHeight="1">
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
-      <c r="D651" s="10"/>
+      <c r="D651" s="9"/>
       <c r="E651" s="3"/>
       <c r="F651" s="3"/>
       <c r="G651" s="3"/>
@@ -19470,7 +19486,7 @@
     <row r="652" ht="15.75" customHeight="1">
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
-      <c r="D652" s="10"/>
+      <c r="D652" s="9"/>
       <c r="E652" s="3"/>
       <c r="F652" s="3"/>
       <c r="G652" s="3"/>
@@ -19497,7 +19513,7 @@
     <row r="653" ht="15.75" customHeight="1">
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
-      <c r="D653" s="10"/>
+      <c r="D653" s="9"/>
       <c r="E653" s="3"/>
       <c r="F653" s="3"/>
       <c r="G653" s="3"/>
@@ -19524,7 +19540,7 @@
     <row r="654" ht="15.75" customHeight="1">
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
-      <c r="D654" s="10"/>
+      <c r="D654" s="9"/>
       <c r="E654" s="3"/>
       <c r="F654" s="3"/>
       <c r="G654" s="3"/>
@@ -19551,7 +19567,7 @@
     <row r="655" ht="15.75" customHeight="1">
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
-      <c r="D655" s="10"/>
+      <c r="D655" s="9"/>
       <c r="E655" s="3"/>
       <c r="F655" s="3"/>
       <c r="G655" s="3"/>
@@ -19578,7 +19594,7 @@
     <row r="656" ht="15.75" customHeight="1">
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
-      <c r="D656" s="10"/>
+      <c r="D656" s="9"/>
       <c r="E656" s="3"/>
       <c r="F656" s="3"/>
       <c r="G656" s="3"/>
@@ -19605,7 +19621,7 @@
     <row r="657" ht="15.75" customHeight="1">
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
-      <c r="D657" s="10"/>
+      <c r="D657" s="9"/>
       <c r="E657" s="3"/>
       <c r="F657" s="3"/>
       <c r="G657" s="3"/>
@@ -19632,7 +19648,7 @@
     <row r="658" ht="15.75" customHeight="1">
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
-      <c r="D658" s="10"/>
+      <c r="D658" s="9"/>
       <c r="E658" s="3"/>
       <c r="F658" s="3"/>
       <c r="G658" s="3"/>
@@ -19659,7 +19675,7 @@
     <row r="659" ht="15.75" customHeight="1">
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
-      <c r="D659" s="10"/>
+      <c r="D659" s="9"/>
       <c r="E659" s="3"/>
       <c r="F659" s="3"/>
       <c r="G659" s="3"/>
@@ -19686,7 +19702,7 @@
     <row r="660" ht="15.75" customHeight="1">
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
-      <c r="D660" s="10"/>
+      <c r="D660" s="9"/>
       <c r="E660" s="3"/>
       <c r="F660" s="3"/>
       <c r="G660" s="3"/>
@@ -19713,7 +19729,7 @@
     <row r="661" ht="15.75" customHeight="1">
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
-      <c r="D661" s="10"/>
+      <c r="D661" s="9"/>
       <c r="E661" s="3"/>
       <c r="F661" s="3"/>
       <c r="G661" s="3"/>
@@ -19740,7 +19756,7 @@
     <row r="662" ht="15.75" customHeight="1">
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
-      <c r="D662" s="10"/>
+      <c r="D662" s="9"/>
       <c r="E662" s="3"/>
       <c r="F662" s="3"/>
       <c r="G662" s="3"/>
@@ -19767,7 +19783,7 @@
     <row r="663" ht="15.75" customHeight="1">
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
-      <c r="D663" s="10"/>
+      <c r="D663" s="9"/>
       <c r="E663" s="3"/>
       <c r="F663" s="3"/>
       <c r="G663" s="3"/>
@@ -19794,7 +19810,7 @@
     <row r="664" ht="15.75" customHeight="1">
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
-      <c r="D664" s="10"/>
+      <c r="D664" s="9"/>
       <c r="E664" s="3"/>
       <c r="F664" s="3"/>
       <c r="G664" s="3"/>
@@ -19821,7 +19837,7 @@
     <row r="665" ht="15.75" customHeight="1">
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
-      <c r="D665" s="10"/>
+      <c r="D665" s="9"/>
       <c r="E665" s="3"/>
       <c r="F665" s="3"/>
       <c r="G665" s="3"/>
@@ -19848,7 +19864,7 @@
     <row r="666" ht="15.75" customHeight="1">
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
-      <c r="D666" s="10"/>
+      <c r="D666" s="9"/>
       <c r="E666" s="3"/>
       <c r="F666" s="3"/>
       <c r="G666" s="3"/>
@@ -19875,7 +19891,7 @@
     <row r="667" ht="15.75" customHeight="1">
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
-      <c r="D667" s="10"/>
+      <c r="D667" s="9"/>
       <c r="E667" s="3"/>
       <c r="F667" s="3"/>
       <c r="G667" s="3"/>
@@ -19902,7 +19918,7 @@
     <row r="668" ht="15.75" customHeight="1">
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
-      <c r="D668" s="10"/>
+      <c r="D668" s="9"/>
       <c r="E668" s="3"/>
       <c r="F668" s="3"/>
       <c r="G668" s="3"/>
@@ -19929,7 +19945,7 @@
     <row r="669" ht="15.75" customHeight="1">
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
-      <c r="D669" s="10"/>
+      <c r="D669" s="9"/>
       <c r="E669" s="3"/>
       <c r="F669" s="3"/>
       <c r="G669" s="3"/>
@@ -19956,7 +19972,7 @@
     <row r="670" ht="15.75" customHeight="1">
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
-      <c r="D670" s="10"/>
+      <c r="D670" s="9"/>
       <c r="E670" s="3"/>
       <c r="F670" s="3"/>
       <c r="G670" s="3"/>
@@ -19983,7 +19999,7 @@
     <row r="671" ht="15.75" customHeight="1">
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
-      <c r="D671" s="10"/>
+      <c r="D671" s="9"/>
       <c r="E671" s="3"/>
       <c r="F671" s="3"/>
       <c r="G671" s="3"/>
@@ -20010,7 +20026,7 @@
     <row r="672" ht="15.75" customHeight="1">
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
-      <c r="D672" s="10"/>
+      <c r="D672" s="9"/>
       <c r="E672" s="3"/>
       <c r="F672" s="3"/>
       <c r="G672" s="3"/>
@@ -20037,7 +20053,7 @@
     <row r="673" ht="15.75" customHeight="1">
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
-      <c r="D673" s="10"/>
+      <c r="D673" s="9"/>
       <c r="E673" s="3"/>
       <c r="F673" s="3"/>
       <c r="G673" s="3"/>
@@ -20064,7 +20080,7 @@
     <row r="674" ht="15.75" customHeight="1">
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
-      <c r="D674" s="10"/>
+      <c r="D674" s="9"/>
       <c r="E674" s="3"/>
       <c r="F674" s="3"/>
       <c r="G674" s="3"/>
@@ -20091,7 +20107,7 @@
     <row r="675" ht="15.75" customHeight="1">
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
-      <c r="D675" s="10"/>
+      <c r="D675" s="9"/>
       <c r="E675" s="3"/>
       <c r="F675" s="3"/>
       <c r="G675" s="3"/>
@@ -20118,7 +20134,7 @@
     <row r="676" ht="15.75" customHeight="1">
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
-      <c r="D676" s="10"/>
+      <c r="D676" s="9"/>
       <c r="E676" s="3"/>
       <c r="F676" s="3"/>
       <c r="G676" s="3"/>
@@ -20145,7 +20161,7 @@
     <row r="677" ht="15.75" customHeight="1">
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
-      <c r="D677" s="10"/>
+      <c r="D677" s="9"/>
       <c r="E677" s="3"/>
       <c r="F677" s="3"/>
       <c r="G677" s="3"/>
@@ -20172,7 +20188,7 @@
     <row r="678" ht="15.75" customHeight="1">
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
-      <c r="D678" s="10"/>
+      <c r="D678" s="9"/>
       <c r="E678" s="3"/>
       <c r="F678" s="3"/>
       <c r="G678" s="3"/>
@@ -20199,7 +20215,7 @@
     <row r="679" ht="15.75" customHeight="1">
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
-      <c r="D679" s="10"/>
+      <c r="D679" s="9"/>
       <c r="E679" s="3"/>
       <c r="F679" s="3"/>
       <c r="G679" s="3"/>
@@ -20226,7 +20242,7 @@
     <row r="680" ht="15.75" customHeight="1">
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
-      <c r="D680" s="10"/>
+      <c r="D680" s="9"/>
       <c r="E680" s="3"/>
       <c r="F680" s="3"/>
       <c r="G680" s="3"/>
@@ -20253,7 +20269,7 @@
     <row r="681" ht="15.75" customHeight="1">
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
-      <c r="D681" s="10"/>
+      <c r="D681" s="9"/>
       <c r="E681" s="3"/>
       <c r="F681" s="3"/>
       <c r="G681" s="3"/>
@@ -20280,7 +20296,7 @@
     <row r="682" ht="15.75" customHeight="1">
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
-      <c r="D682" s="10"/>
+      <c r="D682" s="9"/>
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
       <c r="G682" s="3"/>
@@ -20307,7 +20323,7 @@
     <row r="683" ht="15.75" customHeight="1">
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
-      <c r="D683" s="10"/>
+      <c r="D683" s="9"/>
       <c r="E683" s="3"/>
       <c r="F683" s="3"/>
       <c r="G683" s="3"/>
@@ -20334,7 +20350,7 @@
     <row r="684" ht="15.75" customHeight="1">
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
-      <c r="D684" s="10"/>
+      <c r="D684" s="9"/>
       <c r="E684" s="3"/>
       <c r="F684" s="3"/>
       <c r="G684" s="3"/>
@@ -20361,7 +20377,7 @@
     <row r="685" ht="15.75" customHeight="1">
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
-      <c r="D685" s="10"/>
+      <c r="D685" s="9"/>
       <c r="E685" s="3"/>
       <c r="F685" s="3"/>
       <c r="G685" s="3"/>
@@ -20388,7 +20404,7 @@
     <row r="686" ht="15.75" customHeight="1">
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
-      <c r="D686" s="10"/>
+      <c r="D686" s="9"/>
       <c r="E686" s="3"/>
       <c r="F686" s="3"/>
       <c r="G686" s="3"/>
@@ -20415,7 +20431,7 @@
     <row r="687" ht="15.75" customHeight="1">
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
-      <c r="D687" s="10"/>
+      <c r="D687" s="9"/>
       <c r="E687" s="3"/>
       <c r="F687" s="3"/>
       <c r="G687" s="3"/>
@@ -20442,7 +20458,7 @@
     <row r="688" ht="15.75" customHeight="1">
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
-      <c r="D688" s="10"/>
+      <c r="D688" s="9"/>
       <c r="E688" s="3"/>
       <c r="F688" s="3"/>
       <c r="G688" s="3"/>
@@ -20469,7 +20485,7 @@
     <row r="689" ht="15.75" customHeight="1">
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
-      <c r="D689" s="10"/>
+      <c r="D689" s="9"/>
       <c r="E689" s="3"/>
       <c r="F689" s="3"/>
       <c r="G689" s="3"/>
@@ -20496,7 +20512,7 @@
     <row r="690" ht="15.75" customHeight="1">
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
-      <c r="D690" s="10"/>
+      <c r="D690" s="9"/>
       <c r="E690" s="3"/>
       <c r="F690" s="3"/>
       <c r="G690" s="3"/>
@@ -20523,7 +20539,7 @@
     <row r="691" ht="15.75" customHeight="1">
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
-      <c r="D691" s="10"/>
+      <c r="D691" s="9"/>
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
       <c r="G691" s="3"/>
@@ -20550,7 +20566,7 @@
     <row r="692" ht="15.75" customHeight="1">
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
-      <c r="D692" s="10"/>
+      <c r="D692" s="9"/>
       <c r="E692" s="3"/>
       <c r="F692" s="3"/>
       <c r="G692" s="3"/>
@@ -20577,7 +20593,7 @@
     <row r="693" ht="15.75" customHeight="1">
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
-      <c r="D693" s="10"/>
+      <c r="D693" s="9"/>
       <c r="E693" s="3"/>
       <c r="F693" s="3"/>
       <c r="G693" s="3"/>
@@ -20604,7 +20620,7 @@
     <row r="694" ht="15.75" customHeight="1">
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
-      <c r="D694" s="10"/>
+      <c r="D694" s="9"/>
       <c r="E694" s="3"/>
       <c r="F694" s="3"/>
       <c r="G694" s="3"/>
@@ -20631,7 +20647,7 @@
     <row r="695" ht="15.75" customHeight="1">
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
-      <c r="D695" s="10"/>
+      <c r="D695" s="9"/>
       <c r="E695" s="3"/>
       <c r="F695" s="3"/>
       <c r="G695" s="3"/>
@@ -20658,7 +20674,7 @@
     <row r="696" ht="15.75" customHeight="1">
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
-      <c r="D696" s="10"/>
+      <c r="D696" s="9"/>
       <c r="E696" s="3"/>
       <c r="F696" s="3"/>
       <c r="G696" s="3"/>
@@ -20685,7 +20701,7 @@
     <row r="697" ht="15.75" customHeight="1">
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
-      <c r="D697" s="10"/>
+      <c r="D697" s="9"/>
       <c r="E697" s="3"/>
       <c r="F697" s="3"/>
       <c r="G697" s="3"/>
@@ -20712,7 +20728,7 @@
     <row r="698" ht="15.75" customHeight="1">
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
-      <c r="D698" s="10"/>
+      <c r="D698" s="9"/>
       <c r="E698" s="3"/>
       <c r="F698" s="3"/>
       <c r="G698" s="3"/>
@@ -20739,7 +20755,7 @@
     <row r="699" ht="15.75" customHeight="1">
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
-      <c r="D699" s="10"/>
+      <c r="D699" s="9"/>
       <c r="E699" s="3"/>
       <c r="F699" s="3"/>
       <c r="G699" s="3"/>
@@ -20766,7 +20782,7 @@
     <row r="700" ht="15.75" customHeight="1">
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
-      <c r="D700" s="10"/>
+      <c r="D700" s="9"/>
       <c r="E700" s="3"/>
       <c r="F700" s="3"/>
       <c r="G700" s="3"/>
@@ -20793,7 +20809,7 @@
     <row r="701" ht="15.75" customHeight="1">
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
-      <c r="D701" s="10"/>
+      <c r="D701" s="9"/>
       <c r="E701" s="3"/>
       <c r="F701" s="3"/>
       <c r="G701" s="3"/>
@@ -20820,7 +20836,7 @@
     <row r="702" ht="15.75" customHeight="1">
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
-      <c r="D702" s="10"/>
+      <c r="D702" s="9"/>
       <c r="E702" s="3"/>
       <c r="F702" s="3"/>
       <c r="G702" s="3"/>
@@ -20847,7 +20863,7 @@
     <row r="703" ht="15.75" customHeight="1">
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
-      <c r="D703" s="10"/>
+      <c r="D703" s="9"/>
       <c r="E703" s="3"/>
       <c r="F703" s="3"/>
       <c r="G703" s="3"/>
@@ -20874,7 +20890,7 @@
     <row r="704" ht="15.75" customHeight="1">
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
-      <c r="D704" s="10"/>
+      <c r="D704" s="9"/>
       <c r="E704" s="3"/>
       <c r="F704" s="3"/>
       <c r="G704" s="3"/>
@@ -20901,7 +20917,7 @@
     <row r="705" ht="15.75" customHeight="1">
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
-      <c r="D705" s="10"/>
+      <c r="D705" s="9"/>
       <c r="E705" s="3"/>
       <c r="F705" s="3"/>
       <c r="G705" s="3"/>
@@ -20928,7 +20944,7 @@
     <row r="706" ht="15.75" customHeight="1">
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
-      <c r="D706" s="10"/>
+      <c r="D706" s="9"/>
       <c r="E706" s="3"/>
       <c r="F706" s="3"/>
       <c r="G706" s="3"/>
@@ -20955,7 +20971,7 @@
     <row r="707" ht="15.75" customHeight="1">
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
-      <c r="D707" s="10"/>
+      <c r="D707" s="9"/>
       <c r="E707" s="3"/>
       <c r="F707" s="3"/>
       <c r="G707" s="3"/>
@@ -20982,7 +20998,7 @@
     <row r="708" ht="15.75" customHeight="1">
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
-      <c r="D708" s="10"/>
+      <c r="D708" s="9"/>
       <c r="E708" s="3"/>
       <c r="F708" s="3"/>
       <c r="G708" s="3"/>
@@ -21009,7 +21025,7 @@
     <row r="709" ht="15.75" customHeight="1">
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
-      <c r="D709" s="10"/>
+      <c r="D709" s="9"/>
       <c r="E709" s="3"/>
       <c r="F709" s="3"/>
       <c r="G709" s="3"/>
@@ -21036,7 +21052,7 @@
     <row r="710" ht="15.75" customHeight="1">
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
-      <c r="D710" s="10"/>
+      <c r="D710" s="9"/>
       <c r="E710" s="3"/>
       <c r="F710" s="3"/>
       <c r="G710" s="3"/>
@@ -21063,7 +21079,7 @@
     <row r="711" ht="15.75" customHeight="1">
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
-      <c r="D711" s="10"/>
+      <c r="D711" s="9"/>
       <c r="E711" s="3"/>
       <c r="F711" s="3"/>
       <c r="G711" s="3"/>
@@ -21090,7 +21106,7 @@
     <row r="712" ht="15.75" customHeight="1">
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
-      <c r="D712" s="10"/>
+      <c r="D712" s="9"/>
       <c r="E712" s="3"/>
       <c r="F712" s="3"/>
       <c r="G712" s="3"/>
@@ -21117,7 +21133,7 @@
     <row r="713" ht="15.75" customHeight="1">
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
-      <c r="D713" s="10"/>
+      <c r="D713" s="9"/>
       <c r="E713" s="3"/>
       <c r="F713" s="3"/>
       <c r="G713" s="3"/>
@@ -21144,7 +21160,7 @@
     <row r="714" ht="15.75" customHeight="1">
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
-      <c r="D714" s="10"/>
+      <c r="D714" s="9"/>
       <c r="E714" s="3"/>
       <c r="F714" s="3"/>
       <c r="G714" s="3"/>
@@ -21171,7 +21187,7 @@
     <row r="715" ht="15.75" customHeight="1">
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
-      <c r="D715" s="10"/>
+      <c r="D715" s="9"/>
       <c r="E715" s="3"/>
       <c r="F715" s="3"/>
       <c r="G715" s="3"/>
@@ -21198,7 +21214,7 @@
     <row r="716" ht="15.75" customHeight="1">
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
-      <c r="D716" s="10"/>
+      <c r="D716" s="9"/>
       <c r="E716" s="3"/>
       <c r="F716" s="3"/>
       <c r="G716" s="3"/>
@@ -21225,7 +21241,7 @@
     <row r="717" ht="15.75" customHeight="1">
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
-      <c r="D717" s="10"/>
+      <c r="D717" s="9"/>
       <c r="E717" s="3"/>
       <c r="F717" s="3"/>
       <c r="G717" s="3"/>
@@ -21252,7 +21268,7 @@
     <row r="718" ht="15.75" customHeight="1">
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
-      <c r="D718" s="10"/>
+      <c r="D718" s="9"/>
       <c r="E718" s="3"/>
       <c r="F718" s="3"/>
       <c r="G718" s="3"/>
@@ -21279,7 +21295,7 @@
     <row r="719" ht="15.75" customHeight="1">
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
-      <c r="D719" s="10"/>
+      <c r="D719" s="9"/>
       <c r="E719" s="3"/>
       <c r="F719" s="3"/>
       <c r="G719" s="3"/>
@@ -21306,7 +21322,7 @@
     <row r="720" ht="15.75" customHeight="1">
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
-      <c r="D720" s="10"/>
+      <c r="D720" s="9"/>
       <c r="E720" s="3"/>
       <c r="F720" s="3"/>
       <c r="G720" s="3"/>
@@ -21333,7 +21349,7 @@
     <row r="721" ht="15.75" customHeight="1">
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
-      <c r="D721" s="10"/>
+      <c r="D721" s="9"/>
       <c r="E721" s="3"/>
       <c r="F721" s="3"/>
       <c r="G721" s="3"/>
@@ -21360,7 +21376,7 @@
     <row r="722" ht="15.75" customHeight="1">
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
-      <c r="D722" s="10"/>
+      <c r="D722" s="9"/>
       <c r="E722" s="3"/>
       <c r="F722" s="3"/>
       <c r="G722" s="3"/>
@@ -21387,7 +21403,7 @@
     <row r="723" ht="15.75" customHeight="1">
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
-      <c r="D723" s="10"/>
+      <c r="D723" s="9"/>
       <c r="E723" s="3"/>
       <c r="F723" s="3"/>
       <c r="G723" s="3"/>
@@ -21414,7 +21430,7 @@
     <row r="724" ht="15.75" customHeight="1">
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
-      <c r="D724" s="10"/>
+      <c r="D724" s="9"/>
       <c r="E724" s="3"/>
       <c r="F724" s="3"/>
       <c r="G724" s="3"/>
@@ -21441,7 +21457,7 @@
     <row r="725" ht="15.75" customHeight="1">
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
-      <c r="D725" s="10"/>
+      <c r="D725" s="9"/>
       <c r="E725" s="3"/>
       <c r="F725" s="3"/>
       <c r="G725" s="3"/>
@@ -21468,7 +21484,7 @@
     <row r="726" ht="15.75" customHeight="1">
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
-      <c r="D726" s="10"/>
+      <c r="D726" s="9"/>
       <c r="E726" s="3"/>
       <c r="F726" s="3"/>
       <c r="G726" s="3"/>
@@ -21495,7 +21511,7 @@
     <row r="727" ht="15.75" customHeight="1">
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
-      <c r="D727" s="10"/>
+      <c r="D727" s="9"/>
       <c r="E727" s="3"/>
       <c r="F727" s="3"/>
       <c r="G727" s="3"/>
@@ -21522,7 +21538,7 @@
     <row r="728" ht="15.75" customHeight="1">
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
-      <c r="D728" s="10"/>
+      <c r="D728" s="9"/>
       <c r="E728" s="3"/>
       <c r="F728" s="3"/>
       <c r="G728" s="3"/>
@@ -21549,7 +21565,7 @@
     <row r="729" ht="15.75" customHeight="1">
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
-      <c r="D729" s="10"/>
+      <c r="D729" s="9"/>
       <c r="E729" s="3"/>
       <c r="F729" s="3"/>
       <c r="G729" s="3"/>
@@ -21576,7 +21592,7 @@
     <row r="730" ht="15.75" customHeight="1">
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
-      <c r="D730" s="10"/>
+      <c r="D730" s="9"/>
       <c r="E730" s="3"/>
       <c r="F730" s="3"/>
       <c r="G730" s="3"/>
@@ -21603,7 +21619,7 @@
     <row r="731" ht="15.75" customHeight="1">
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
-      <c r="D731" s="10"/>
+      <c r="D731" s="9"/>
       <c r="E731" s="3"/>
       <c r="F731" s="3"/>
       <c r="G731" s="3"/>
@@ -21630,7 +21646,7 @@
     <row r="732" ht="15.75" customHeight="1">
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
-      <c r="D732" s="10"/>
+      <c r="D732" s="9"/>
       <c r="E732" s="3"/>
       <c r="F732" s="3"/>
       <c r="G732" s="3"/>
@@ -21657,7 +21673,7 @@
     <row r="733" ht="15.75" customHeight="1">
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
-      <c r="D733" s="10"/>
+      <c r="D733" s="9"/>
       <c r="E733" s="3"/>
       <c r="F733" s="3"/>
       <c r="G733" s="3"/>
@@ -21684,7 +21700,7 @@
     <row r="734" ht="15.75" customHeight="1">
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
-      <c r="D734" s="10"/>
+      <c r="D734" s="9"/>
       <c r="E734" s="3"/>
       <c r="F734" s="3"/>
       <c r="G734" s="3"/>
@@ -21711,7 +21727,7 @@
     <row r="735" ht="15.75" customHeight="1">
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
-      <c r="D735" s="10"/>
+      <c r="D735" s="9"/>
       <c r="E735" s="3"/>
       <c r="F735" s="3"/>
       <c r="G735" s="3"/>
@@ -21738,7 +21754,7 @@
     <row r="736" ht="15.75" customHeight="1">
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
-      <c r="D736" s="10"/>
+      <c r="D736" s="9"/>
       <c r="E736" s="3"/>
       <c r="F736" s="3"/>
       <c r="G736" s="3"/>
@@ -21765,7 +21781,7 @@
     <row r="737" ht="15.75" customHeight="1">
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
-      <c r="D737" s="10"/>
+      <c r="D737" s="9"/>
       <c r="E737" s="3"/>
       <c r="F737" s="3"/>
       <c r="G737" s="3"/>
@@ -21792,7 +21808,7 @@
     <row r="738" ht="15.75" customHeight="1">
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
-      <c r="D738" s="10"/>
+      <c r="D738" s="9"/>
       <c r="E738" s="3"/>
       <c r="F738" s="3"/>
       <c r="G738" s="3"/>
@@ -21819,7 +21835,7 @@
     <row r="739" ht="15.75" customHeight="1">
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
-      <c r="D739" s="10"/>
+      <c r="D739" s="9"/>
       <c r="E739" s="3"/>
       <c r="F739" s="3"/>
       <c r="G739" s="3"/>
@@ -21846,7 +21862,7 @@
     <row r="740" ht="15.75" customHeight="1">
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
-      <c r="D740" s="10"/>
+      <c r="D740" s="9"/>
       <c r="E740" s="3"/>
       <c r="F740" s="3"/>
       <c r="G740" s="3"/>
@@ -21873,7 +21889,7 @@
     <row r="741" ht="15.75" customHeight="1">
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
-      <c r="D741" s="10"/>
+      <c r="D741" s="9"/>
       <c r="E741" s="3"/>
       <c r="F741" s="3"/>
       <c r="G741" s="3"/>
@@ -21900,7 +21916,7 @@
     <row r="742" ht="15.75" customHeight="1">
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
-      <c r="D742" s="10"/>
+      <c r="D742" s="9"/>
       <c r="E742" s="3"/>
       <c r="F742" s="3"/>
       <c r="G742" s="3"/>
@@ -21927,7 +21943,7 @@
     <row r="743" ht="15.75" customHeight="1">
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
-      <c r="D743" s="10"/>
+      <c r="D743" s="9"/>
       <c r="E743" s="3"/>
       <c r="F743" s="3"/>
       <c r="G743" s="3"/>
@@ -21954,7 +21970,7 @@
     <row r="744" ht="15.75" customHeight="1">
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
-      <c r="D744" s="10"/>
+      <c r="D744" s="9"/>
       <c r="E744" s="3"/>
       <c r="F744" s="3"/>
       <c r="G744" s="3"/>
@@ -21981,7 +21997,7 @@
     <row r="745" ht="15.75" customHeight="1">
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
-      <c r="D745" s="10"/>
+      <c r="D745" s="9"/>
       <c r="E745" s="3"/>
       <c r="F745" s="3"/>
       <c r="G745" s="3"/>
@@ -22008,7 +22024,7 @@
     <row r="746" ht="15.75" customHeight="1">
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
-      <c r="D746" s="10"/>
+      <c r="D746" s="9"/>
       <c r="E746" s="3"/>
       <c r="F746" s="3"/>
       <c r="G746" s="3"/>
@@ -22035,7 +22051,7 @@
     <row r="747" ht="15.75" customHeight="1">
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
-      <c r="D747" s="10"/>
+      <c r="D747" s="9"/>
       <c r="E747" s="3"/>
       <c r="F747" s="3"/>
       <c r="G747" s="3"/>
@@ -22062,7 +22078,7 @@
     <row r="748" ht="15.75" customHeight="1">
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
-      <c r="D748" s="10"/>
+      <c r="D748" s="9"/>
       <c r="E748" s="3"/>
       <c r="F748" s="3"/>
       <c r="G748" s="3"/>
@@ -22089,7 +22105,7 @@
     <row r="749" ht="15.75" customHeight="1">
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
-      <c r="D749" s="10"/>
+      <c r="D749" s="9"/>
       <c r="E749" s="3"/>
       <c r="F749" s="3"/>
       <c r="G749" s="3"/>
@@ -22116,7 +22132,7 @@
     <row r="750" ht="15.75" customHeight="1">
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
-      <c r="D750" s="10"/>
+      <c r="D750" s="9"/>
       <c r="E750" s="3"/>
       <c r="F750" s="3"/>
       <c r="G750" s="3"/>
@@ -22143,7 +22159,7 @@
     <row r="751" ht="15.75" customHeight="1">
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
-      <c r="D751" s="10"/>
+      <c r="D751" s="9"/>
       <c r="E751" s="3"/>
       <c r="F751" s="3"/>
       <c r="G751" s="3"/>
@@ -22170,7 +22186,7 @@
     <row r="752" ht="15.75" customHeight="1">
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
-      <c r="D752" s="10"/>
+      <c r="D752" s="9"/>
       <c r="E752" s="3"/>
       <c r="F752" s="3"/>
       <c r="G752" s="3"/>
@@ -22197,7 +22213,7 @@
     <row r="753" ht="15.75" customHeight="1">
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
-      <c r="D753" s="10"/>
+      <c r="D753" s="9"/>
       <c r="E753" s="3"/>
       <c r="F753" s="3"/>
       <c r="G753" s="3"/>
@@ -22224,7 +22240,7 @@
     <row r="754" ht="15.75" customHeight="1">
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
-      <c r="D754" s="10"/>
+      <c r="D754" s="9"/>
       <c r="E754" s="3"/>
       <c r="F754" s="3"/>
       <c r="G754" s="3"/>
@@ -22251,7 +22267,7 @@
     <row r="755" ht="15.75" customHeight="1">
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
-      <c r="D755" s="10"/>
+      <c r="D755" s="9"/>
       <c r="E755" s="3"/>
       <c r="F755" s="3"/>
       <c r="G755" s="3"/>
@@ -22278,7 +22294,7 @@
     <row r="756" ht="15.75" customHeight="1">
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
-      <c r="D756" s="10"/>
+      <c r="D756" s="9"/>
       <c r="E756" s="3"/>
       <c r="F756" s="3"/>
       <c r="G756" s="3"/>
@@ -22305,7 +22321,7 @@
     <row r="757" ht="15.75" customHeight="1">
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
-      <c r="D757" s="10"/>
+      <c r="D757" s="9"/>
       <c r="E757" s="3"/>
       <c r="F757" s="3"/>
       <c r="G757" s="3"/>
@@ -22332,7 +22348,7 @@
     <row r="758" ht="15.75" customHeight="1">
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
-      <c r="D758" s="10"/>
+      <c r="D758" s="9"/>
       <c r="E758" s="3"/>
       <c r="F758" s="3"/>
       <c r="G758" s="3"/>
@@ -22359,7 +22375,7 @@
     <row r="759" ht="15.75" customHeight="1">
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
-      <c r="D759" s="10"/>
+      <c r="D759" s="9"/>
       <c r="E759" s="3"/>
       <c r="F759" s="3"/>
       <c r="G759" s="3"/>
@@ -22386,7 +22402,7 @@
     <row r="760" ht="15.75" customHeight="1">
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
-      <c r="D760" s="10"/>
+      <c r="D760" s="9"/>
       <c r="E760" s="3"/>
       <c r="F760" s="3"/>
       <c r="G760" s="3"/>
@@ -22413,7 +22429,7 @@
     <row r="761" ht="15.75" customHeight="1">
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
-      <c r="D761" s="10"/>
+      <c r="D761" s="9"/>
       <c r="E761" s="3"/>
       <c r="F761" s="3"/>
       <c r="G761" s="3"/>
@@ -22440,7 +22456,7 @@
     <row r="762" ht="15.75" customHeight="1">
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
-      <c r="D762" s="10"/>
+      <c r="D762" s="9"/>
       <c r="E762" s="3"/>
       <c r="F762" s="3"/>
       <c r="G762" s="3"/>
@@ -22467,7 +22483,7 @@
     <row r="763" ht="15.75" customHeight="1">
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
-      <c r="D763" s="10"/>
+      <c r="D763" s="9"/>
       <c r="E763" s="3"/>
       <c r="F763" s="3"/>
       <c r="G763" s="3"/>
@@ -22494,7 +22510,7 @@
     <row r="764" ht="15.75" customHeight="1">
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
-      <c r="D764" s="10"/>
+      <c r="D764" s="9"/>
       <c r="E764" s="3"/>
       <c r="F764" s="3"/>
       <c r="G764" s="3"/>
@@ -22521,7 +22537,7 @@
     <row r="765" ht="15.75" customHeight="1">
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
-      <c r="D765" s="10"/>
+      <c r="D765" s="9"/>
       <c r="E765" s="3"/>
       <c r="F765" s="3"/>
       <c r="G765" s="3"/>
@@ -22548,7 +22564,7 @@
     <row r="766" ht="15.75" customHeight="1">
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
-      <c r="D766" s="10"/>
+      <c r="D766" s="9"/>
       <c r="E766" s="3"/>
       <c r="F766" s="3"/>
       <c r="G766" s="3"/>
@@ -22575,7 +22591,7 @@
     <row r="767" ht="15.75" customHeight="1">
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
-      <c r="D767" s="10"/>
+      <c r="D767" s="9"/>
       <c r="E767" s="3"/>
       <c r="F767" s="3"/>
       <c r="G767" s="3"/>
@@ -22602,7 +22618,7 @@
     <row r="768" ht="15.75" customHeight="1">
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
-      <c r="D768" s="10"/>
+      <c r="D768" s="9"/>
       <c r="E768" s="3"/>
       <c r="F768" s="3"/>
       <c r="G768" s="3"/>
@@ -22629,7 +22645,7 @@
     <row r="769" ht="15.75" customHeight="1">
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
-      <c r="D769" s="10"/>
+      <c r="D769" s="9"/>
       <c r="E769" s="3"/>
       <c r="F769" s="3"/>
       <c r="G769" s="3"/>
@@ -22656,7 +22672,7 @@
     <row r="770" ht="15.75" customHeight="1">
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
-      <c r="D770" s="10"/>
+      <c r="D770" s="9"/>
       <c r="E770" s="3"/>
       <c r="F770" s="3"/>
       <c r="G770" s="3"/>
@@ -22683,7 +22699,7 @@
     <row r="771" ht="15.75" customHeight="1">
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
-      <c r="D771" s="10"/>
+      <c r="D771" s="9"/>
       <c r="E771" s="3"/>
       <c r="F771" s="3"/>
       <c r="G771" s="3"/>
@@ -22710,7 +22726,7 @@
     <row r="772" ht="15.75" customHeight="1">
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
-      <c r="D772" s="10"/>
+      <c r="D772" s="9"/>
       <c r="E772" s="3"/>
       <c r="F772" s="3"/>
       <c r="G772" s="3"/>
@@ -22737,7 +22753,7 @@
     <row r="773" ht="15.75" customHeight="1">
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
-      <c r="D773" s="10"/>
+      <c r="D773" s="9"/>
       <c r="E773" s="3"/>
       <c r="F773" s="3"/>
       <c r="G773" s="3"/>
@@ -22764,7 +22780,7 @@
     <row r="774" ht="15.75" customHeight="1">
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
-      <c r="D774" s="10"/>
+      <c r="D774" s="9"/>
       <c r="E774" s="3"/>
       <c r="F774" s="3"/>
       <c r="G774" s="3"/>
@@ -22791,7 +22807,7 @@
     <row r="775" ht="15.75" customHeight="1">
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
-      <c r="D775" s="10"/>
+      <c r="D775" s="9"/>
       <c r="E775" s="3"/>
       <c r="F775" s="3"/>
       <c r="G775" s="3"/>
@@ -22818,7 +22834,7 @@
     <row r="776" ht="15.75" customHeight="1">
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
-      <c r="D776" s="10"/>
+      <c r="D776" s="9"/>
       <c r="E776" s="3"/>
       <c r="F776" s="3"/>
       <c r="G776" s="3"/>
@@ -22845,7 +22861,7 @@
     <row r="777" ht="15.75" customHeight="1">
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
-      <c r="D777" s="10"/>
+      <c r="D777" s="9"/>
       <c r="E777" s="3"/>
       <c r="F777" s="3"/>
       <c r="G777" s="3"/>
@@ -22872,7 +22888,7 @@
     <row r="778" ht="15.75" customHeight="1">
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
-      <c r="D778" s="10"/>
+      <c r="D778" s="9"/>
       <c r="E778" s="3"/>
       <c r="F778" s="3"/>
       <c r="G778" s="3"/>
@@ -22899,7 +22915,7 @@
     <row r="779" ht="15.75" customHeight="1">
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
-      <c r="D779" s="10"/>
+      <c r="D779" s="9"/>
       <c r="E779" s="3"/>
       <c r="F779" s="3"/>
       <c r="G779" s="3"/>
@@ -22926,7 +22942,7 @@
     <row r="780" ht="15.75" customHeight="1">
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
-      <c r="D780" s="10"/>
+      <c r="D780" s="9"/>
       <c r="E780" s="3"/>
       <c r="F780" s="3"/>
       <c r="G780" s="3"/>
@@ -22953,7 +22969,7 @@
     <row r="781" ht="15.75" customHeight="1">
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
-      <c r="D781" s="10"/>
+      <c r="D781" s="9"/>
       <c r="E781" s="3"/>
       <c r="F781" s="3"/>
       <c r="G781" s="3"/>
@@ -22980,7 +22996,7 @@
     <row r="782" ht="15.75" customHeight="1">
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
-      <c r="D782" s="10"/>
+      <c r="D782" s="9"/>
       <c r="E782" s="3"/>
       <c r="F782" s="3"/>
       <c r="G782" s="3"/>
@@ -23007,7 +23023,7 @@
     <row r="783" ht="15.75" customHeight="1">
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
-      <c r="D783" s="10"/>
+      <c r="D783" s="9"/>
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
       <c r="G783" s="3"/>
@@ -23034,7 +23050,7 @@
     <row r="784" ht="15.75" customHeight="1">
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
-      <c r="D784" s="10"/>
+      <c r="D784" s="9"/>
       <c r="E784" s="3"/>
       <c r="F784" s="3"/>
       <c r="G784" s="3"/>
@@ -23061,7 +23077,7 @@
     <row r="785" ht="15.75" customHeight="1">
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
-      <c r="D785" s="10"/>
+      <c r="D785" s="9"/>
       <c r="E785" s="3"/>
       <c r="F785" s="3"/>
       <c r="G785" s="3"/>
@@ -23088,7 +23104,7 @@
     <row r="786" ht="15.75" customHeight="1">
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
-      <c r="D786" s="10"/>
+      <c r="D786" s="9"/>
       <c r="E786" s="3"/>
       <c r="F786" s="3"/>
       <c r="G786" s="3"/>
@@ -23115,7 +23131,7 @@
     <row r="787" ht="15.75" customHeight="1">
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
-      <c r="D787" s="10"/>
+      <c r="D787" s="9"/>
       <c r="E787" s="3"/>
       <c r="F787" s="3"/>
       <c r="G787" s="3"/>
@@ -23142,7 +23158,7 @@
     <row r="788" ht="15.75" customHeight="1">
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
-      <c r="D788" s="10"/>
+      <c r="D788" s="9"/>
       <c r="E788" s="3"/>
       <c r="F788" s="3"/>
       <c r="G788" s="3"/>
@@ -23169,7 +23185,7 @@
     <row r="789" ht="15.75" customHeight="1">
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
-      <c r="D789" s="10"/>
+      <c r="D789" s="9"/>
       <c r="E789" s="3"/>
       <c r="F789" s="3"/>
       <c r="G789" s="3"/>
@@ -23196,7 +23212,7 @@
     <row r="790" ht="15.75" customHeight="1">
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
-      <c r="D790" s="10"/>
+      <c r="D790" s="9"/>
       <c r="E790" s="3"/>
       <c r="F790" s="3"/>
       <c r="G790" s="3"/>
@@ -23223,7 +23239,7 @@
     <row r="791" ht="15.75" customHeight="1">
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
-      <c r="D791" s="10"/>
+      <c r="D791" s="9"/>
       <c r="E791" s="3"/>
       <c r="F791" s="3"/>
       <c r="G791" s="3"/>
@@ -23250,7 +23266,7 @@
     <row r="792" ht="15.75" customHeight="1">
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
-      <c r="D792" s="10"/>
+      <c r="D792" s="9"/>
       <c r="E792" s="3"/>
       <c r="F792" s="3"/>
       <c r="G792" s="3"/>
@@ -23277,7 +23293,7 @@
     <row r="793" ht="15.75" customHeight="1">
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
-      <c r="D793" s="10"/>
+      <c r="D793" s="9"/>
       <c r="E793" s="3"/>
       <c r="F793" s="3"/>
       <c r="G793" s="3"/>
@@ -23304,7 +23320,7 @@
     <row r="794" ht="15.75" customHeight="1">
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
-      <c r="D794" s="10"/>
+      <c r="D794" s="9"/>
       <c r="E794" s="3"/>
       <c r="F794" s="3"/>
       <c r="G794" s="3"/>
@@ -23331,7 +23347,7 @@
     <row r="795" ht="15.75" customHeight="1">
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
-      <c r="D795" s="10"/>
+      <c r="D795" s="9"/>
       <c r="E795" s="3"/>
       <c r="F795" s="3"/>
       <c r="G795" s="3"/>
@@ -23358,7 +23374,7 @@
     <row r="796" ht="15.75" customHeight="1">
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
-      <c r="D796" s="10"/>
+      <c r="D796" s="9"/>
       <c r="E796" s="3"/>
       <c r="F796" s="3"/>
       <c r="G796" s="3"/>
@@ -23385,7 +23401,7 @@
     <row r="797" ht="15.75" customHeight="1">
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
-      <c r="D797" s="10"/>
+      <c r="D797" s="9"/>
       <c r="E797" s="3"/>
       <c r="F797" s="3"/>
       <c r="G797" s="3"/>
@@ -23412,7 +23428,7 @@
     <row r="798" ht="15.75" customHeight="1">
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
-      <c r="D798" s="10"/>
+      <c r="D798" s="9"/>
       <c r="E798" s="3"/>
       <c r="F798" s="3"/>
       <c r="G798" s="3"/>
@@ -23439,7 +23455,7 @@
     <row r="799" ht="15.75" customHeight="1">
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
-      <c r="D799" s="10"/>
+      <c r="D799" s="9"/>
       <c r="E799" s="3"/>
       <c r="F799" s="3"/>
       <c r="G799" s="3"/>
@@ -23466,7 +23482,7 @@
     <row r="800" ht="15.75" customHeight="1">
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
-      <c r="D800" s="10"/>
+      <c r="D800" s="9"/>
       <c r="E800" s="3"/>
       <c r="F800" s="3"/>
       <c r="G800" s="3"/>
@@ -23493,7 +23509,7 @@
     <row r="801" ht="15.75" customHeight="1">
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
-      <c r="D801" s="10"/>
+      <c r="D801" s="9"/>
       <c r="E801" s="3"/>
       <c r="F801" s="3"/>
       <c r="G801" s="3"/>
@@ -23520,7 +23536,7 @@
     <row r="802" ht="15.75" customHeight="1">
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
-      <c r="D802" s="10"/>
+      <c r="D802" s="9"/>
       <c r="E802" s="3"/>
       <c r="F802" s="3"/>
       <c r="G802" s="3"/>
@@ -23547,7 +23563,7 @@
     <row r="803" ht="15.75" customHeight="1">
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
-      <c r="D803" s="10"/>
+      <c r="D803" s="9"/>
       <c r="E803" s="3"/>
       <c r="F803" s="3"/>
       <c r="G803" s="3"/>
@@ -23574,7 +23590,7 @@
     <row r="804" ht="15.75" customHeight="1">
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
-      <c r="D804" s="10"/>
+      <c r="D804" s="9"/>
       <c r="E804" s="3"/>
       <c r="F804" s="3"/>
       <c r="G804" s="3"/>
@@ -23601,7 +23617,7 @@
     <row r="805" ht="15.75" customHeight="1">
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
-      <c r="D805" s="10"/>
+      <c r="D805" s="9"/>
       <c r="E805" s="3"/>
       <c r="F805" s="3"/>
       <c r="G805" s="3"/>
@@ -23628,7 +23644,7 @@
     <row r="806" ht="15.75" customHeight="1">
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
-      <c r="D806" s="10"/>
+      <c r="D806" s="9"/>
       <c r="E806" s="3"/>
       <c r="F806" s="3"/>
       <c r="G806" s="3"/>
@@ -23655,7 +23671,7 @@
     <row r="807" ht="15.75" customHeight="1">
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
-      <c r="D807" s="10"/>
+      <c r="D807" s="9"/>
       <c r="E807" s="3"/>
       <c r="F807" s="3"/>
       <c r="G807" s="3"/>
@@ -23682,7 +23698,7 @@
     <row r="808" ht="15.75" customHeight="1">
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
-      <c r="D808" s="10"/>
+      <c r="D808" s="9"/>
       <c r="E808" s="3"/>
       <c r="F808" s="3"/>
       <c r="G808" s="3"/>
@@ -23709,7 +23725,7 @@
     <row r="809" ht="15.75" customHeight="1">
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
-      <c r="D809" s="10"/>
+      <c r="D809" s="9"/>
       <c r="E809" s="3"/>
       <c r="F809" s="3"/>
       <c r="G809" s="3"/>
@@ -23736,7 +23752,7 @@
     <row r="810" ht="15.75" customHeight="1">
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
-      <c r="D810" s="10"/>
+      <c r="D810" s="9"/>
       <c r="E810" s="3"/>
       <c r="F810" s="3"/>
       <c r="G810" s="3"/>
@@ -23763,7 +23779,7 @@
     <row r="811" ht="15.75" customHeight="1">
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
-      <c r="D811" s="10"/>
+      <c r="D811" s="9"/>
       <c r="E811" s="3"/>
       <c r="F811" s="3"/>
       <c r="G811" s="3"/>
@@ -23790,7 +23806,7 @@
     <row r="812" ht="15.75" customHeight="1">
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
-      <c r="D812" s="10"/>
+      <c r="D812" s="9"/>
       <c r="E812" s="3"/>
       <c r="F812" s="3"/>
       <c r="G812" s="3"/>
@@ -23817,7 +23833,7 @@
     <row r="813" ht="15.75" customHeight="1">
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
-      <c r="D813" s="10"/>
+      <c r="D813" s="9"/>
       <c r="E813" s="3"/>
       <c r="F813" s="3"/>
       <c r="G813" s="3"/>
@@ -23844,7 +23860,7 @@
     <row r="814" ht="15.75" customHeight="1">
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
-      <c r="D814" s="10"/>
+      <c r="D814" s="9"/>
       <c r="E814" s="3"/>
       <c r="F814" s="3"/>
       <c r="G814" s="3"/>
@@ -23871,7 +23887,7 @@
     <row r="815" ht="15.75" customHeight="1">
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
-      <c r="D815" s="10"/>
+      <c r="D815" s="9"/>
       <c r="E815" s="3"/>
       <c r="F815" s="3"/>
       <c r="G815" s="3"/>
@@ -23898,7 +23914,7 @@
     <row r="816" ht="15.75" customHeight="1">
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
-      <c r="D816" s="10"/>
+      <c r="D816" s="9"/>
       <c r="E816" s="3"/>
       <c r="F816" s="3"/>
       <c r="G816" s="3"/>
@@ -23925,7 +23941,7 @@
     <row r="817" ht="15.75" customHeight="1">
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
-      <c r="D817" s="10"/>
+      <c r="D817" s="9"/>
       <c r="E817" s="3"/>
       <c r="F817" s="3"/>
       <c r="G817" s="3"/>
@@ -23952,7 +23968,7 @@
     <row r="818" ht="15.75" customHeight="1">
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
-      <c r="D818" s="10"/>
+      <c r="D818" s="9"/>
       <c r="E818" s="3"/>
       <c r="F818" s="3"/>
       <c r="G818" s="3"/>
@@ -23979,7 +23995,7 @@
     <row r="819" ht="15.75" customHeight="1">
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
-      <c r="D819" s="10"/>
+      <c r="D819" s="9"/>
       <c r="E819" s="3"/>
       <c r="F819" s="3"/>
       <c r="G819" s="3"/>
@@ -24006,7 +24022,7 @@
     <row r="820" ht="15.75" customHeight="1">
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
-      <c r="D820" s="10"/>
+      <c r="D820" s="9"/>
       <c r="E820" s="3"/>
       <c r="F820" s="3"/>
       <c r="G820" s="3"/>
@@ -24033,7 +24049,7 @@
     <row r="821" ht="15.75" customHeight="1">
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
-      <c r="D821" s="10"/>
+      <c r="D821" s="9"/>
       <c r="E821" s="3"/>
       <c r="F821" s="3"/>
       <c r="G821" s="3"/>
@@ -24060,7 +24076,7 @@
     <row r="822" ht="15.75" customHeight="1">
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
-      <c r="D822" s="10"/>
+      <c r="D822" s="9"/>
       <c r="E822" s="3"/>
       <c r="F822" s="3"/>
       <c r="G822" s="3"/>
@@ -24087,7 +24103,7 @@
     <row r="823" ht="15.75" customHeight="1">
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
-      <c r="D823" s="10"/>
+      <c r="D823" s="9"/>
       <c r="E823" s="3"/>
       <c r="F823" s="3"/>
       <c r="G823" s="3"/>
@@ -24114,7 +24130,7 @@
     <row r="824" ht="15.75" customHeight="1">
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
-      <c r="D824" s="10"/>
+      <c r="D824" s="9"/>
       <c r="E824" s="3"/>
       <c r="F824" s="3"/>
       <c r="G824" s="3"/>
@@ -24141,7 +24157,7 @@
     <row r="825" ht="15.75" customHeight="1">
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
-      <c r="D825" s="10"/>
+      <c r="D825" s="9"/>
       <c r="E825" s="3"/>
       <c r="F825" s="3"/>
       <c r="G825" s="3"/>
@@ -24168,7 +24184,7 @@
     <row r="826" ht="15.75" customHeight="1">
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
-      <c r="D826" s="10"/>
+      <c r="D826" s="9"/>
       <c r="E826" s="3"/>
       <c r="F826" s="3"/>
       <c r="G826" s="3"/>
@@ -24195,7 +24211,7 @@
     <row r="827" ht="15.75" customHeight="1">
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
-      <c r="D827" s="10"/>
+      <c r="D827" s="9"/>
       <c r="E827" s="3"/>
       <c r="F827" s="3"/>
       <c r="G827" s="3"/>
@@ -24222,7 +24238,7 @@
     <row r="828" ht="15.75" customHeight="1">
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
-      <c r="D828" s="10"/>
+      <c r="D828" s="9"/>
       <c r="E828" s="3"/>
       <c r="F828" s="3"/>
       <c r="G828" s="3"/>
@@ -24249,7 +24265,7 @@
     <row r="829" ht="15.75" customHeight="1">
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
-      <c r="D829" s="10"/>
+      <c r="D829" s="9"/>
       <c r="E829" s="3"/>
       <c r="F829" s="3"/>
       <c r="G829" s="3"/>
@@ -24276,7 +24292,7 @@
     <row r="830" ht="15.75" customHeight="1">
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
-      <c r="D830" s="10"/>
+      <c r="D830" s="9"/>
       <c r="E830" s="3"/>
       <c r="F830" s="3"/>
       <c r="G830" s="3"/>
@@ -24303,7 +24319,7 @@
     <row r="831" ht="15.75" customHeight="1">
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
-      <c r="D831" s="10"/>
+      <c r="D831" s="9"/>
       <c r="E831" s="3"/>
       <c r="F831" s="3"/>
       <c r="G831" s="3"/>
@@ -24330,7 +24346,7 @@
     <row r="832" ht="15.75" customHeight="1">
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
-      <c r="D832" s="10"/>
+      <c r="D832" s="9"/>
       <c r="E832" s="3"/>
       <c r="F832" s="3"/>
       <c r="G832" s="3"/>
@@ -24357,7 +24373,7 @@
     <row r="833" ht="15.75" customHeight="1">
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
-      <c r="D833" s="10"/>
+      <c r="D833" s="9"/>
       <c r="E833" s="3"/>
       <c r="F833" s="3"/>
       <c r="G833" s="3"/>
@@ -24384,7 +24400,7 @@
     <row r="834" ht="15.75" customHeight="1">
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
-      <c r="D834" s="10"/>
+      <c r="D834" s="9"/>
       <c r="E834" s="3"/>
       <c r="F834" s="3"/>
       <c r="G834" s="3"/>
@@ -24411,7 +24427,7 @@
     <row r="835" ht="15.75" customHeight="1">
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
-      <c r="D835" s="10"/>
+      <c r="D835" s="9"/>
       <c r="E835" s="3"/>
       <c r="F835" s="3"/>
       <c r="G835" s="3"/>
@@ -24438,7 +24454,7 @@
     <row r="836" ht="15.75" customHeight="1">
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
-      <c r="D836" s="10"/>
+      <c r="D836" s="9"/>
       <c r="E836" s="3"/>
       <c r="F836" s="3"/>
       <c r="G836" s="3"/>
@@ -24465,7 +24481,7 @@
     <row r="837" ht="15.75" customHeight="1">
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
-      <c r="D837" s="10"/>
+      <c r="D837" s="9"/>
       <c r="E837" s="3"/>
       <c r="F837" s="3"/>
       <c r="G837" s="3"/>
@@ -24492,7 +24508,7 @@
     <row r="838" ht="15.75" customHeight="1">
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
-      <c r="D838" s="10"/>
+      <c r="D838" s="9"/>
       <c r="E838" s="3"/>
       <c r="F838" s="3"/>
       <c r="G838" s="3"/>
@@ -24519,7 +24535,7 @@
     <row r="839" ht="15.75" customHeight="1">
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
-      <c r="D839" s="10"/>
+      <c r="D839" s="9"/>
       <c r="E839" s="3"/>
       <c r="F839" s="3"/>
       <c r="G839" s="3"/>
@@ -24546,7 +24562,7 @@
     <row r="840" ht="15.75" customHeight="1">
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
-      <c r="D840" s="10"/>
+      <c r="D840" s="9"/>
       <c r="E840" s="3"/>
       <c r="F840" s="3"/>
       <c r="G840" s="3"/>
@@ -24573,7 +24589,7 @@
     <row r="841" ht="15.75" customHeight="1">
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
-      <c r="D841" s="10"/>
+      <c r="D841" s="9"/>
       <c r="E841" s="3"/>
       <c r="F841" s="3"/>
       <c r="G841" s="3"/>
@@ -24600,7 +24616,7 @@
     <row r="842" ht="15.75" customHeight="1">
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
-      <c r="D842" s="10"/>
+      <c r="D842" s="9"/>
       <c r="E842" s="3"/>
       <c r="F842" s="3"/>
       <c r="G842" s="3"/>
@@ -24627,7 +24643,7 @@
     <row r="843" ht="15.75" customHeight="1">
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
-      <c r="D843" s="10"/>
+      <c r="D843" s="9"/>
       <c r="E843" s="3"/>
       <c r="F843" s="3"/>
       <c r="G843" s="3"/>
@@ -24654,7 +24670,7 @@
     <row r="844" ht="15.75" customHeight="1">
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
-      <c r="D844" s="10"/>
+      <c r="D844" s="9"/>
       <c r="E844" s="3"/>
       <c r="F844" s="3"/>
       <c r="G844" s="3"/>
@@ -24681,7 +24697,7 @@
     <row r="845" ht="15.75" customHeight="1">
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
-      <c r="D845" s="10"/>
+      <c r="D845" s="9"/>
       <c r="E845" s="3"/>
       <c r="F845" s="3"/>
       <c r="G845" s="3"/>
@@ -24708,7 +24724,7 @@
     <row r="846" ht="15.75" customHeight="1">
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
-      <c r="D846" s="10"/>
+      <c r="D846" s="9"/>
       <c r="E846" s="3"/>
       <c r="F846" s="3"/>
       <c r="G846" s="3"/>
@@ -24735,7 +24751,7 @@
     <row r="847" ht="15.75" customHeight="1">
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
-      <c r="D847" s="10"/>
+      <c r="D847" s="9"/>
       <c r="E847" s="3"/>
       <c r="F847" s="3"/>
       <c r="G847" s="3"/>
@@ -24762,7 +24778,7 @@
     <row r="848" ht="15.75" customHeight="1">
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
-      <c r="D848" s="10"/>
+      <c r="D848" s="9"/>
       <c r="E848" s="3"/>
       <c r="F848" s="3"/>
       <c r="G848" s="3"/>
@@ -24789,7 +24805,7 @@
     <row r="849" ht="15.75" customHeight="1">
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
-      <c r="D849" s="10"/>
+      <c r="D849" s="9"/>
       <c r="E849" s="3"/>
       <c r="F849" s="3"/>
       <c r="G849" s="3"/>
@@ -24816,7 +24832,7 @@
     <row r="850" ht="15.75" customHeight="1">
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
-      <c r="D850" s="10"/>
+      <c r="D850" s="9"/>
       <c r="E850" s="3"/>
       <c r="F850" s="3"/>
       <c r="G850" s="3"/>
@@ -24843,7 +24859,7 @@
     <row r="851" ht="15.75" customHeight="1">
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
-      <c r="D851" s="10"/>
+      <c r="D851" s="9"/>
       <c r="E851" s="3"/>
       <c r="F851" s="3"/>
       <c r="G851" s="3"/>
@@ -24870,7 +24886,7 @@
     <row r="852" ht="15.75" customHeight="1">
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
-      <c r="D852" s="10"/>
+      <c r="D852" s="9"/>
       <c r="E852" s="3"/>
       <c r="F852" s="3"/>
       <c r="G852" s="3"/>
@@ -24897,7 +24913,7 @@
     <row r="853" ht="15.75" customHeight="1">
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
-      <c r="D853" s="10"/>
+      <c r="D853" s="9"/>
       <c r="E853" s="3"/>
       <c r="F853" s="3"/>
       <c r="G853" s="3"/>
@@ -24924,7 +24940,7 @@
     <row r="854" ht="15.75" customHeight="1">
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
-      <c r="D854" s="10"/>
+      <c r="D854" s="9"/>
       <c r="E854" s="3"/>
       <c r="F854" s="3"/>
       <c r="G854" s="3"/>
@@ -24951,7 +24967,7 @@
     <row r="855" ht="15.75" customHeight="1">
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
-      <c r="D855" s="10"/>
+      <c r="D855" s="9"/>
       <c r="E855" s="3"/>
       <c r="F855" s="3"/>
       <c r="G855" s="3"/>
@@ -24978,7 +24994,7 @@
     <row r="856" ht="15.75" customHeight="1">
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
-      <c r="D856" s="10"/>
+      <c r="D856" s="9"/>
       <c r="E856" s="3"/>
       <c r="F856" s="3"/>
       <c r="G856" s="3"/>
@@ -25005,7 +25021,7 @@
     <row r="857" ht="15.75" customHeight="1">
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
-      <c r="D857" s="10"/>
+      <c r="D857" s="9"/>
       <c r="E857" s="3"/>
       <c r="F857" s="3"/>
       <c r="G857" s="3"/>
@@ -25032,7 +25048,7 @@
     <row r="858" ht="15.75" customHeight="1">
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
-      <c r="D858" s="10"/>
+      <c r="D858" s="9"/>
       <c r="E858" s="3"/>
       <c r="F858" s="3"/>
       <c r="G858" s="3"/>
@@ -25059,7 +25075,7 @@
     <row r="859" ht="15.75" customHeight="1">
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
-      <c r="D859" s="10"/>
+      <c r="D859" s="9"/>
       <c r="E859" s="3"/>
       <c r="F859" s="3"/>
       <c r="G859" s="3"/>
@@ -25086,7 +25102,7 @@
     <row r="860" ht="15.75" customHeight="1">
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
-      <c r="D860" s="10"/>
+      <c r="D860" s="9"/>
       <c r="E860" s="3"/>
       <c r="F860" s="3"/>
       <c r="G860" s="3"/>
@@ -25113,7 +25129,7 @@
     <row r="861" ht="15.75" customHeight="1">
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
-      <c r="D861" s="10"/>
+      <c r="D861" s="9"/>
       <c r="E861" s="3"/>
       <c r="F861" s="3"/>
       <c r="G861" s="3"/>
@@ -25140,7 +25156,7 @@
     <row r="862" ht="15.75" customHeight="1">
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
-      <c r="D862" s="10"/>
+      <c r="D862" s="9"/>
       <c r="E862" s="3"/>
       <c r="F862" s="3"/>
       <c r="G862" s="3"/>
@@ -25167,7 +25183,7 @@
     <row r="863" ht="15.75" customHeight="1">
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
-      <c r="D863" s="10"/>
+      <c r="D863" s="9"/>
       <c r="E863" s="3"/>
       <c r="F863" s="3"/>
       <c r="G863" s="3"/>
@@ -25194,7 +25210,7 @@
     <row r="864" ht="15.75" customHeight="1">
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
-      <c r="D864" s="10"/>
+      <c r="D864" s="9"/>
       <c r="E864" s="3"/>
       <c r="F864" s="3"/>
       <c r="G864" s="3"/>
@@ -25221,7 +25237,7 @@
     <row r="865" ht="15.75" customHeight="1">
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
-      <c r="D865" s="10"/>
+      <c r="D865" s="9"/>
       <c r="E865" s="3"/>
       <c r="F865" s="3"/>
       <c r="G865" s="3"/>
@@ -25248,7 +25264,7 @@
     <row r="866" ht="15.75" customHeight="1">
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
-      <c r="D866" s="10"/>
+      <c r="D866" s="9"/>
       <c r="E866" s="3"/>
       <c r="F866" s="3"/>
       <c r="G866" s="3"/>
@@ -25275,7 +25291,7 @@
     <row r="867" ht="15.75" customHeight="1">
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
-      <c r="D867" s="10"/>
+      <c r="D867" s="9"/>
       <c r="E867" s="3"/>
       <c r="F867" s="3"/>
       <c r="G867" s="3"/>
@@ -25302,7 +25318,7 @@
     <row r="868" ht="15.75" customHeight="1">
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
-      <c r="D868" s="10"/>
+      <c r="D868" s="9"/>
       <c r="E868" s="3"/>
       <c r="F868" s="3"/>
       <c r="G868" s="3"/>
@@ -25329,7 +25345,7 @@
     <row r="869" ht="15.75" customHeight="1">
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
-      <c r="D869" s="10"/>
+      <c r="D869" s="9"/>
       <c r="E869" s="3"/>
       <c r="F869" s="3"/>
       <c r="G869" s="3"/>
@@ -25356,7 +25372,7 @@
     <row r="870" ht="15.75" customHeight="1">
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
-      <c r="D870" s="10"/>
+      <c r="D870" s="9"/>
       <c r="E870" s="3"/>
       <c r="F870" s="3"/>
       <c r="G870" s="3"/>
@@ -25383,7 +25399,7 @@
     <row r="871" ht="15.75" customHeight="1">
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
-      <c r="D871" s="10"/>
+      <c r="D871" s="9"/>
       <c r="E871" s="3"/>
       <c r="F871" s="3"/>
       <c r="G871" s="3"/>
@@ -25410,7 +25426,7 @@
     <row r="872" ht="15.75" customHeight="1">
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
-      <c r="D872" s="10"/>
+      <c r="D872" s="9"/>
       <c r="E872" s="3"/>
       <c r="F872" s="3"/>
       <c r="G872" s="3"/>
@@ -25437,7 +25453,7 @@
     <row r="873" ht="15.75" customHeight="1">
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
-      <c r="D873" s="10"/>
+      <c r="D873" s="9"/>
       <c r="E873" s="3"/>
       <c r="F873" s="3"/>
       <c r="G873" s="3"/>
@@ -25464,7 +25480,7 @@
     <row r="874" ht="15.75" customHeight="1">
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
-      <c r="D874" s="10"/>
+      <c r="D874" s="9"/>
       <c r="E874" s="3"/>
       <c r="F874" s="3"/>
       <c r="G874" s="3"/>
@@ -25491,7 +25507,7 @@
     <row r="875" ht="15.75" customHeight="1">
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
-      <c r="D875" s="10"/>
+      <c r="D875" s="9"/>
       <c r="E875" s="3"/>
       <c r="F875" s="3"/>
       <c r="G875" s="3"/>
@@ -25518,7 +25534,7 @@
     <row r="876" ht="15.75" customHeight="1">
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
-      <c r="D876" s="10"/>
+      <c r="D876" s="9"/>
       <c r="E876" s="3"/>
       <c r="F876" s="3"/>
       <c r="G876" s="3"/>
@@ -25545,7 +25561,7 @@
     <row r="877" ht="15.75" customHeight="1">
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
-      <c r="D877" s="10"/>
+      <c r="D877" s="9"/>
       <c r="E877" s="3"/>
       <c r="F877" s="3"/>
       <c r="G877" s="3"/>
@@ -25572,7 +25588,7 @@
     <row r="878" ht="15.75" customHeight="1">
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
-      <c r="D878" s="10"/>
+      <c r="D878" s="9"/>
       <c r="E878" s="3"/>
       <c r="F878" s="3"/>
       <c r="G878" s="3"/>
@@ -25599,7 +25615,7 @@
     <row r="879" ht="15.75" customHeight="1">
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
-      <c r="D879" s="10"/>
+      <c r="D879" s="9"/>
       <c r="E879" s="3"/>
       <c r="F879" s="3"/>
       <c r="G879" s="3"/>
@@ -25626,7 +25642,7 @@
     <row r="880" ht="15.75" customHeight="1">
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
-      <c r="D880" s="10"/>
+      <c r="D880" s="9"/>
       <c r="E880" s="3"/>
       <c r="F880" s="3"/>
       <c r="G880" s="3"/>
@@ -25653,7 +25669,7 @@
     <row r="881" ht="15.75" customHeight="1">
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
-      <c r="D881" s="10"/>
+      <c r="D881" s="9"/>
       <c r="E881" s="3"/>
       <c r="F881" s="3"/>
       <c r="G881" s="3"/>
@@ -25680,7 +25696,7 @@
     <row r="882" ht="15.75" customHeight="1">
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
-      <c r="D882" s="10"/>
+      <c r="D882" s="9"/>
       <c r="E882" s="3"/>
       <c r="F882" s="3"/>
       <c r="G882" s="3"/>
@@ -25707,7 +25723,7 @@
     <row r="883" ht="15.75" customHeight="1">
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
-      <c r="D883" s="10"/>
+      <c r="D883" s="9"/>
       <c r="E883" s="3"/>
       <c r="F883" s="3"/>
       <c r="G883" s="3"/>
@@ -25734,7 +25750,7 @@
     <row r="884" ht="15.75" customHeight="1">
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
-      <c r="D884" s="10"/>
+      <c r="D884" s="9"/>
       <c r="E884" s="3"/>
       <c r="F884" s="3"/>
       <c r="G884" s="3"/>
@@ -25761,7 +25777,7 @@
     <row r="885" ht="15.75" customHeight="1">
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
-      <c r="D885" s="10"/>
+      <c r="D885" s="9"/>
       <c r="E885" s="3"/>
       <c r="F885" s="3"/>
       <c r="G885" s="3"/>
@@ -25788,7 +25804,7 @@
     <row r="886" ht="15.75" customHeight="1">
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
-      <c r="D886" s="10"/>
+      <c r="D886" s="9"/>
       <c r="E886" s="3"/>
       <c r="F886" s="3"/>
       <c r="G886" s="3"/>
@@ -25815,7 +25831,7 @@
     <row r="887" ht="15.75" customHeight="1">
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
-      <c r="D887" s="10"/>
+      <c r="D887" s="9"/>
       <c r="E887" s="3"/>
       <c r="F887" s="3"/>
       <c r="G887" s="3"/>
@@ -25842,7 +25858,7 @@
     <row r="888" ht="15.75" customHeight="1">
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
-      <c r="D888" s="10"/>
+      <c r="D888" s="9"/>
       <c r="E888" s="3"/>
       <c r="F888" s="3"/>
       <c r="G888" s="3"/>
@@ -25869,7 +25885,7 @@
     <row r="889" ht="15.75" customHeight="1">
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
-      <c r="D889" s="10"/>
+      <c r="D889" s="9"/>
       <c r="E889" s="3"/>
       <c r="F889" s="3"/>
       <c r="G889" s="3"/>
@@ -25896,7 +25912,7 @@
     <row r="890" ht="15.75" customHeight="1">
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
-      <c r="D890" s="10"/>
+      <c r="D890" s="9"/>
       <c r="E890" s="3"/>
       <c r="F890" s="3"/>
       <c r="G890" s="3"/>
@@ -25923,7 +25939,7 @@
     <row r="891" ht="15.75" customHeight="1">
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
-      <c r="D891" s="10"/>
+      <c r="D891" s="9"/>
       <c r="E891" s="3"/>
       <c r="F891" s="3"/>
       <c r="G891" s="3"/>
@@ -25950,7 +25966,7 @@
     <row r="892" ht="15.75" customHeight="1">
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
-      <c r="D892" s="10"/>
+      <c r="D892" s="9"/>
       <c r="E892" s="3"/>
       <c r="F892" s="3"/>
       <c r="G892" s="3"/>
@@ -25977,7 +25993,7 @@
     <row r="893" ht="15.75" customHeight="1">
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
-      <c r="D893" s="10"/>
+      <c r="D893" s="9"/>
       <c r="E893" s="3"/>
       <c r="F893" s="3"/>
       <c r="G893" s="3"/>
@@ -26004,7 +26020,7 @@
     <row r="894" ht="15.75" customHeight="1">
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
-      <c r="D894" s="10"/>
+      <c r="D894" s="9"/>
       <c r="E894" s="3"/>
       <c r="F894" s="3"/>
       <c r="G894" s="3"/>
@@ -26031,7 +26047,7 @@
     <row r="895" ht="15.75" customHeight="1">
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
-      <c r="D895" s="10"/>
+      <c r="D895" s="9"/>
       <c r="E895" s="3"/>
       <c r="F895" s="3"/>
       <c r="G895" s="3"/>
@@ -26058,7 +26074,7 @@
     <row r="896" ht="15.75" customHeight="1">
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
-      <c r="D896" s="10"/>
+      <c r="D896" s="9"/>
       <c r="E896" s="3"/>
       <c r="F896" s="3"/>
       <c r="G896" s="3"/>
@@ -26085,7 +26101,7 @@
     <row r="897" ht="15.75" customHeight="1">
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
-      <c r="D897" s="10"/>
+      <c r="D897" s="9"/>
       <c r="E897" s="3"/>
       <c r="F897" s="3"/>
       <c r="G897" s="3"/>
@@ -26112,7 +26128,7 @@
     <row r="898" ht="15.75" customHeight="1">
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
-      <c r="D898" s="10"/>
+      <c r="D898" s="9"/>
       <c r="E898" s="3"/>
       <c r="F898" s="3"/>
       <c r="G898" s="3"/>
@@ -26139,7 +26155,7 @@
     <row r="899" ht="15.75" customHeight="1">
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
-      <c r="D899" s="10"/>
+      <c r="D899" s="9"/>
       <c r="E899" s="3"/>
       <c r="F899" s="3"/>
       <c r="G899" s="3"/>
@@ -26166,7 +26182,7 @@
     <row r="900" ht="15.75" customHeight="1">
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
-      <c r="D900" s="10"/>
+      <c r="D900" s="9"/>
       <c r="E900" s="3"/>
       <c r="F900" s="3"/>
       <c r="G900" s="3"/>
@@ -26193,7 +26209,7 @@
     <row r="901" ht="15.75" customHeight="1">
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
-      <c r="D901" s="10"/>
+      <c r="D901" s="9"/>
       <c r="E901" s="3"/>
       <c r="F901" s="3"/>
       <c r="G901" s="3"/>
@@ -26220,7 +26236,7 @@
     <row r="902" ht="15.75" customHeight="1">
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
-      <c r="D902" s="10"/>
+      <c r="D902" s="9"/>
       <c r="E902" s="3"/>
       <c r="F902" s="3"/>
       <c r="G902" s="3"/>
@@ -26247,7 +26263,7 @@
     <row r="903" ht="15.75" customHeight="1">
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
-      <c r="D903" s="10"/>
+      <c r="D903" s="9"/>
       <c r="E903" s="3"/>
       <c r="F903" s="3"/>
       <c r="G903" s="3"/>
@@ -26274,7 +26290,7 @@
     <row r="904" ht="15.75" customHeight="1">
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
-      <c r="D904" s="10"/>
+      <c r="D904" s="9"/>
       <c r="E904" s="3"/>
       <c r="F904" s="3"/>
       <c r="G904" s="3"/>
@@ -26301,7 +26317,7 @@
     <row r="905" ht="15.75" customHeight="1">
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
-      <c r="D905" s="10"/>
+      <c r="D905" s="9"/>
       <c r="E905" s="3"/>
       <c r="F905" s="3"/>
       <c r="G905" s="3"/>
@@ -26328,7 +26344,7 @@
     <row r="906" ht="15.75" customHeight="1">
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
-      <c r="D906" s="10"/>
+      <c r="D906" s="9"/>
       <c r="E906" s="3"/>
       <c r="F906" s="3"/>
       <c r="G906" s="3"/>
@@ -26355,7 +26371,7 @@
     <row r="907" ht="15.75" customHeight="1">
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
-      <c r="D907" s="10"/>
+      <c r="D907" s="9"/>
       <c r="E907" s="3"/>
       <c r="F907" s="3"/>
       <c r="G907" s="3"/>
@@ -26382,7 +26398,7 @@
     <row r="908" ht="15.75" customHeight="1">
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
-      <c r="D908" s="10"/>
+      <c r="D908" s="9"/>
       <c r="E908" s="3"/>
       <c r="F908" s="3"/>
       <c r="G908" s="3"/>
@@ -26409,7 +26425,7 @@
     <row r="909" ht="15.75" customHeight="1">
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
-      <c r="D909" s="10"/>
+      <c r="D909" s="9"/>
       <c r="E909" s="3"/>
       <c r="F909" s="3"/>
       <c r="G909" s="3"/>
@@ -26436,7 +26452,7 @@
     <row r="910" ht="15.75" customHeight="1">
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
-      <c r="D910" s="10"/>
+      <c r="D910" s="9"/>
       <c r="E910" s="3"/>
       <c r="F910" s="3"/>
       <c r="G910" s="3"/>
@@ -26463,7 +26479,7 @@
     <row r="911" ht="15.75" customHeight="1">
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
-      <c r="D911" s="10"/>
+      <c r="D911" s="9"/>
       <c r="E911" s="3"/>
       <c r="F911" s="3"/>
       <c r="G911" s="3"/>
@@ -26490,7 +26506,7 @@
     <row r="912" ht="15.75" customHeight="1">
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
-      <c r="D912" s="10"/>
+      <c r="D912" s="9"/>
       <c r="E912" s="3"/>
       <c r="F912" s="3"/>
       <c r="G912" s="3"/>
@@ -26517,7 +26533,7 @@
     <row r="913" ht="15.75" customHeight="1">
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
-      <c r="D913" s="10"/>
+      <c r="D913" s="9"/>
       <c r="E913" s="3"/>
       <c r="F913" s="3"/>
       <c r="G913" s="3"/>
@@ -26544,7 +26560,7 @@
     <row r="914" ht="15.75" customHeight="1">
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
-      <c r="D914" s="10"/>
+      <c r="D914" s="9"/>
       <c r="E914" s="3"/>
       <c r="F914" s="3"/>
       <c r="G914" s="3"/>
@@ -26571,7 +26587,7 @@
     <row r="915" ht="15.75" customHeight="1">
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
-      <c r="D915" s="10"/>
+      <c r="D915" s="9"/>
       <c r="E915" s="3"/>
       <c r="F915" s="3"/>
       <c r="G915" s="3"/>
@@ -26598,7 +26614,7 @@
     <row r="916" ht="15.75" customHeight="1">
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
-      <c r="D916" s="10"/>
+      <c r="D916" s="9"/>
       <c r="E916" s="3"/>
       <c r="F916" s="3"/>
       <c r="G916" s="3"/>
@@ -26625,7 +26641,7 @@
     <row r="917" ht="15.75" customHeight="1">
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
-      <c r="D917" s="10"/>
+      <c r="D917" s="9"/>
       <c r="E917" s="3"/>
       <c r="F917" s="3"/>
       <c r="G917" s="3"/>
@@ -26652,7 +26668,7 @@
     <row r="918" ht="15.75" customHeight="1">
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
-      <c r="D918" s="10"/>
+      <c r="D918" s="9"/>
       <c r="E918" s="3"/>
       <c r="F918" s="3"/>
       <c r="G918" s="3"/>
@@ -26679,7 +26695,7 @@
     <row r="919" ht="15.75" customHeight="1">
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
-      <c r="D919" s="10"/>
+      <c r="D919" s="9"/>
       <c r="E919" s="3"/>
       <c r="F919" s="3"/>
       <c r="G919" s="3"/>
@@ -26706,7 +26722,7 @@
     <row r="920" ht="15.75" customHeight="1">
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
-      <c r="D920" s="10"/>
+      <c r="D920" s="9"/>
       <c r="E920" s="3"/>
       <c r="F920" s="3"/>
       <c r="G920" s="3"/>
@@ -26733,7 +26749,7 @@
     <row r="921" ht="15.75" customHeight="1">
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
-      <c r="D921" s="10"/>
+      <c r="D921" s="9"/>
       <c r="E921" s="3"/>
       <c r="F921" s="3"/>
       <c r="G921" s="3"/>
@@ -26760,7 +26776,7 @@
     <row r="922" ht="15.75" customHeight="1">
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
-      <c r="D922" s="10"/>
+      <c r="D922" s="9"/>
       <c r="E922" s="3"/>
       <c r="F922" s="3"/>
       <c r="G922" s="3"/>
@@ -26787,7 +26803,7 @@
     <row r="923" ht="15.75" customHeight="1">
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
-      <c r="D923" s="10"/>
+      <c r="D923" s="9"/>
       <c r="E923" s="3"/>
       <c r="F923" s="3"/>
       <c r="G923" s="3"/>
@@ -26814,7 +26830,7 @@
     <row r="924" ht="15.75" customHeight="1">
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
-      <c r="D924" s="10"/>
+      <c r="D924" s="9"/>
       <c r="E924" s="3"/>
       <c r="F924" s="3"/>
       <c r="G924" s="3"/>
@@ -26841,7 +26857,7 @@
     <row r="925" ht="15.75" customHeight="1">
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
-      <c r="D925" s="10"/>
+      <c r="D925" s="9"/>
       <c r="E925" s="3"/>
       <c r="F925" s="3"/>
       <c r="G925" s="3"/>
@@ -26868,7 +26884,7 @@
     <row r="926" ht="15.75" customHeight="1">
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
-      <c r="D926" s="10"/>
+      <c r="D926" s="9"/>
       <c r="E926" s="3"/>
       <c r="F926" s="3"/>
       <c r="G926" s="3"/>
@@ -26895,7 +26911,7 @@
     <row r="927" ht="15.75" customHeight="1">
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
-      <c r="D927" s="10"/>
+      <c r="D927" s="9"/>
       <c r="E927" s="3"/>
       <c r="F927" s="3"/>
       <c r="G927" s="3"/>
@@ -26922,7 +26938,7 @@
     <row r="928" ht="15.75" customHeight="1">
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
-      <c r="D928" s="10"/>
+      <c r="D928" s="9"/>
       <c r="E928" s="3"/>
       <c r="F928" s="3"/>
       <c r="G928" s="3"/>
@@ -26949,7 +26965,7 @@
     <row r="929" ht="15.75" customHeight="1">
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
-      <c r="D929" s="10"/>
+      <c r="D929" s="9"/>
       <c r="E929" s="3"/>
       <c r="F929" s="3"/>
       <c r="G929" s="3"/>
@@ -26976,7 +26992,7 @@
     <row r="930" ht="15.75" customHeight="1">
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
-      <c r="D930" s="10"/>
+      <c r="D930" s="9"/>
       <c r="E930" s="3"/>
       <c r="F930" s="3"/>
       <c r="G930" s="3"/>
@@ -27003,7 +27019,7 @@
     <row r="931" ht="15.75" customHeight="1">
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
-      <c r="D931" s="10"/>
+      <c r="D931" s="9"/>
       <c r="E931" s="3"/>
       <c r="F931" s="3"/>
       <c r="G931" s="3"/>
@@ -27030,7 +27046,7 @@
     <row r="932" ht="15.75" customHeight="1">
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
-      <c r="D932" s="10"/>
+      <c r="D932" s="9"/>
       <c r="E932" s="3"/>
       <c r="F932" s="3"/>
       <c r="G932" s="3"/>
@@ -27057,7 +27073,7 @@
     <row r="933" ht="15.75" customHeight="1">
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
-      <c r="D933" s="10"/>
+      <c r="D933" s="9"/>
       <c r="E933" s="3"/>
       <c r="F933" s="3"/>
       <c r="G933" s="3"/>
@@ -27084,7 +27100,7 @@
     <row r="934" ht="15.75" customHeight="1">
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
-      <c r="D934" s="10"/>
+      <c r="D934" s="9"/>
       <c r="E934" s="3"/>
       <c r="F934" s="3"/>
       <c r="G934" s="3"/>
@@ -27111,7 +27127,7 @@
     <row r="935" ht="15.75" customHeight="1">
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
-      <c r="D935" s="10"/>
+      <c r="D935" s="9"/>
       <c r="E935" s="3"/>
       <c r="F935" s="3"/>
       <c r="G935" s="3"/>
@@ -27138,7 +27154,7 @@
     <row r="936" ht="15.75" customHeight="1">
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
-      <c r="D936" s="10"/>
+      <c r="D936" s="9"/>
       <c r="E936" s="3"/>
       <c r="F936" s="3"/>
       <c r="G936" s="3"/>
@@ -27165,7 +27181,7 @@
     <row r="937" ht="15.75" customHeight="1">
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
-      <c r="D937" s="10"/>
+      <c r="D937" s="9"/>
       <c r="E937" s="3"/>
       <c r="F937" s="3"/>
       <c r="G937" s="3"/>
@@ -27192,7 +27208,7 @@
     <row r="938" ht="15.75" customHeight="1">
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
-      <c r="D938" s="10"/>
+      <c r="D938" s="9"/>
       <c r="E938" s="3"/>
       <c r="F938" s="3"/>
       <c r="G938" s="3"/>
@@ -27219,7 +27235,7 @@
     <row r="939" ht="15.75" customHeight="1">
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
-      <c r="D939" s="10"/>
+      <c r="D939" s="9"/>
       <c r="E939" s="3"/>
       <c r="F939" s="3"/>
       <c r="G939" s="3"/>
@@ -27246,7 +27262,7 @@
     <row r="940" ht="15.75" customHeight="1">
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
-      <c r="D940" s="10"/>
+      <c r="D940" s="9"/>
       <c r="E940" s="3"/>
       <c r="F940" s="3"/>
       <c r="G940" s="3"/>
@@ -27273,7 +27289,7 @@
     <row r="941" ht="15.75" customHeight="1">
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
-      <c r="D941" s="10"/>
+      <c r="D941" s="9"/>
       <c r="E941" s="3"/>
       <c r="F941" s="3"/>
       <c r="G941" s="3"/>
@@ -27300,7 +27316,7 @@
     <row r="942" ht="15.75" customHeight="1">
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
-      <c r="D942" s="10"/>
+      <c r="D942" s="9"/>
       <c r="E942" s="3"/>
       <c r="F942" s="3"/>
       <c r="G942" s="3"/>
@@ -27327,7 +27343,7 @@
     <row r="943" ht="15.75" customHeight="1">
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
-      <c r="D943" s="10"/>
+      <c r="D943" s="9"/>
       <c r="E943" s="3"/>
       <c r="F943" s="3"/>
       <c r="G943" s="3"/>
@@ -27354,7 +27370,7 @@
     <row r="944" ht="15.75" customHeight="1">
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
-      <c r="D944" s="10"/>
+      <c r="D944" s="9"/>
       <c r="E944" s="3"/>
       <c r="F944" s="3"/>
       <c r="G944" s="3"/>
@@ -27381,7 +27397,7 @@
     <row r="945" ht="15.75" customHeight="1">
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
-      <c r="D945" s="10"/>
+      <c r="D945" s="9"/>
       <c r="E945" s="3"/>
       <c r="F945" s="3"/>
       <c r="G945" s="3"/>
@@ -27408,7 +27424,7 @@
     <row r="946" ht="15.75" customHeight="1">
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
-      <c r="D946" s="10"/>
+      <c r="D946" s="9"/>
       <c r="E946" s="3"/>
       <c r="F946" s="3"/>
       <c r="G946" s="3"/>
@@ -27435,7 +27451,7 @@
     <row r="947" ht="15.75" customHeight="1">
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
-      <c r="D947" s="10"/>
+      <c r="D947" s="9"/>
       <c r="E947" s="3"/>
       <c r="F947" s="3"/>
       <c r="G947" s="3"/>
@@ -27462,7 +27478,7 @@
     <row r="948" ht="15.75" customHeight="1">
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
-      <c r="D948" s="10"/>
+      <c r="D948" s="9"/>
       <c r="E948" s="3"/>
       <c r="F948" s="3"/>
       <c r="G948" s="3"/>
@@ -27489,7 +27505,7 @@
     <row r="949" ht="15.75" customHeight="1">
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
-      <c r="D949" s="10"/>
+      <c r="D949" s="9"/>
       <c r="E949" s="3"/>
       <c r="F949" s="3"/>
       <c r="G949" s="3"/>
@@ -27516,7 +27532,7 @@
     <row r="950" ht="15.75" customHeight="1">
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
-      <c r="D950" s="10"/>
+      <c r="D950" s="9"/>
       <c r="E950" s="3"/>
       <c r="F950" s="3"/>
       <c r="G950" s="3"/>
@@ -27543,7 +27559,7 @@
     <row r="951" ht="15.75" customHeight="1">
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
-      <c r="D951" s="10"/>
+      <c r="D951" s="9"/>
       <c r="E951" s="3"/>
       <c r="F951" s="3"/>
       <c r="G951" s="3"/>
@@ -27570,7 +27586,7 @@
     <row r="952" ht="15.75" customHeight="1">
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
-      <c r="D952" s="10"/>
+      <c r="D952" s="9"/>
       <c r="E952" s="3"/>
       <c r="F952" s="3"/>
       <c r="G952" s="3"/>
@@ -27597,7 +27613,7 @@
     <row r="953" ht="15.75" customHeight="1">
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
-      <c r="D953" s="10"/>
+      <c r="D953" s="9"/>
       <c r="E953" s="3"/>
       <c r="F953" s="3"/>
       <c r="G953" s="3"/>
@@ -27624,7 +27640,7 @@
     <row r="954" ht="15.75" customHeight="1">
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
-      <c r="D954" s="10"/>
+      <c r="D954" s="9"/>
       <c r="E954" s="3"/>
       <c r="F954" s="3"/>
       <c r="G954" s="3"/>
@@ -27651,7 +27667,7 @@
     <row r="955" ht="15.75" customHeight="1">
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
-      <c r="D955" s="10"/>
+      <c r="D955" s="9"/>
       <c r="E955" s="3"/>
       <c r="F955" s="3"/>
       <c r="G955" s="3"/>
@@ -27678,7 +27694,7 @@
     <row r="956" ht="15.75" customHeight="1">
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
-      <c r="D956" s="10"/>
+      <c r="D956" s="9"/>
       <c r="E956" s="3"/>
       <c r="F956" s="3"/>
       <c r="G956" s="3"/>
@@ -27705,7 +27721,7 @@
     <row r="957" ht="15.75" customHeight="1">
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
-      <c r="D957" s="10"/>
+      <c r="D957" s="9"/>
       <c r="E957" s="3"/>
       <c r="F957" s="3"/>
       <c r="G957" s="3"/>
@@ -27732,7 +27748,7 @@
     <row r="958" ht="15.75" customHeight="1">
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
-      <c r="D958" s="10"/>
+      <c r="D958" s="9"/>
       <c r="E958" s="3"/>
       <c r="F958" s="3"/>
       <c r="G958" s="3"/>
@@ -27759,7 +27775,7 @@
     <row r="959" ht="15.75" customHeight="1">
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
-      <c r="D959" s="10"/>
+      <c r="D959" s="9"/>
       <c r="E959" s="3"/>
       <c r="F959" s="3"/>
       <c r="G959" s="3"/>
@@ -27786,7 +27802,7 @@
     <row r="960" ht="15.75" customHeight="1">
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
-      <c r="D960" s="10"/>
+      <c r="D960" s="9"/>
       <c r="E960" s="3"/>
       <c r="F960" s="3"/>
       <c r="G960" s="3"/>
@@ -27813,7 +27829,7 @@
     <row r="961" ht="15.75" customHeight="1">
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
-      <c r="D961" s="10"/>
+      <c r="D961" s="9"/>
       <c r="E961" s="3"/>
       <c r="F961" s="3"/>
       <c r="G961" s="3"/>
@@ -27840,7 +27856,7 @@
     <row r="962" ht="15.75" customHeight="1">
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
-      <c r="D962" s="10"/>
+      <c r="D962" s="9"/>
       <c r="E962" s="3"/>
       <c r="F962" s="3"/>
       <c r="G962" s="3"/>
@@ -27867,7 +27883,7 @@
     <row r="963" ht="15.75" customHeight="1">
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
-      <c r="D963" s="10"/>
+      <c r="D963" s="9"/>
       <c r="E963" s="3"/>
       <c r="F963" s="3"/>
       <c r="G963" s="3"/>
@@ -27894,7 +27910,7 @@
     <row r="964" ht="15.75" customHeight="1">
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
-      <c r="D964" s="10"/>
+      <c r="D964" s="9"/>
       <c r="E964" s="3"/>
       <c r="F964" s="3"/>
       <c r="G964" s="3"/>
@@ -27921,7 +27937,7 @@
     <row r="965" ht="15.75" customHeight="1">
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
-      <c r="D965" s="10"/>
+      <c r="D965" s="9"/>
       <c r="E965" s="3"/>
       <c r="F965" s="3"/>
       <c r="G965" s="3"/>
@@ -27948,7 +27964,7 @@
     <row r="966" ht="15.75" customHeight="1">
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
-      <c r="D966" s="10"/>
+      <c r="D966" s="9"/>
       <c r="E966" s="3"/>
       <c r="F966" s="3"/>
       <c r="G966" s="3"/>
@@ -27975,7 +27991,7 @@
     <row r="967" ht="15.75" customHeight="1">
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
-      <c r="D967" s="10"/>
+      <c r="D967" s="9"/>
       <c r="E967" s="3"/>
       <c r="F967" s="3"/>
       <c r="G967" s="3"/>
@@ -28002,7 +28018,7 @@
     <row r="968" ht="15.75" customHeight="1">
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
-      <c r="D968" s="10"/>
+      <c r="D968" s="9"/>
       <c r="E968" s="3"/>
       <c r="F968" s="3"/>
       <c r="G968" s="3"/>
@@ -28029,7 +28045,7 @@
     <row r="969" ht="15.75" customHeight="1">
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
-      <c r="D969" s="10"/>
+      <c r="D969" s="9"/>
       <c r="E969" s="3"/>
       <c r="F969" s="3"/>
       <c r="G969" s="3"/>
@@ -28056,7 +28072,7 @@
     <row r="970" ht="15.75" customHeight="1">
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
-      <c r="D970" s="10"/>
+      <c r="D970" s="9"/>
       <c r="E970" s="3"/>
       <c r="F970" s="3"/>
       <c r="G970" s="3"/>
@@ -28083,7 +28099,7 @@
     <row r="971" ht="15.75" customHeight="1">
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
-      <c r="D971" s="10"/>
+      <c r="D971" s="9"/>
       <c r="E971" s="3"/>
       <c r="F971" s="3"/>
       <c r="G971" s="3"/>
@@ -28110,7 +28126,7 @@
     <row r="972" ht="15.75" customHeight="1">
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
-      <c r="D972" s="10"/>
+      <c r="D972" s="9"/>
       <c r="E972" s="3"/>
       <c r="F972" s="3"/>
       <c r="G972" s="3"/>
@@ -28134,8 +28150,35 @@
       <c r="Y972" s="3"/>
       <c r="Z972" s="3"/>
     </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="B973" s="3"/>
+      <c r="C973" s="3"/>
+      <c r="D973" s="9"/>
+      <c r="E973" s="3"/>
+      <c r="F973" s="3"/>
+      <c r="G973" s="3"/>
+      <c r="H973" s="3"/>
+      <c r="I973" s="3"/>
+      <c r="J973" s="3"/>
+      <c r="K973" s="3"/>
+      <c r="L973" s="3"/>
+      <c r="M973" s="3"/>
+      <c r="N973" s="3"/>
+      <c r="O973" s="3"/>
+      <c r="P973" s="3"/>
+      <c r="Q973" s="3"/>
+      <c r="R973" s="3"/>
+      <c r="S973" s="3"/>
+      <c r="T973" s="3"/>
+      <c r="U973" s="3"/>
+      <c r="V973" s="3"/>
+      <c r="W973" s="3"/>
+      <c r="X973" s="3"/>
+      <c r="Y973" s="3"/>
+      <c r="Z973" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$D$1:$D$972"/>
+  <autoFilter ref="$D$1:$D$973"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
